--- a/25-11-pdf-Analyzer/analyse_ergebnisse_v4-Zahlenbuch6.xlsx
+++ b/25-11-pdf-Analyzer/analyse_ergebnisse_v4-Zahlenbuch6.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/131a8beddc4e0454/01JupyterAndCo/04GitHub/GitHubCloneMBP/richard4231.github.io/25-11-pdf-Analyzer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="205" documentId="8_{BE8529B4-A718-E347-A274-C290A7E4C617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D60D0D7-3FF8-FA46-8815-3268220B6CE3}"/>
+  <xr:revisionPtr revIDLastSave="207" documentId="8_{BE8529B4-A718-E347-A274-C290A7E4C617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44C3E54C-9E32-B048-9875-DAA7FDE445C5}"/>
   <bookViews>
     <workbookView xWindow="13500" yWindow="620" windowWidth="13540" windowHeight="15880" xr2:uid="{FE24CF1A-29D8-AD43-BDC9-42C6FD31B724}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -1034,12 +1034,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20 % - Akzent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1087,6 +1086,12 @@
   </cellStyles>
   <dxfs count="4">
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="164" formatCode="0.0"/>
     </dxf>
     <dxf>
@@ -1094,12 +1099,6 @@
         <b/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1142,18 +1141,18 @@
   </sortState>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{713F0655-C542-7A4F-9F65-43EA0B990620}" name="Seite"/>
-    <tableColumn id="11" xr3:uid="{68591F43-D653-3B4D-AFCE-CDDBB8116C2F}" name="Schulbuchseite" dataDxfId="1">
+    <tableColumn id="11" xr3:uid="{68591F43-D653-3B4D-AFCE-CDDBB8116C2F}" name="Schulbuchseite" dataDxfId="3">
       <calculatedColumnFormula>Tabelle3[[#This Row],[Seite]]-1</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{0C8943D0-BA34-9D4E-9C4B-65C67530137F}" name="Anzahl"/>
     <tableColumn id="3" xr3:uid="{365A1A6A-AA82-5A4C-8142-37D7D164D27D}" name="Rang"/>
-    <tableColumn id="4" xr3:uid="{39E0955D-5CFF-8E41-8A78-6EEB19A95E4D}" name="Summe Score" dataDxfId="0">
+    <tableColumn id="4" xr3:uid="{39E0955D-5CFF-8E41-8A78-6EEB19A95E4D}" name="Summe Score" dataDxfId="2">
       <calculatedColumnFormula array="1">SUMPRODUCT((Tabelle2[Seite]=V2)*Tabelle2[Score_Gewichtet])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{BFFBE5A2-D90A-D745-93F7-B8C800E92A76}" name="Thema" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{BFFBE5A2-D90A-D745-93F7-B8C800E92A76}" name="Thema" dataDxfId="1"/>
     <tableColumn id="5" xr3:uid="{AED20AEE-4193-0942-948A-59629141D377}" name="implizit"/>
     <tableColumn id="6" xr3:uid="{75F540EC-744A-C54D-97C2-0BCFC1FFC926}" name="explizit"/>
-    <tableColumn id="8" xr3:uid="{C58EF833-17CA-894A-9351-88284AD363A6}" name="ohne BNE-Bezug" dataDxfId="2">
+    <tableColumn id="8" xr3:uid="{C58EF833-17CA-894A-9351-88284AD363A6}" name="ohne BNE-Bezug" dataDxfId="0">
       <calculatedColumnFormula>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{4E2FBED5-25A2-2A4B-883F-8EAC087C589E}" name="Reflexionstiefe"/>
@@ -4964,7 +4963,7 @@
         <v>15.7</v>
       </c>
       <c r="AA51" s="2"/>
-      <c r="AD51" s="4" t="s">
+      <c r="AD51" t="s">
         <v>150</v>
       </c>
     </row>
@@ -5031,7 +5030,7 @@
         <v>44.75</v>
       </c>
       <c r="AA52" s="2"/>
-      <c r="AD52" s="4" t="s">
+      <c r="AD52" t="s">
         <v>150</v>
       </c>
     </row>
@@ -6025,7 +6024,7 @@
         <v>8</v>
       </c>
       <c r="T67">
-        <f t="shared" ref="T67:T117" si="3">RANK(S67, $S$2:$S$116)</f>
+        <f t="shared" ref="T67:T116" si="3">RANK(S67, $S$2:$S$116)</f>
         <v>75</v>
       </c>
       <c r="V67">
@@ -9090,7 +9089,7 @@
       </c>
       <c r="AA112" s="2"/>
     </row>
-    <row r="113" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>11</v>
       </c>
@@ -9154,7 +9153,7 @@
       </c>
       <c r="AA113" s="2"/>
     </row>
-    <row r="114" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>11</v>
       </c>
@@ -9217,9 +9216,8 @@
         <v>5.6</v>
       </c>
       <c r="AA114" s="2"/>
-      <c r="AD114" s="4"/>
-    </row>
-    <row r="115" spans="1:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="115" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>11</v>
       </c>
@@ -9282,9 +9280,8 @@
         <v>35.999999999999993</v>
       </c>
       <c r="AA115" s="2"/>
-      <c r="AD115" s="4"/>
-    </row>
-    <row r="116" spans="1:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="116" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>11</v>
       </c>
@@ -9347,9 +9344,8 @@
         <v>7.4</v>
       </c>
       <c r="AA116" s="2"/>
-      <c r="AD116" s="4"/>
-    </row>
-    <row r="117" spans="1:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="117" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>11</v>
       </c>
@@ -9386,9 +9382,8 @@
       <c r="W117" s="3"/>
       <c r="Z117" s="2"/>
       <c r="AA117" s="2"/>
-      <c r="AD117" s="4"/>
-    </row>
-    <row r="118" spans="1:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="118" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>11</v>
       </c>
@@ -9425,9 +9420,8 @@
       <c r="W118" s="3"/>
       <c r="Z118" s="2"/>
       <c r="AA118" s="2"/>
-      <c r="AD118" s="4"/>
-    </row>
-    <row r="119" spans="1:30" x14ac:dyDescent="0.2">
+    </row>
+    <row r="119" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>11</v>
       </c>
@@ -9462,7 +9456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>11</v>
       </c>
@@ -9497,7 +9491,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="121" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>11</v>
       </c>
@@ -9532,7 +9526,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="122" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>11</v>
       </c>
@@ -9567,7 +9561,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="123" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>11</v>
       </c>
@@ -9602,7 +9596,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="124" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>11</v>
       </c>
@@ -9637,7 +9631,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="125" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>11</v>
       </c>
@@ -9672,7 +9666,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="126" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>11</v>
       </c>
@@ -9707,7 +9701,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="127" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>11</v>
       </c>
@@ -9742,7 +9736,7 @@
         <v>3.35</v>
       </c>
     </row>
-    <row r="128" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>11</v>
       </c>
@@ -52128,6 +52122,16 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="Z2:Z116">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
   <ignoredErrors>
     <ignoredError sqref="AD2:AD40 AD81 AD83:AD84 AD100 AD104:AD116" calculatedColumn="1"/>

--- a/25-11-pdf-Analyzer/analyse_ergebnisse_v4-Zahlenbuch6.xlsx
+++ b/25-11-pdf-Analyzer/analyse_ergebnisse_v4-Zahlenbuch6.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/131a8beddc4e0454/01JupyterAndCo/04GitHub/GitHubCloneMBP/richard4231.github.io/25-11-pdf-Analyzer/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/131a8beddc4e0454/01JupyterAndCo/04GitHub/GitHubCloneMac/richard4231.github.io/25-11-pdf-Analyzer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="207" documentId="8_{BE8529B4-A718-E347-A274-C290A7E4C617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44C3E54C-9E32-B048-9875-DAA7FDE445C5}"/>
+  <xr:revisionPtr revIDLastSave="377" documentId="8_{BE8529B4-A718-E347-A274-C290A7E4C617}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3ACF2679-225B-6645-9CB2-B25F36D40E7D}"/>
   <bookViews>
-    <workbookView xWindow="13500" yWindow="620" windowWidth="13540" windowHeight="15880" xr2:uid="{FE24CF1A-29D8-AD43-BDC9-42C6FD31B724}"/>
+    <workbookView xWindow="20000" yWindow="880" windowWidth="13540" windowHeight="15880" xr2:uid="{FE24CF1A-29D8-AD43-BDC9-42C6FD31B724}"/>
   </bookViews>
   <sheets>
     <sheet name="analyse_ergebnisse" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5498" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5421" uniqueCount="175">
   <si>
     <t>PDF</t>
   </si>
@@ -495,22 +495,7 @@
     <t>Thema</t>
   </si>
   <si>
-    <t>implizit</t>
-  </si>
-  <si>
-    <t>explizit</t>
-  </si>
-  <si>
-    <t>ohne BNE-Bezug</t>
-  </si>
-  <si>
     <t>Reflexionstiefe</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>(x)</t>
   </si>
   <si>
     <t>Glossar</t>
@@ -542,6 +527,60 @@
   <si>
     <t>Sporttag planen</t>
   </si>
+  <si>
+    <t>Stufe BNE</t>
+  </si>
+  <si>
+    <t>Einschätzung Potenzial</t>
+  </si>
+  <si>
+    <t>Grössen auf Schiffen</t>
+  </si>
+  <si>
+    <t>Anderes Thema zu Mobilität</t>
+  </si>
+  <si>
+    <t>Überschlagsrechnung</t>
+  </si>
+  <si>
+    <t>Spinnen</t>
+  </si>
+  <si>
+    <t>Staffellauf</t>
+  </si>
+  <si>
+    <t>Zahlen zum Leben</t>
+  </si>
+  <si>
+    <t>Modellieren</t>
+  </si>
+  <si>
+    <t>BNE Kontext</t>
+  </si>
+  <si>
+    <t>BNE Bezug</t>
+  </si>
+  <si>
+    <t>Stufe 0</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Potenzial</t>
+  </si>
+  <si>
+    <t>hoch</t>
+  </si>
+  <si>
+    <t>mittel</t>
+  </si>
+  <si>
+    <t>tief</t>
+  </si>
+  <si>
+    <t>kein</t>
+  </si>
 </sst>
 </file>
 
@@ -550,7 +589,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -690,6 +729,13 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -990,7 +1036,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -1033,14 +1079,17 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="42" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20 % - Akzent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20 % - Akzent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20 % - Akzent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -1073,6 +1122,7 @@
     <cellStyle name="Gut" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Notiz" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Prozent" xfId="42" builtinId="5"/>
     <cellStyle name="Schlecht" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
     <cellStyle name="Überschrift" xfId="1" builtinId="15" customBuiltin="1"/>
@@ -1134,12 +1184,12 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F422D5D4-AE20-504F-BEA4-74148AE6A84B}" name="Tabelle3" displayName="Tabelle3" ref="V1:AE116" totalsRowShown="0">
-  <autoFilter ref="V1:AE116" xr:uid="{F422D5D4-AE20-504F-BEA4-74148AE6A84B}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="V2:AE116">
-    <sortCondition ref="W1:W116"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{F422D5D4-AE20-504F-BEA4-74148AE6A84B}" name="Tabelle3" displayName="Tabelle3" ref="Q1:Y107" totalsRowShown="0">
+  <autoFilter ref="Q1:Y107" xr:uid="{F422D5D4-AE20-504F-BEA4-74148AE6A84B}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="Q2:Y120">
+    <sortCondition ref="R1:R120"/>
   </sortState>
-  <tableColumns count="10">
+  <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{713F0655-C542-7A4F-9F65-43EA0B990620}" name="Seite"/>
     <tableColumn id="11" xr3:uid="{68591F43-D653-3B4D-AFCE-CDDBB8116C2F}" name="Schulbuchseite" dataDxfId="3">
       <calculatedColumnFormula>Tabelle3[[#This Row],[Seite]]-1</calculatedColumnFormula>
@@ -1147,15 +1197,12 @@
     <tableColumn id="2" xr3:uid="{0C8943D0-BA34-9D4E-9C4B-65C67530137F}" name="Anzahl"/>
     <tableColumn id="3" xr3:uid="{365A1A6A-AA82-5A4C-8142-37D7D164D27D}" name="Rang"/>
     <tableColumn id="4" xr3:uid="{39E0955D-5CFF-8E41-8A78-6EEB19A95E4D}" name="Summe Score" dataDxfId="2">
-      <calculatedColumnFormula array="1">SUMPRODUCT((Tabelle2[Seite]=V2)*Tabelle2[Score_Gewichtet])</calculatedColumnFormula>
+      <calculatedColumnFormula array="1">SUMPRODUCT((Tabelle2[Seite]=Q2)*Tabelle2[Score_Gewichtet])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{BFFBE5A2-D90A-D745-93F7-B8C800E92A76}" name="Thema" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{AED20AEE-4193-0942-948A-59629141D377}" name="implizit"/>
-    <tableColumn id="6" xr3:uid="{75F540EC-744A-C54D-97C2-0BCFC1FFC926}" name="explizit"/>
-    <tableColumn id="8" xr3:uid="{C58EF833-17CA-894A-9351-88284AD363A6}" name="ohne BNE-Bezug" dataDxfId="0">
-      <calculatedColumnFormula>IF(Tabelle3[[#This Row],[Summe Score]]&lt;5,"x","")</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="7" xr3:uid="{4E2FBED5-25A2-2A4B-883F-8EAC087C589E}" name="Reflexionstiefe"/>
+    <tableColumn id="5" xr3:uid="{AED20AEE-4193-0942-948A-59629141D377}" name="Stufe BNE"/>
+    <tableColumn id="6" xr3:uid="{75F540EC-744A-C54D-97C2-0BCFC1FFC926}" name="Reflexionstiefe"/>
+    <tableColumn id="8" xr3:uid="{C58EF833-17CA-894A-9351-88284AD363A6}" name="Einschätzung Potenzial" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1478,16 +1525,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FBC5847-98E4-414C-9659-3E229512BC38}">
-  <dimension ref="A1:AE1338"/>
+  <dimension ref="A1:Z1338"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="8" max="8" width="14.1640625" customWidth="1"/>
     <col min="10" max="10" width="16.5" customWidth="1"/>
     <col min="11" max="11" width="17.5" customWidth="1"/>
-    <col min="29" max="29" width="4.33203125" customWidth="1"/>
+    <col min="27" max="27" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1521,8 +1568,20 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="M1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N1" t="s">
+        <v>141</v>
+      </c>
+      <c r="O1" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>1</v>
+      </c>
       <c r="R1" t="s">
-        <v>1</v>
+        <v>143</v>
       </c>
       <c r="S1" t="s">
         <v>141</v>
@@ -1530,38 +1589,23 @@
       <c r="T1" t="s">
         <v>142</v>
       </c>
+      <c r="U1" t="s">
+        <v>144</v>
+      </c>
       <c r="V1" t="s">
-        <v>1</v>
+        <v>145</v>
       </c>
       <c r="W1" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="X1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="Y1" t="s">
-        <v>142</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>145</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>146</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>147</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>148</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1595,41 +1639,47 @@
       <c r="K2">
         <v>0.5</v>
       </c>
-      <c r="R2" cm="1">
-        <f t="array" ref="R2:R116">_xlfn.UNIQUE(B$2:B$1338)</f>
-        <v>2</v>
+      <c r="M2" cm="1">
+        <f t="array" ref="M2:M116">_xlfn.UNIQUE(B$2:B$1338)</f>
+        <v>2</v>
+      </c>
+      <c r="N2">
+        <f>COUNTIF(B$2:B$1338, M2)</f>
+        <v>3</v>
+      </c>
+      <c r="O2">
+        <f>RANK(N2, $N$2:$N$116)</f>
+        <v>108</v>
+      </c>
+      <c r="Q2">
+        <v>2</v>
+      </c>
+      <c r="R2" s="1">
+        <f>Tabelle3[[#This Row],[Seite]]-1</f>
+        <v>1</v>
       </c>
       <c r="S2">
-        <f>COUNTIF(B$2:B$1338, R2)</f>
         <v>3</v>
       </c>
       <c r="T2">
-        <f>RANK(S2, $S$2:$S$116)</f>
         <v>108</v>
       </c>
-      <c r="V2">
-        <v>2</v>
-      </c>
-      <c r="W2" s="1">
-        <f>Tabelle3[[#This Row],[Seite]]-1</f>
-        <v>1</v>
+      <c r="U2" s="2" cm="1">
+        <f t="array" ref="U2">SUMPRODUCT((Tabelle2[Seite]=Q2)*Tabelle2[Score_Gewichtet])</f>
+        <v>0.7</v>
+      </c>
+      <c r="V2" s="2"/>
+      <c r="W2">
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>108</v>
-      </c>
-      <c r="Z2" s="2" cm="1">
-        <f t="array" ref="Z2">SUMPRODUCT((Tabelle2[Seite]=V2)*Tabelle2[Score_Gewichtet])</f>
-        <v>0.7</v>
-      </c>
-      <c r="AA2" s="2"/>
-      <c r="AD2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1663,40 +1713,46 @@
       <c r="K3">
         <v>0.1</v>
       </c>
-      <c r="R3">
+      <c r="M3">
         <v>3</v>
       </c>
+      <c r="N3">
+        <f>COUNTIF(B$2:B$1338, M3)</f>
+        <v>2</v>
+      </c>
+      <c r="O3">
+        <f>RANK(N3, $N$2:$N$116)</f>
+        <v>112</v>
+      </c>
+      <c r="Q3">
+        <v>3</v>
+      </c>
+      <c r="R3" s="1">
+        <f>Tabelle3[[#This Row],[Seite]]-1</f>
+        <v>2</v>
+      </c>
       <c r="S3">
-        <f t="shared" ref="S3:S66" si="0">COUNTIF(B$2:B$1338, R3)</f>
         <v>2</v>
       </c>
       <c r="T3">
-        <f t="shared" ref="T3:T66" si="1">RANK(S3, $S$2:$S$116)</f>
         <v>112</v>
       </c>
-      <c r="V3">
-        <v>3</v>
-      </c>
-      <c r="W3" s="1">
-        <f>Tabelle3[[#This Row],[Seite]]-1</f>
-        <v>2</v>
+      <c r="U3" s="2" cm="1">
+        <f t="array" ref="U3">SUMPRODUCT((Tabelle2[Seite]=Q3)*Tabelle2[Score_Gewichtet])</f>
+        <v>1.35</v>
+      </c>
+      <c r="V3" s="2"/>
+      <c r="W3">
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>112</v>
-      </c>
-      <c r="Z3" s="2" cm="1">
-        <f t="array" ref="Z3">SUMPRODUCT((Tabelle2[Seite]=V3)*Tabelle2[Score_Gewichtet])</f>
-        <v>1.35</v>
-      </c>
-      <c r="AA3" s="2"/>
-      <c r="AD3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1730,40 +1786,46 @@
       <c r="K4">
         <v>0.1</v>
       </c>
-      <c r="R4">
+      <c r="M4">
         <v>4</v>
       </c>
-      <c r="S4">
-        <f t="shared" si="0"/>
+      <c r="N4">
+        <f>COUNTIF(B$2:B$1338, M4)</f>
         <v>5</v>
       </c>
-      <c r="T4">
-        <f t="shared" si="1"/>
+      <c r="O4">
+        <f>RANK(N4, $N$2:$N$116)</f>
         <v>100</v>
       </c>
-      <c r="V4">
+      <c r="Q4">
         <v>4</v>
       </c>
-      <c r="W4" s="1">
+      <c r="R4" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>3</v>
       </c>
+      <c r="S4">
+        <v>5</v>
+      </c>
+      <c r="T4">
+        <v>100</v>
+      </c>
+      <c r="U4" s="2" cm="1">
+        <f t="array" ref="U4">SUMPRODUCT((Tabelle2[Seite]=Q4)*Tabelle2[Score_Gewichtet])</f>
+        <v>2.75</v>
+      </c>
+      <c r="V4" s="2"/>
+      <c r="W4">
+        <v>0</v>
+      </c>
       <c r="X4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>100</v>
-      </c>
-      <c r="Z4" s="2" cm="1">
-        <f t="array" ref="Z4">SUMPRODUCT((Tabelle2[Seite]=V4)*Tabelle2[Score_Gewichtet])</f>
-        <v>2.75</v>
-      </c>
-      <c r="AA4" s="2"/>
-      <c r="AD4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1797,40 +1859,46 @@
       <c r="K5">
         <v>0.75</v>
       </c>
-      <c r="R5">
+      <c r="M5">
         <v>5</v>
       </c>
-      <c r="S5">
-        <f t="shared" si="0"/>
+      <c r="N5">
+        <f>COUNTIF(B$2:B$1338, M5)</f>
         <v>26</v>
       </c>
-      <c r="T5">
-        <f t="shared" si="1"/>
+      <c r="O5">
+        <f>RANK(N5, $N$2:$N$116)</f>
         <v>5</v>
       </c>
-      <c r="V5">
+      <c r="Q5">
         <v>5</v>
       </c>
-      <c r="W5" s="1">
+      <c r="R5" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>4</v>
       </c>
+      <c r="S5">
+        <v>26</v>
+      </c>
+      <c r="T5">
+        <v>5</v>
+      </c>
+      <c r="U5" s="2" cm="1">
+        <f t="array" ref="U5">SUMPRODUCT((Tabelle2[Seite]=Q5)*Tabelle2[Score_Gewichtet])</f>
+        <v>32.000000000000007</v>
+      </c>
+      <c r="V5" s="2"/>
+      <c r="W5">
+        <v>0</v>
+      </c>
       <c r="X5">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>5</v>
-      </c>
-      <c r="Z5" s="2" cm="1">
-        <f t="array" ref="Z5">SUMPRODUCT((Tabelle2[Seite]=V5)*Tabelle2[Score_Gewichtet])</f>
-        <v>32.000000000000007</v>
-      </c>
-      <c r="AA5" s="2"/>
-      <c r="AD5" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -1864,40 +1932,46 @@
       <c r="K6">
         <v>0.6</v>
       </c>
-      <c r="R6">
+      <c r="M6">
         <v>6</v>
       </c>
-      <c r="S6">
-        <f t="shared" si="0"/>
+      <c r="N6">
+        <f>COUNTIF(B$2:B$1338, M6)</f>
         <v>9</v>
       </c>
-      <c r="T6">
-        <f t="shared" si="1"/>
+      <c r="O6">
+        <f>RANK(N6, $N$2:$N$116)</f>
         <v>61</v>
       </c>
-      <c r="V6">
+      <c r="Q6">
         <v>6</v>
       </c>
-      <c r="W6" s="1">
+      <c r="R6" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>5</v>
       </c>
+      <c r="S6">
+        <v>9</v>
+      </c>
+      <c r="T6">
+        <v>61</v>
+      </c>
+      <c r="U6" s="2" cm="1">
+        <f t="array" ref="U6">SUMPRODUCT((Tabelle2[Seite]=Q6)*Tabelle2[Score_Gewichtet])</f>
+        <v>10.6</v>
+      </c>
+      <c r="V6" s="2"/>
+      <c r="W6">
+        <v>0</v>
+      </c>
       <c r="X6">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>61</v>
-      </c>
-      <c r="Z6" s="2" cm="1">
-        <f t="array" ref="Z6">SUMPRODUCT((Tabelle2[Seite]=V6)*Tabelle2[Score_Gewichtet])</f>
-        <v>10.6</v>
-      </c>
-      <c r="AA6" s="2"/>
-      <c r="AD6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1931,40 +2005,46 @@
       <c r="K7">
         <v>0.5</v>
       </c>
-      <c r="R7">
+      <c r="M7">
         <v>7</v>
       </c>
-      <c r="S7">
-        <f t="shared" si="0"/>
+      <c r="N7">
+        <f>COUNTIF(B$2:B$1338, M7)</f>
         <v>10</v>
       </c>
-      <c r="T7">
-        <f t="shared" si="1"/>
+      <c r="O7">
+        <f>RANK(N7, $N$2:$N$116)</f>
         <v>55</v>
       </c>
-      <c r="V7">
+      <c r="Q7">
         <v>7</v>
       </c>
-      <c r="W7" s="1">
+      <c r="R7" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>6</v>
       </c>
+      <c r="S7">
+        <v>10</v>
+      </c>
+      <c r="T7">
+        <v>55</v>
+      </c>
+      <c r="U7" s="2" cm="1">
+        <f t="array" ref="U7">SUMPRODUCT((Tabelle2[Seite]=Q7)*Tabelle2[Score_Gewichtet])</f>
+        <v>34.299999999999997</v>
+      </c>
+      <c r="V7" s="2"/>
+      <c r="W7">
+        <v>0</v>
+      </c>
       <c r="X7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>55</v>
-      </c>
-      <c r="Z7" s="2" cm="1">
-        <f t="array" ref="Z7">SUMPRODUCT((Tabelle2[Seite]=V7)*Tabelle2[Score_Gewichtet])</f>
-        <v>34.299999999999997</v>
-      </c>
-      <c r="AA7" s="2"/>
-      <c r="AD7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1998,40 +2078,46 @@
       <c r="K8">
         <v>0.75</v>
       </c>
-      <c r="R8">
+      <c r="M8">
         <v>8</v>
       </c>
-      <c r="S8">
-        <f t="shared" si="0"/>
+      <c r="N8">
+        <f>COUNTIF(B$2:B$1338, M8)</f>
         <v>9</v>
       </c>
-      <c r="T8">
-        <f t="shared" si="1"/>
+      <c r="O8">
+        <f>RANK(N8, $N$2:$N$116)</f>
         <v>61</v>
       </c>
-      <c r="V8">
+      <c r="Q8">
         <v>8</v>
       </c>
-      <c r="W8" s="1">
+      <c r="R8" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>7</v>
       </c>
+      <c r="S8">
+        <v>9</v>
+      </c>
+      <c r="T8">
+        <v>61</v>
+      </c>
+      <c r="U8" s="2" cm="1">
+        <f t="array" ref="U8">SUMPRODUCT((Tabelle2[Seite]=Q8)*Tabelle2[Score_Gewichtet])</f>
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="V8" s="2"/>
+      <c r="W8">
+        <v>0</v>
+      </c>
       <c r="X8">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>61</v>
-      </c>
-      <c r="Z8" s="2" cm="1">
-        <f t="array" ref="Z8">SUMPRODUCT((Tabelle2[Seite]=V8)*Tabelle2[Score_Gewichtet])</f>
-        <v>8.5500000000000007</v>
-      </c>
-      <c r="AA8" s="2"/>
-      <c r="AD8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -2065,40 +2151,46 @@
       <c r="K9">
         <v>0.5</v>
       </c>
-      <c r="R9">
+      <c r="M9">
         <v>9</v>
       </c>
-      <c r="S9">
-        <f t="shared" si="0"/>
+      <c r="N9">
+        <f>COUNTIF(B$2:B$1338, M9)</f>
         <v>8</v>
       </c>
-      <c r="T9">
-        <f t="shared" si="1"/>
+      <c r="O9">
+        <f>RANK(N9, $N$2:$N$116)</f>
         <v>75</v>
       </c>
-      <c r="V9">
+      <c r="Q9">
         <v>9</v>
       </c>
-      <c r="W9" s="1">
+      <c r="R9" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>8</v>
       </c>
+      <c r="S9">
+        <v>8</v>
+      </c>
+      <c r="T9">
+        <v>75</v>
+      </c>
+      <c r="U9" s="2" cm="1">
+        <f t="array" ref="U9">SUMPRODUCT((Tabelle2[Seite]=Q9)*Tabelle2[Score_Gewichtet])</f>
+        <v>7.9</v>
+      </c>
+      <c r="V9" s="2"/>
+      <c r="W9">
+        <v>0</v>
+      </c>
       <c r="X9">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>75</v>
-      </c>
-      <c r="Z9" s="2" cm="1">
-        <f t="array" ref="Z9">SUMPRODUCT((Tabelle2[Seite]=V9)*Tabelle2[Score_Gewichtet])</f>
-        <v>7.9</v>
-      </c>
-      <c r="AA9" s="2"/>
-      <c r="AD9" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -2132,40 +2224,46 @@
       <c r="K10">
         <v>0.5</v>
       </c>
-      <c r="R10">
+      <c r="M10">
         <v>10</v>
       </c>
-      <c r="S10">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="T10">
-        <f t="shared" si="1"/>
+      <c r="N10">
+        <f>COUNTIF(B$2:B$1338, M10)</f>
+        <v>13</v>
+      </c>
+      <c r="O10">
+        <f>RANK(N10, $N$2:$N$116)</f>
         <v>34</v>
       </c>
-      <c r="V10">
+      <c r="Q10">
         <v>10</v>
       </c>
-      <c r="W10" s="1">
+      <c r="R10" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>9</v>
       </c>
+      <c r="S10">
+        <v>13</v>
+      </c>
+      <c r="T10">
+        <v>34</v>
+      </c>
+      <c r="U10" s="2" cm="1">
+        <f t="array" ref="U10">SUMPRODUCT((Tabelle2[Seite]=Q10)*Tabelle2[Score_Gewichtet])</f>
+        <v>10.5</v>
+      </c>
+      <c r="V10" s="2"/>
+      <c r="W10">
+        <v>0</v>
+      </c>
       <c r="X10">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y10">
-        <v>34</v>
-      </c>
-      <c r="Z10" s="2" cm="1">
-        <f t="array" ref="Z10">SUMPRODUCT((Tabelle2[Seite]=V10)*Tabelle2[Score_Gewichtet])</f>
-        <v>10.5</v>
-      </c>
-      <c r="AA10" s="2"/>
-      <c r="AD10" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -2199,45 +2297,48 @@
       <c r="K11">
         <v>0.5</v>
       </c>
-      <c r="R11">
-        <v>11</v>
-      </c>
-      <c r="S11">
-        <f t="shared" si="0"/>
+      <c r="M11">
+        <v>11</v>
+      </c>
+      <c r="N11">
+        <f>COUNTIF(B$2:B$1338, M11)</f>
         <v>15</v>
       </c>
-      <c r="T11">
-        <f t="shared" si="1"/>
+      <c r="O11">
+        <f>RANK(N11, $N$2:$N$116)</f>
         <v>26</v>
       </c>
-      <c r="V11">
-        <v>11</v>
-      </c>
-      <c r="W11" s="1">
+      <c r="Q11">
+        <v>11</v>
+      </c>
+      <c r="R11" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>10</v>
       </c>
+      <c r="S11">
+        <v>15</v>
+      </c>
+      <c r="T11">
+        <v>26</v>
+      </c>
+      <c r="U11" s="2" cm="1">
+        <f t="array" ref="U11">SUMPRODUCT((Tabelle2[Seite]=Q11)*Tabelle2[Score_Gewichtet])</f>
+        <v>11.1</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="W11">
+        <v>1</v>
+      </c>
       <c r="X11">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y11">
-        <v>26</v>
-      </c>
-      <c r="Z11" s="2" cm="1">
-        <f t="array" ref="Z11">SUMPRODUCT((Tabelle2[Seite]=V11)*Tabelle2[Score_Gewichtet])</f>
-        <v>11.1</v>
-      </c>
-      <c r="AA11" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -2271,45 +2372,48 @@
       <c r="K12">
         <v>3.5</v>
       </c>
-      <c r="R12">
+      <c r="M12">
         <v>12</v>
       </c>
+      <c r="N12">
+        <f>COUNTIF(B$2:B$1338, M12)</f>
+        <v>19</v>
+      </c>
+      <c r="O12">
+        <f>RANK(N12, $N$2:$N$116)</f>
+        <v>17</v>
+      </c>
+      <c r="Q12">
+        <v>12</v>
+      </c>
+      <c r="R12" s="1">
+        <f>Tabelle3[[#This Row],[Seite]]-1</f>
+        <v>11</v>
+      </c>
       <c r="S12">
-        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="T12">
-        <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="V12">
-        <v>12</v>
-      </c>
-      <c r="W12" s="1">
-        <f>Tabelle3[[#This Row],[Seite]]-1</f>
-        <v>11</v>
+      <c r="U12" s="2" cm="1">
+        <f t="array" ref="U12">SUMPRODUCT((Tabelle2[Seite]=Q12)*Tabelle2[Score_Gewichtet])</f>
+        <v>10.049999999999997</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="W12">
+        <v>1</v>
       </c>
       <c r="X12">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="Y12">
-        <v>17</v>
-      </c>
-      <c r="Z12" s="2" cm="1">
-        <f t="array" ref="Z12">SUMPRODUCT((Tabelle2[Seite]=V12)*Tabelle2[Score_Gewichtet])</f>
-        <v>10.049999999999997</v>
-      </c>
-      <c r="AA12" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -2343,40 +2447,46 @@
       <c r="K13">
         <v>3.5</v>
       </c>
-      <c r="R13">
-        <v>13</v>
-      </c>
-      <c r="S13">
-        <f t="shared" si="0"/>
+      <c r="M13">
+        <v>13</v>
+      </c>
+      <c r="N13">
+        <f>COUNTIF(B$2:B$1338, M13)</f>
         <v>12</v>
       </c>
-      <c r="T13">
-        <f t="shared" si="1"/>
+      <c r="O13">
+        <f>RANK(N13, $N$2:$N$116)</f>
         <v>39</v>
       </c>
-      <c r="V13">
-        <v>13</v>
-      </c>
-      <c r="W13" s="1">
+      <c r="Q13">
+        <v>13</v>
+      </c>
+      <c r="R13" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>12</v>
       </c>
+      <c r="S13">
+        <v>12</v>
+      </c>
+      <c r="T13">
+        <v>39</v>
+      </c>
+      <c r="U13" s="2" cm="1">
+        <f t="array" ref="U13">SUMPRODUCT((Tabelle2[Seite]=Q13)*Tabelle2[Score_Gewichtet])</f>
+        <v>13.799999999999999</v>
+      </c>
+      <c r="V13" s="2"/>
+      <c r="W13">
+        <v>0</v>
+      </c>
       <c r="X13">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>39</v>
-      </c>
-      <c r="Z13" s="2" cm="1">
-        <f t="array" ref="Z13">SUMPRODUCT((Tabelle2[Seite]=V13)*Tabelle2[Score_Gewichtet])</f>
-        <v>13.799999999999999</v>
-      </c>
-      <c r="AA13" s="2"/>
-      <c r="AD13" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -2410,40 +2520,46 @@
       <c r="K14">
         <v>5.5</v>
       </c>
-      <c r="R14">
+      <c r="M14">
         <v>14</v>
       </c>
+      <c r="N14">
+        <f>COUNTIF(B$2:B$1338, M14)</f>
+        <v>9</v>
+      </c>
+      <c r="O14">
+        <f>RANK(N14, $N$2:$N$116)</f>
+        <v>61</v>
+      </c>
+      <c r="Q14">
+        <v>14</v>
+      </c>
+      <c r="R14" s="1">
+        <f>Tabelle3[[#This Row],[Seite]]-1</f>
+        <v>13</v>
+      </c>
       <c r="S14">
-        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="T14">
-        <f t="shared" si="1"/>
         <v>61</v>
       </c>
-      <c r="V14">
-        <v>14</v>
-      </c>
-      <c r="W14" s="1">
-        <f>Tabelle3[[#This Row],[Seite]]-1</f>
-        <v>13</v>
+      <c r="U14" s="2" cm="1">
+        <f t="array" ref="U14">SUMPRODUCT((Tabelle2[Seite]=Q14)*Tabelle2[Score_Gewichtet])</f>
+        <v>7.7999999999999989</v>
+      </c>
+      <c r="V14" s="2"/>
+      <c r="W14">
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>61</v>
-      </c>
-      <c r="Z14" s="2" cm="1">
-        <f t="array" ref="Z14">SUMPRODUCT((Tabelle2[Seite]=V14)*Tabelle2[Score_Gewichtet])</f>
-        <v>7.7999999999999989</v>
-      </c>
-      <c r="AA14" s="2"/>
-      <c r="AD14" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -2477,40 +2593,46 @@
       <c r="K15">
         <v>0.5</v>
       </c>
-      <c r="R15">
+      <c r="M15">
         <v>15</v>
       </c>
-      <c r="S15">
-        <f t="shared" si="0"/>
+      <c r="N15">
+        <f>COUNTIF(B$2:B$1338, M15)</f>
         <v>8</v>
       </c>
-      <c r="T15">
-        <f t="shared" si="1"/>
+      <c r="O15">
+        <f>RANK(N15, $N$2:$N$116)</f>
         <v>75</v>
       </c>
-      <c r="V15">
+      <c r="Q15">
         <v>15</v>
       </c>
-      <c r="W15" s="1">
+      <c r="R15" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>14</v>
       </c>
+      <c r="S15">
+        <v>8</v>
+      </c>
+      <c r="T15">
+        <v>75</v>
+      </c>
+      <c r="U15" s="2" cm="1">
+        <f t="array" ref="U15">SUMPRODUCT((Tabelle2[Seite]=Q15)*Tabelle2[Score_Gewichtet])</f>
+        <v>3.6500000000000004</v>
+      </c>
+      <c r="V15" s="2"/>
+      <c r="W15">
+        <v>0</v>
+      </c>
       <c r="X15">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y15">
-        <v>75</v>
-      </c>
-      <c r="Z15" s="2" cm="1">
-        <f t="array" ref="Z15">SUMPRODUCT((Tabelle2[Seite]=V15)*Tabelle2[Score_Gewichtet])</f>
-        <v>3.6500000000000004</v>
-      </c>
-      <c r="AA15" s="2"/>
-      <c r="AD15" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -2544,40 +2666,46 @@
       <c r="K16">
         <v>1</v>
       </c>
-      <c r="R16">
+      <c r="M16">
         <v>16</v>
       </c>
-      <c r="S16">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="T16">
-        <f t="shared" si="1"/>
+      <c r="N16">
+        <f>COUNTIF(B$2:B$1338, M16)</f>
+        <v>11</v>
+      </c>
+      <c r="O16">
+        <f>RANK(N16, $N$2:$N$116)</f>
         <v>47</v>
       </c>
-      <c r="V16">
+      <c r="Q16">
         <v>16</v>
       </c>
-      <c r="W16" s="1">
+      <c r="R16" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>15</v>
       </c>
+      <c r="S16">
+        <v>11</v>
+      </c>
+      <c r="T16">
+        <v>47</v>
+      </c>
+      <c r="U16" s="2" cm="1">
+        <f t="array" ref="U16">SUMPRODUCT((Tabelle2[Seite]=Q16)*Tabelle2[Score_Gewichtet])</f>
+        <v>7.4999999999999991</v>
+      </c>
+      <c r="V16" s="2"/>
+      <c r="W16">
+        <v>0</v>
+      </c>
       <c r="X16">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>47</v>
-      </c>
-      <c r="Z16" s="2" cm="1">
-        <f t="array" ref="Z16">SUMPRODUCT((Tabelle2[Seite]=V16)*Tabelle2[Score_Gewichtet])</f>
-        <v>7.4999999999999991</v>
-      </c>
-      <c r="AA16" s="2"/>
-      <c r="AD16" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -2611,45 +2739,48 @@
       <c r="K17">
         <v>1</v>
       </c>
-      <c r="R17">
+      <c r="M17">
         <v>17</v>
       </c>
-      <c r="S17">
-        <f t="shared" si="0"/>
+      <c r="N17">
+        <f>COUNTIF(B$2:B$1338, M17)</f>
         <v>9</v>
       </c>
-      <c r="T17">
-        <f t="shared" si="1"/>
+      <c r="O17">
+        <f>RANK(N17, $N$2:$N$116)</f>
         <v>61</v>
       </c>
-      <c r="V17">
+      <c r="Q17">
         <v>17</v>
       </c>
-      <c r="W17" s="1">
+      <c r="R17" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>16</v>
       </c>
+      <c r="S17">
+        <v>9</v>
+      </c>
+      <c r="T17">
+        <v>61</v>
+      </c>
+      <c r="U17" s="2" cm="1">
+        <f t="array" ref="U17">SUMPRODUCT((Tabelle2[Seite]=Q17)*Tabelle2[Score_Gewichtet])</f>
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="W17">
+        <v>1</v>
+      </c>
       <c r="X17">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y17">
-        <v>61</v>
-      </c>
-      <c r="Z17" s="2" cm="1">
-        <f t="array" ref="Z17">SUMPRODUCT((Tabelle2[Seite]=V17)*Tabelle2[Score_Gewichtet])</f>
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="AA17" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="AB17" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -2683,45 +2814,48 @@
       <c r="K18">
         <v>0.75</v>
       </c>
-      <c r="R18">
+      <c r="M18">
         <v>18</v>
       </c>
-      <c r="S18">
-        <f t="shared" si="0"/>
+      <c r="N18">
+        <f>COUNTIF(B$2:B$1338, M18)</f>
         <v>3</v>
       </c>
-      <c r="T18">
-        <f t="shared" si="1"/>
+      <c r="O18">
+        <f>RANK(N18, $N$2:$N$116)</f>
         <v>108</v>
       </c>
-      <c r="V18">
+      <c r="Q18">
         <v>18</v>
       </c>
-      <c r="W18" s="1">
+      <c r="R18" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>17</v>
       </c>
+      <c r="S18">
+        <v>3</v>
+      </c>
+      <c r="T18">
+        <v>108</v>
+      </c>
+      <c r="U18" s="2" cm="1">
+        <f t="array" ref="U18">SUMPRODUCT((Tabelle2[Seite]=Q18)*Tabelle2[Score_Gewichtet])</f>
+        <v>1.45</v>
+      </c>
+      <c r="V18" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="W18">
+        <v>1</v>
+      </c>
       <c r="X18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y18">
-        <v>108</v>
-      </c>
-      <c r="Z18" s="2" cm="1">
-        <f t="array" ref="Z18">SUMPRODUCT((Tabelle2[Seite]=V18)*Tabelle2[Score_Gewichtet])</f>
-        <v>1.45</v>
-      </c>
-      <c r="AA18" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="AB18" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -2755,45 +2889,48 @@
       <c r="K19">
         <v>0.75</v>
       </c>
-      <c r="R19">
+      <c r="M19">
         <v>19</v>
       </c>
-      <c r="S19">
-        <f t="shared" si="0"/>
+      <c r="N19">
+        <f>COUNTIF(B$2:B$1338, M19)</f>
         <v>10</v>
       </c>
-      <c r="T19">
-        <f t="shared" si="1"/>
+      <c r="O19">
+        <f>RANK(N19, $N$2:$N$116)</f>
         <v>55</v>
       </c>
-      <c r="V19">
+      <c r="Q19">
         <v>19</v>
       </c>
-      <c r="W19" s="1">
+      <c r="R19" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>18</v>
       </c>
+      <c r="S19">
+        <v>10</v>
+      </c>
+      <c r="T19">
+        <v>55</v>
+      </c>
+      <c r="U19" s="2" cm="1">
+        <f t="array" ref="U19">SUMPRODUCT((Tabelle2[Seite]=Q19)*Tabelle2[Score_Gewichtet])</f>
+        <v>11.850000000000001</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="W19">
+        <v>1</v>
+      </c>
       <c r="X19">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>55</v>
-      </c>
-      <c r="Z19" s="2" cm="1">
-        <f t="array" ref="Z19">SUMPRODUCT((Tabelle2[Seite]=V19)*Tabelle2[Score_Gewichtet])</f>
-        <v>11.850000000000001</v>
-      </c>
-      <c r="AA19" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB19" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -2827,45 +2964,48 @@
       <c r="K20">
         <v>1</v>
       </c>
-      <c r="R20">
+      <c r="M20">
         <v>20</v>
       </c>
-      <c r="S20">
-        <f t="shared" si="0"/>
+      <c r="N20">
+        <f>COUNTIF(B$2:B$1338, M20)</f>
         <v>18</v>
       </c>
-      <c r="T20">
-        <f t="shared" si="1"/>
+      <c r="O20">
+        <f>RANK(N20, $N$2:$N$116)</f>
         <v>18</v>
       </c>
-      <c r="V20">
+      <c r="Q20">
         <v>20</v>
       </c>
-      <c r="W20" s="1">
+      <c r="R20" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>19</v>
       </c>
+      <c r="S20">
+        <v>18</v>
+      </c>
+      <c r="T20">
+        <v>18</v>
+      </c>
+      <c r="U20" s="2" cm="1">
+        <f t="array" ref="U20">SUMPRODUCT((Tabelle2[Seite]=Q20)*Tabelle2[Score_Gewichtet])</f>
+        <v>18.100000000000001</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="W20">
+        <v>1</v>
+      </c>
       <c r="X20">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>18</v>
-      </c>
-      <c r="Z20" s="2" cm="1">
-        <f t="array" ref="Z20">SUMPRODUCT((Tabelle2[Seite]=V20)*Tabelle2[Score_Gewichtet])</f>
-        <v>18.100000000000001</v>
-      </c>
-      <c r="AA20" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -2899,45 +3039,48 @@
       <c r="K21">
         <v>0.6</v>
       </c>
-      <c r="R21">
+      <c r="M21">
         <v>21</v>
       </c>
-      <c r="S21">
-        <f t="shared" si="0"/>
+      <c r="N21">
+        <f>COUNTIF(B$2:B$1338, M21)</f>
         <v>26</v>
       </c>
-      <c r="T21">
-        <f t="shared" si="1"/>
+      <c r="O21">
+        <f>RANK(N21, $N$2:$N$116)</f>
         <v>5</v>
       </c>
-      <c r="V21">
+      <c r="Q21">
         <v>21</v>
       </c>
-      <c r="W21" s="1">
+      <c r="R21" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>20</v>
       </c>
+      <c r="S21">
+        <v>26</v>
+      </c>
+      <c r="T21">
+        <v>5</v>
+      </c>
+      <c r="U21" s="2" cm="1">
+        <f t="array" ref="U21">SUMPRODUCT((Tabelle2[Seite]=Q21)*Tabelle2[Score_Gewichtet])</f>
+        <v>23.45</v>
+      </c>
+      <c r="V21" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W21">
+        <v>2</v>
+      </c>
       <c r="X21">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>5</v>
-      </c>
-      <c r="Z21" s="2" cm="1">
-        <f t="array" ref="Z21">SUMPRODUCT((Tabelle2[Seite]=V21)*Tabelle2[Score_Gewichtet])</f>
-        <v>23.45</v>
-      </c>
-      <c r="AA21" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="AB21" t="s">
-        <v>150</v>
-      </c>
-      <c r="AE21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -2971,45 +3114,48 @@
       <c r="K22">
         <v>0.75</v>
       </c>
-      <c r="R22">
+      <c r="M22">
         <v>22</v>
       </c>
-      <c r="S22">
-        <f t="shared" si="0"/>
+      <c r="N22">
+        <f>COUNTIF(B$2:B$1338, M22)</f>
         <v>10</v>
       </c>
-      <c r="T22">
-        <f t="shared" si="1"/>
+      <c r="O22">
+        <f>RANK(N22, $N$2:$N$116)</f>
         <v>55</v>
       </c>
-      <c r="V22">
+      <c r="Q22">
         <v>22</v>
       </c>
-      <c r="W22" s="1">
+      <c r="R22" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>21</v>
       </c>
+      <c r="S22">
+        <v>10</v>
+      </c>
+      <c r="T22">
+        <v>55</v>
+      </c>
+      <c r="U22" s="2" cm="1">
+        <f t="array" ref="U22">SUMPRODUCT((Tabelle2[Seite]=Q22)*Tabelle2[Score_Gewichtet])</f>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="V22" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="W22">
+        <v>2</v>
+      </c>
       <c r="X22">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y22">
-        <v>55</v>
-      </c>
-      <c r="Z22" s="2" cm="1">
-        <f t="array" ref="Z22">SUMPRODUCT((Tabelle2[Seite]=V22)*Tabelle2[Score_Gewichtet])</f>
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="AA22" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="AB22" t="s">
-        <v>150</v>
-      </c>
-      <c r="AE22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -3043,40 +3189,51 @@
       <c r="K23">
         <v>2</v>
       </c>
-      <c r="R23">
+      <c r="M23">
         <v>23</v>
       </c>
-      <c r="S23">
-        <f t="shared" si="0"/>
+      <c r="N23">
+        <f>COUNTIF(B$2:B$1338, M23)</f>
         <v>6</v>
       </c>
-      <c r="T23">
-        <f t="shared" si="1"/>
+      <c r="O23">
+        <f>RANK(N23, $N$2:$N$116)</f>
         <v>95</v>
       </c>
-      <c r="V23">
+      <c r="Q23">
         <v>23</v>
       </c>
-      <c r="W23" s="1">
+      <c r="R23" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>22</v>
       </c>
+      <c r="S23">
+        <v>6</v>
+      </c>
+      <c r="T23">
+        <v>95</v>
+      </c>
+      <c r="U23" s="2" cm="1">
+        <f t="array" ref="U23">SUMPRODUCT((Tabelle2[Seite]=Q23)*Tabelle2[Score_Gewichtet])</f>
+        <v>2.0500000000000003</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
       <c r="X23">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y23">
-        <v>95</v>
-      </c>
-      <c r="Z23" s="2" cm="1">
-        <f t="array" ref="Z23">SUMPRODUCT((Tabelle2[Seite]=V23)*Tabelle2[Score_Gewichtet])</f>
-        <v>2.0500000000000003</v>
-      </c>
-      <c r="AA23" s="2"/>
-      <c r="AD23" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -3110,40 +3267,46 @@
       <c r="K24">
         <v>0.5</v>
       </c>
-      <c r="R24">
+      <c r="M24">
         <v>24</v>
       </c>
-      <c r="S24">
-        <f t="shared" si="0"/>
+      <c r="N24">
+        <f>COUNTIF(B$2:B$1338, M24)</f>
         <v>16</v>
       </c>
-      <c r="T24">
-        <f t="shared" si="1"/>
+      <c r="O24">
+        <f>RANK(N24, $N$2:$N$116)</f>
         <v>21</v>
       </c>
-      <c r="V24">
+      <c r="Q24">
         <v>24</v>
       </c>
-      <c r="W24" s="1">
+      <c r="R24" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>23</v>
       </c>
+      <c r="S24">
+        <v>16</v>
+      </c>
+      <c r="T24">
+        <v>21</v>
+      </c>
+      <c r="U24" s="2" cm="1">
+        <f t="array" ref="U24">SUMPRODUCT((Tabelle2[Seite]=Q24)*Tabelle2[Score_Gewichtet])</f>
+        <v>14.75</v>
+      </c>
+      <c r="V24" s="2"/>
+      <c r="W24">
+        <v>0</v>
+      </c>
       <c r="X24">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>21</v>
-      </c>
-      <c r="Z24" s="2" cm="1">
-        <f t="array" ref="Z24">SUMPRODUCT((Tabelle2[Seite]=V24)*Tabelle2[Score_Gewichtet])</f>
-        <v>14.75</v>
-      </c>
-      <c r="AA24" s="2"/>
-      <c r="AD24" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -3177,40 +3340,46 @@
       <c r="K25">
         <v>0.1</v>
       </c>
-      <c r="R25">
+      <c r="M25">
         <v>25</v>
       </c>
-      <c r="S25">
-        <f t="shared" si="0"/>
+      <c r="N25">
+        <f>COUNTIF(B$2:B$1338, M25)</f>
         <v>12</v>
       </c>
-      <c r="T25">
-        <f t="shared" si="1"/>
+      <c r="O25">
+        <f>RANK(N25, $N$2:$N$116)</f>
         <v>39</v>
       </c>
-      <c r="V25">
+      <c r="Q25">
         <v>25</v>
       </c>
-      <c r="W25" s="1">
+      <c r="R25" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>24</v>
       </c>
+      <c r="S25">
+        <v>12</v>
+      </c>
+      <c r="T25">
+        <v>39</v>
+      </c>
+      <c r="U25" s="2" cm="1">
+        <f t="array" ref="U25">SUMPRODUCT((Tabelle2[Seite]=Q25)*Tabelle2[Score_Gewichtet])</f>
+        <v>16.95</v>
+      </c>
+      <c r="V25" s="2"/>
+      <c r="W25">
+        <v>0</v>
+      </c>
       <c r="X25">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>39</v>
-      </c>
-      <c r="Z25" s="2" cm="1">
-        <f t="array" ref="Z25">SUMPRODUCT((Tabelle2[Seite]=V25)*Tabelle2[Score_Gewichtet])</f>
-        <v>16.95</v>
-      </c>
-      <c r="AA25" s="2"/>
-      <c r="AD25" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -3244,40 +3413,46 @@
       <c r="K26">
         <v>0.5</v>
       </c>
-      <c r="R26">
+      <c r="M26">
         <v>26</v>
       </c>
-      <c r="S26">
-        <f t="shared" si="0"/>
+      <c r="N26">
+        <f>COUNTIF(B$2:B$1338, M26)</f>
         <v>9</v>
       </c>
-      <c r="T26">
-        <f t="shared" si="1"/>
+      <c r="O26">
+        <f>RANK(N26, $N$2:$N$116)</f>
         <v>61</v>
       </c>
-      <c r="V26">
+      <c r="Q26">
         <v>26</v>
       </c>
-      <c r="W26" s="1">
+      <c r="R26" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>25</v>
       </c>
+      <c r="S26">
+        <v>9</v>
+      </c>
+      <c r="T26">
+        <v>61</v>
+      </c>
+      <c r="U26" s="2" cm="1">
+        <f t="array" ref="U26">SUMPRODUCT((Tabelle2[Seite]=Q26)*Tabelle2[Score_Gewichtet])</f>
+        <v>10.399999999999999</v>
+      </c>
+      <c r="V26" s="2"/>
+      <c r="W26">
+        <v>0</v>
+      </c>
       <c r="X26">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>61</v>
-      </c>
-      <c r="Z26" s="2" cm="1">
-        <f t="array" ref="Z26">SUMPRODUCT((Tabelle2[Seite]=V26)*Tabelle2[Score_Gewichtet])</f>
-        <v>10.399999999999999</v>
-      </c>
-      <c r="AA26" s="2"/>
-      <c r="AD26" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -3311,40 +3486,46 @@
       <c r="K27">
         <v>0.1</v>
       </c>
-      <c r="R27">
+      <c r="M27">
         <v>27</v>
       </c>
-      <c r="S27">
-        <f t="shared" si="0"/>
+      <c r="N27">
+        <f>COUNTIF(B$2:B$1338, M27)</f>
         <v>9</v>
       </c>
-      <c r="T27">
-        <f t="shared" si="1"/>
+      <c r="O27">
+        <f>RANK(N27, $N$2:$N$116)</f>
         <v>61</v>
       </c>
-      <c r="V27">
+      <c r="Q27">
         <v>27</v>
       </c>
-      <c r="W27" s="1">
+      <c r="R27" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>26</v>
       </c>
+      <c r="S27">
+        <v>9</v>
+      </c>
+      <c r="T27">
+        <v>61</v>
+      </c>
+      <c r="U27" s="2" cm="1">
+        <f t="array" ref="U27">SUMPRODUCT((Tabelle2[Seite]=Q27)*Tabelle2[Score_Gewichtet])</f>
+        <v>5.0000000000000009</v>
+      </c>
+      <c r="V27" s="2"/>
+      <c r="W27">
+        <v>0</v>
+      </c>
       <c r="X27">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y27">
-        <v>61</v>
-      </c>
-      <c r="Z27" s="2" cm="1">
-        <f t="array" ref="Z27">SUMPRODUCT((Tabelle2[Seite]=V27)*Tabelle2[Score_Gewichtet])</f>
-        <v>5.0000000000000009</v>
-      </c>
-      <c r="AA27" s="2"/>
-      <c r="AD27" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -3378,40 +3559,46 @@
       <c r="K28">
         <v>2</v>
       </c>
-      <c r="R28">
+      <c r="M28">
         <v>28</v>
       </c>
-      <c r="S28">
-        <f t="shared" si="0"/>
+      <c r="N28">
+        <f>COUNTIF(B$2:B$1338, M28)</f>
         <v>7</v>
       </c>
-      <c r="T28">
-        <f t="shared" si="1"/>
+      <c r="O28">
+        <f>RANK(N28, $N$2:$N$116)</f>
         <v>87</v>
       </c>
-      <c r="V28">
+      <c r="Q28">
         <v>28</v>
       </c>
-      <c r="W28" s="1">
+      <c r="R28" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>27</v>
       </c>
+      <c r="S28">
+        <v>7</v>
+      </c>
+      <c r="T28">
+        <v>87</v>
+      </c>
+      <c r="U28" s="2" cm="1">
+        <f t="array" ref="U28">SUMPRODUCT((Tabelle2[Seite]=Q28)*Tabelle2[Score_Gewichtet])</f>
+        <v>6.55</v>
+      </c>
+      <c r="V28" s="2"/>
+      <c r="W28">
+        <v>0</v>
+      </c>
       <c r="X28">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y28">
-        <v>87</v>
-      </c>
-      <c r="Z28" s="2" cm="1">
-        <f t="array" ref="Z28">SUMPRODUCT((Tabelle2[Seite]=V28)*Tabelle2[Score_Gewichtet])</f>
-        <v>6.55</v>
-      </c>
-      <c r="AA28" s="2"/>
-      <c r="AD28" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>11</v>
       </c>
@@ -3445,40 +3632,46 @@
       <c r="K29">
         <v>0.1</v>
       </c>
-      <c r="R29">
+      <c r="M29">
         <v>29</v>
       </c>
-      <c r="S29">
-        <f t="shared" si="0"/>
+      <c r="N29">
+        <f>COUNTIF(B$2:B$1338, M29)</f>
         <v>12</v>
       </c>
-      <c r="T29">
-        <f t="shared" si="1"/>
+      <c r="O29">
+        <f>RANK(N29, $N$2:$N$116)</f>
         <v>39</v>
       </c>
-      <c r="V29">
+      <c r="Q29">
         <v>29</v>
       </c>
-      <c r="W29" s="1">
+      <c r="R29" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>28</v>
       </c>
+      <c r="S29">
+        <v>12</v>
+      </c>
+      <c r="T29">
+        <v>39</v>
+      </c>
+      <c r="U29" s="2" cm="1">
+        <f t="array" ref="U29">SUMPRODUCT((Tabelle2[Seite]=Q29)*Tabelle2[Score_Gewichtet])</f>
+        <v>19.399999999999999</v>
+      </c>
+      <c r="V29" s="2"/>
+      <c r="W29">
+        <v>0</v>
+      </c>
       <c r="X29">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Y29">
-        <v>39</v>
-      </c>
-      <c r="Z29" s="2" cm="1">
-        <f t="array" ref="Z29">SUMPRODUCT((Tabelle2[Seite]=V29)*Tabelle2[Score_Gewichtet])</f>
-        <v>19.399999999999999</v>
-      </c>
-      <c r="AA29" s="2"/>
-      <c r="AD29" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -3512,40 +3705,46 @@
       <c r="K30">
         <v>0.75</v>
       </c>
-      <c r="R30">
+      <c r="M30">
         <v>30</v>
       </c>
-      <c r="S30">
-        <f t="shared" si="0"/>
+      <c r="N30">
+        <f>COUNTIF(B$2:B$1338, M30)</f>
         <v>9</v>
       </c>
-      <c r="T30">
-        <f t="shared" si="1"/>
+      <c r="O30">
+        <f>RANK(N30, $N$2:$N$116)</f>
         <v>61</v>
       </c>
-      <c r="V30">
+      <c r="Q30">
         <v>30</v>
       </c>
-      <c r="W30" s="1">
+      <c r="R30" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>29</v>
       </c>
+      <c r="S30">
+        <v>9</v>
+      </c>
+      <c r="T30">
+        <v>61</v>
+      </c>
+      <c r="U30" s="2" cm="1">
+        <f t="array" ref="U30">SUMPRODUCT((Tabelle2[Seite]=Q30)*Tabelle2[Score_Gewichtet])</f>
+        <v>4.0500000000000007</v>
+      </c>
+      <c r="V30" s="2"/>
+      <c r="W30">
+        <v>0</v>
+      </c>
       <c r="X30">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y30">
-        <v>61</v>
-      </c>
-      <c r="Z30" s="2" cm="1">
-        <f t="array" ref="Z30">SUMPRODUCT((Tabelle2[Seite]=V30)*Tabelle2[Score_Gewichtet])</f>
-        <v>4.0500000000000007</v>
-      </c>
-      <c r="AA30" s="2"/>
-      <c r="AD30" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>11</v>
       </c>
@@ -3579,45 +3778,48 @@
       <c r="K31">
         <v>1</v>
       </c>
-      <c r="R31">
+      <c r="M31">
         <v>31</v>
       </c>
-      <c r="S31">
-        <f t="shared" si="0"/>
+      <c r="N31">
+        <f>COUNTIF(B$2:B$1338, M31)</f>
         <v>12</v>
       </c>
-      <c r="T31">
-        <f t="shared" si="1"/>
+      <c r="O31">
+        <f>RANK(N31, $N$2:$N$116)</f>
         <v>39</v>
       </c>
-      <c r="V31">
+      <c r="Q31">
         <v>31</v>
       </c>
-      <c r="W31" s="1">
+      <c r="R31" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>30</v>
       </c>
+      <c r="S31">
+        <v>12</v>
+      </c>
+      <c r="T31">
+        <v>39</v>
+      </c>
+      <c r="U31" s="2" cm="1">
+        <f t="array" ref="U31">SUMPRODUCT((Tabelle2[Seite]=Q31)*Tabelle2[Score_Gewichtet])</f>
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="V31" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="W31">
+        <v>1</v>
+      </c>
       <c r="X31">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>39</v>
-      </c>
-      <c r="Z31" s="2" cm="1">
-        <f t="array" ref="Z31">SUMPRODUCT((Tabelle2[Seite]=V31)*Tabelle2[Score_Gewichtet])</f>
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="AA31" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="AB31" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>11</v>
       </c>
@@ -3651,40 +3853,46 @@
       <c r="K32">
         <v>0.75</v>
       </c>
-      <c r="R32">
+      <c r="M32">
         <v>32</v>
       </c>
-      <c r="S32">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="T32">
-        <f t="shared" si="1"/>
+      <c r="N32">
+        <f>COUNTIF(B$2:B$1338, M32)</f>
+        <v>11</v>
+      </c>
+      <c r="O32">
+        <f>RANK(N32, $N$2:$N$116)</f>
         <v>47</v>
       </c>
-      <c r="V32">
+      <c r="Q32">
         <v>32</v>
       </c>
-      <c r="W32" s="1">
+      <c r="R32" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>31</v>
       </c>
+      <c r="S32">
+        <v>11</v>
+      </c>
+      <c r="T32">
+        <v>47</v>
+      </c>
+      <c r="U32" s="2" cm="1">
+        <f t="array" ref="U32">SUMPRODUCT((Tabelle2[Seite]=Q32)*Tabelle2[Score_Gewichtet])</f>
+        <v>7.5499999999999989</v>
+      </c>
+      <c r="V32" s="2"/>
+      <c r="W32">
+        <v>0</v>
+      </c>
       <c r="X32">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>47</v>
-      </c>
-      <c r="Z32" s="2" cm="1">
-        <f t="array" ref="Z32">SUMPRODUCT((Tabelle2[Seite]=V32)*Tabelle2[Score_Gewichtet])</f>
-        <v>7.5499999999999989</v>
-      </c>
-      <c r="AA32" s="2"/>
-      <c r="AD32" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -3718,40 +3926,46 @@
       <c r="K33">
         <v>3.5</v>
       </c>
-      <c r="R33">
+      <c r="M33">
         <v>33</v>
       </c>
-      <c r="S33">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="T33">
-        <f t="shared" si="1"/>
+      <c r="N33">
+        <f>COUNTIF(B$2:B$1338, M33)</f>
+        <v>1</v>
+      </c>
+      <c r="O33">
+        <f>RANK(N33, $N$2:$N$116)</f>
         <v>115</v>
       </c>
-      <c r="V33">
+      <c r="Q33">
         <v>33</v>
       </c>
-      <c r="W33" s="1">
+      <c r="R33" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>32</v>
       </c>
+      <c r="S33">
+        <v>1</v>
+      </c>
+      <c r="T33">
+        <v>115</v>
+      </c>
+      <c r="U33" s="2" cm="1">
+        <f t="array" ref="U33">SUMPRODUCT((Tabelle2[Seite]=Q33)*Tabelle2[Score_Gewichtet])</f>
+        <v>7.8</v>
+      </c>
+      <c r="V33" s="2"/>
+      <c r="W33">
+        <v>0</v>
+      </c>
       <c r="X33">
         <v>1</v>
       </c>
       <c r="Y33">
-        <v>115</v>
-      </c>
-      <c r="Z33" s="2" cm="1">
-        <f t="array" ref="Z33">SUMPRODUCT((Tabelle2[Seite]=V33)*Tabelle2[Score_Gewichtet])</f>
-        <v>7.8</v>
-      </c>
-      <c r="AA33" s="2"/>
-      <c r="AD33" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>11</v>
       </c>
@@ -3785,40 +3999,46 @@
       <c r="K34">
         <v>0.1</v>
       </c>
-      <c r="R34">
+      <c r="M34">
         <v>34</v>
       </c>
-      <c r="S34">
-        <f t="shared" si="0"/>
+      <c r="N34">
+        <f>COUNTIF(B$2:B$1338, M34)</f>
         <v>9</v>
       </c>
-      <c r="T34">
-        <f t="shared" si="1"/>
+      <c r="O34">
+        <f>RANK(N34, $N$2:$N$116)</f>
         <v>61</v>
       </c>
-      <c r="V34">
+      <c r="Q34">
         <v>34</v>
       </c>
-      <c r="W34" s="1">
+      <c r="R34" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>33</v>
       </c>
+      <c r="S34">
+        <v>9</v>
+      </c>
+      <c r="T34">
+        <v>61</v>
+      </c>
+      <c r="U34" s="2" cm="1">
+        <f t="array" ref="U34">SUMPRODUCT((Tabelle2[Seite]=Q34)*Tabelle2[Score_Gewichtet])</f>
+        <v>11.7</v>
+      </c>
+      <c r="V34" s="2"/>
+      <c r="W34">
+        <v>0</v>
+      </c>
       <c r="X34">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>61</v>
-      </c>
-      <c r="Z34" s="2" cm="1">
-        <f t="array" ref="Z34">SUMPRODUCT((Tabelle2[Seite]=V34)*Tabelle2[Score_Gewichtet])</f>
-        <v>11.7</v>
-      </c>
-      <c r="AA34" s="2"/>
-      <c r="AD34" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -3852,40 +4072,46 @@
       <c r="K35">
         <v>0.75</v>
       </c>
-      <c r="R35">
+      <c r="M35">
         <v>35</v>
       </c>
-      <c r="S35">
-        <f t="shared" si="0"/>
+      <c r="N35">
+        <f>COUNTIF(B$2:B$1338, M35)</f>
         <v>3</v>
       </c>
-      <c r="T35">
-        <f t="shared" si="1"/>
+      <c r="O35">
+        <f>RANK(N35, $N$2:$N$116)</f>
         <v>108</v>
       </c>
-      <c r="V35">
+      <c r="Q35">
         <v>35</v>
       </c>
-      <c r="W35" s="1">
+      <c r="R35" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>34</v>
       </c>
+      <c r="S35">
+        <v>3</v>
+      </c>
+      <c r="T35">
+        <v>108</v>
+      </c>
+      <c r="U35" s="2" cm="1">
+        <f t="array" ref="U35">SUMPRODUCT((Tabelle2[Seite]=Q35)*Tabelle2[Score_Gewichtet])</f>
+        <v>1.7000000000000002</v>
+      </c>
+      <c r="V35" s="2"/>
+      <c r="W35">
+        <v>0</v>
+      </c>
       <c r="X35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y35">
-        <v>108</v>
-      </c>
-      <c r="Z35" s="2" cm="1">
-        <f t="array" ref="Z35">SUMPRODUCT((Tabelle2[Seite]=V35)*Tabelle2[Score_Gewichtet])</f>
-        <v>1.7000000000000002</v>
-      </c>
-      <c r="AA35" s="2"/>
-      <c r="AD35" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -3919,40 +4145,46 @@
       <c r="K36">
         <v>0.5</v>
       </c>
-      <c r="R36">
+      <c r="M36">
         <v>36</v>
       </c>
-      <c r="S36">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="T36">
-        <f t="shared" si="1"/>
+      <c r="N36">
+        <f>COUNTIF(B$2:B$1338, M36)</f>
+        <v>2</v>
+      </c>
+      <c r="O36">
+        <f>RANK(N36, $N$2:$N$116)</f>
         <v>112</v>
       </c>
-      <c r="V36">
+      <c r="Q36">
         <v>36</v>
       </c>
-      <c r="W36" s="1">
+      <c r="R36" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>35</v>
       </c>
+      <c r="S36">
+        <v>2</v>
+      </c>
+      <c r="T36">
+        <v>112</v>
+      </c>
+      <c r="U36" s="2" cm="1">
+        <f t="array" ref="U36">SUMPRODUCT((Tabelle2[Seite]=Q36)*Tabelle2[Score_Gewichtet])</f>
+        <v>4.75</v>
+      </c>
+      <c r="V36" s="2"/>
+      <c r="W36">
+        <v>0</v>
+      </c>
       <c r="X36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y36">
-        <v>112</v>
-      </c>
-      <c r="Z36" s="2" cm="1">
-        <f t="array" ref="Z36">SUMPRODUCT((Tabelle2[Seite]=V36)*Tabelle2[Score_Gewichtet])</f>
-        <v>4.75</v>
-      </c>
-      <c r="AA36" s="2"/>
-      <c r="AD36" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>11</v>
       </c>
@@ -3986,40 +4218,46 @@
       <c r="K37">
         <v>0.5</v>
       </c>
-      <c r="R37">
+      <c r="M37">
         <v>37</v>
       </c>
-      <c r="S37">
-        <f t="shared" si="0"/>
+      <c r="N37">
+        <f>COUNTIF(B$2:B$1338, M37)</f>
         <v>12</v>
       </c>
-      <c r="T37">
-        <f t="shared" si="1"/>
+      <c r="O37">
+        <f>RANK(N37, $N$2:$N$116)</f>
         <v>39</v>
       </c>
-      <c r="V37">
+      <c r="Q37">
         <v>37</v>
       </c>
-      <c r="W37" s="1">
+      <c r="R37" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>36</v>
       </c>
+      <c r="S37">
+        <v>12</v>
+      </c>
+      <c r="T37">
+        <v>39</v>
+      </c>
+      <c r="U37" s="2" cm="1">
+        <f t="array" ref="U37">SUMPRODUCT((Tabelle2[Seite]=Q37)*Tabelle2[Score_Gewichtet])</f>
+        <v>9.1999999999999975</v>
+      </c>
+      <c r="V37" s="2"/>
+      <c r="W37">
+        <v>0</v>
+      </c>
       <c r="X37">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Y37">
-        <v>39</v>
-      </c>
-      <c r="Z37" s="2" cm="1">
-        <f t="array" ref="Z37">SUMPRODUCT((Tabelle2[Seite]=V37)*Tabelle2[Score_Gewichtet])</f>
-        <v>9.1999999999999975</v>
-      </c>
-      <c r="AA37" s="2"/>
-      <c r="AD37" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>11</v>
       </c>
@@ -4053,40 +4291,46 @@
       <c r="K38">
         <v>1</v>
       </c>
-      <c r="R38">
+      <c r="M38">
         <v>38</v>
       </c>
-      <c r="S38">
-        <f t="shared" si="0"/>
+      <c r="N38">
+        <f>COUNTIF(B$2:B$1338, M38)</f>
         <v>6</v>
       </c>
-      <c r="T38">
-        <f t="shared" si="1"/>
+      <c r="O38">
+        <f>RANK(N38, $N$2:$N$116)</f>
         <v>95</v>
       </c>
-      <c r="V38">
+      <c r="Q38">
         <v>38</v>
       </c>
-      <c r="W38" s="1">
+      <c r="R38" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>37</v>
       </c>
+      <c r="S38">
+        <v>6</v>
+      </c>
+      <c r="T38">
+        <v>95</v>
+      </c>
+      <c r="U38" s="2" cm="1">
+        <f t="array" ref="U38">SUMPRODUCT((Tabelle2[Seite]=Q38)*Tabelle2[Score_Gewichtet])</f>
+        <v>13.7</v>
+      </c>
+      <c r="V38" s="2"/>
+      <c r="W38">
+        <v>0</v>
+      </c>
       <c r="X38">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y38">
-        <v>95</v>
-      </c>
-      <c r="Z38" s="2" cm="1">
-        <f t="array" ref="Z38">SUMPRODUCT((Tabelle2[Seite]=V38)*Tabelle2[Score_Gewichtet])</f>
-        <v>13.7</v>
-      </c>
-      <c r="AA38" s="2"/>
-      <c r="AD38" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>11</v>
       </c>
@@ -4120,40 +4364,46 @@
       <c r="K39">
         <v>1</v>
       </c>
-      <c r="R39">
+      <c r="M39">
         <v>39</v>
       </c>
-      <c r="S39">
-        <f t="shared" si="0"/>
+      <c r="N39">
+        <f>COUNTIF(B$2:B$1338, M39)</f>
         <v>8</v>
       </c>
-      <c r="T39">
-        <f t="shared" si="1"/>
+      <c r="O39">
+        <f>RANK(N39, $N$2:$N$116)</f>
         <v>75</v>
       </c>
-      <c r="V39">
+      <c r="Q39">
         <v>39</v>
       </c>
-      <c r="W39" s="1">
+      <c r="R39" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>38</v>
       </c>
+      <c r="S39">
+        <v>8</v>
+      </c>
+      <c r="T39">
+        <v>75</v>
+      </c>
+      <c r="U39" s="2" cm="1">
+        <f t="array" ref="U39">SUMPRODUCT((Tabelle2[Seite]=Q39)*Tabelle2[Score_Gewichtet])</f>
+        <v>6.3</v>
+      </c>
+      <c r="V39" s="2"/>
+      <c r="W39">
+        <v>0</v>
+      </c>
       <c r="X39">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y39">
-        <v>75</v>
-      </c>
-      <c r="Z39" s="2" cm="1">
-        <f t="array" ref="Z39">SUMPRODUCT((Tabelle2[Seite]=V39)*Tabelle2[Score_Gewichtet])</f>
-        <v>6.3</v>
-      </c>
-      <c r="AA39" s="2"/>
-      <c r="AD39" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>11</v>
       </c>
@@ -4187,45 +4437,46 @@
       <c r="K40">
         <v>3</v>
       </c>
-      <c r="R40">
+      <c r="M40">
         <v>40</v>
       </c>
-      <c r="S40">
-        <f t="shared" si="0"/>
+      <c r="N40">
+        <f>COUNTIF(B$2:B$1338, M40)</f>
         <v>6</v>
       </c>
-      <c r="T40">
-        <f t="shared" si="1"/>
+      <c r="O40">
+        <f>RANK(N40, $N$2:$N$116)</f>
         <v>95</v>
       </c>
-      <c r="V40">
+      <c r="Q40">
         <v>40</v>
       </c>
-      <c r="W40" s="1">
+      <c r="R40" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>39</v>
       </c>
+      <c r="S40">
+        <v>6</v>
+      </c>
+      <c r="T40">
+        <v>95</v>
+      </c>
+      <c r="U40" s="2" cm="1">
+        <f t="array" ref="U40">SUMPRODUCT((Tabelle2[Seite]=Q40)*Tabelle2[Score_Gewichtet])</f>
+        <v>6.3</v>
+      </c>
+      <c r="V40" s="2"/>
+      <c r="W40">
+        <v>1</v>
+      </c>
       <c r="X40">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y40">
-        <v>95</v>
-      </c>
-      <c r="Z40" s="2" cm="1">
-        <f t="array" ref="Z40">SUMPRODUCT((Tabelle2[Seite]=V40)*Tabelle2[Score_Gewichtet])</f>
-        <v>6.3</v>
-      </c>
-      <c r="AA40" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB40" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>11</v>
       </c>
@@ -4259,45 +4510,51 @@
       <c r="K41">
         <v>0.75</v>
       </c>
-      <c r="R41">
+      <c r="M41">
         <v>41</v>
       </c>
-      <c r="S41">
-        <f t="shared" si="0"/>
+      <c r="N41">
+        <f>COUNTIF(B$2:B$1338, M41)</f>
         <v>18</v>
       </c>
-      <c r="T41">
-        <f t="shared" si="1"/>
+      <c r="O41">
+        <f>RANK(N41, $N$2:$N$116)</f>
         <v>18</v>
       </c>
-      <c r="V41">
+      <c r="Q41">
         <v>41</v>
       </c>
-      <c r="W41" s="1">
+      <c r="R41" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>40</v>
       </c>
+      <c r="S41">
+        <v>18</v>
+      </c>
+      <c r="T41">
+        <v>18</v>
+      </c>
+      <c r="U41" s="2" cm="1">
+        <f t="array" ref="U41">SUMPRODUCT((Tabelle2[Seite]=Q41)*Tabelle2[Score_Gewichtet])</f>
+        <v>25.500000000000004</v>
+      </c>
+      <c r="V41" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="W41">
+        <v>1</v>
+      </c>
       <c r="X41">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y41">
-        <v>18</v>
-      </c>
-      <c r="Z41" s="2" cm="1">
-        <f t="array" ref="Z41">SUMPRODUCT((Tabelle2[Seite]=V41)*Tabelle2[Score_Gewichtet])</f>
-        <v>25.500000000000004</v>
-      </c>
-      <c r="AA41" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB41" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>11</v>
       </c>
@@ -4331,40 +4588,48 @@
       <c r="K42">
         <v>0.1</v>
       </c>
-      <c r="R42">
+      <c r="M42">
         <v>42</v>
       </c>
-      <c r="S42">
-        <f t="shared" si="0"/>
+      <c r="N42">
+        <f>COUNTIF(B$2:B$1338, M42)</f>
         <v>35</v>
       </c>
-      <c r="T42">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="V42">
+      <c r="O42">
+        <f>RANK(N42, $N$2:$N$116)</f>
+        <v>2</v>
+      </c>
+      <c r="Q42">
         <v>42</v>
       </c>
-      <c r="W42" s="1">
+      <c r="R42" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>41</v>
       </c>
+      <c r="S42">
+        <v>35</v>
+      </c>
+      <c r="T42">
+        <v>2</v>
+      </c>
+      <c r="U42" s="2" cm="1">
+        <f t="array" ref="U42">SUMPRODUCT((Tabelle2[Seite]=Q42)*Tabelle2[Score_Gewichtet])</f>
+        <v>40.70000000000001</v>
+      </c>
+      <c r="V42" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="W42">
+        <v>1</v>
+      </c>
       <c r="X42">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="Y42">
-        <v>2</v>
-      </c>
-      <c r="Z42" s="2" cm="1">
-        <f t="array" ref="Z42">SUMPRODUCT((Tabelle2[Seite]=V42)*Tabelle2[Score_Gewichtet])</f>
-        <v>40.70000000000001</v>
-      </c>
-      <c r="AA42" s="2"/>
-      <c r="AD42" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>11</v>
       </c>
@@ -4398,40 +4663,46 @@
       <c r="K43">
         <v>1.5</v>
       </c>
-      <c r="R43">
+      <c r="M43">
         <v>43</v>
       </c>
-      <c r="S43">
-        <f t="shared" si="0"/>
+      <c r="N43">
+        <f>COUNTIF(B$2:B$1338, M43)</f>
         <v>7</v>
       </c>
-      <c r="T43">
-        <f t="shared" si="1"/>
+      <c r="O43">
+        <f>RANK(N43, $N$2:$N$116)</f>
         <v>87</v>
       </c>
-      <c r="V43">
+      <c r="Q43">
         <v>43</v>
       </c>
-      <c r="W43" s="1">
+      <c r="R43" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>42</v>
       </c>
+      <c r="S43">
+        <v>7</v>
+      </c>
+      <c r="T43">
+        <v>87</v>
+      </c>
+      <c r="U43" s="2" cm="1">
+        <f t="array" ref="U43">SUMPRODUCT((Tabelle2[Seite]=Q43)*Tabelle2[Score_Gewichtet])</f>
+        <v>6.7</v>
+      </c>
+      <c r="V43" s="2"/>
+      <c r="W43">
+        <v>0</v>
+      </c>
       <c r="X43">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y43">
-        <v>87</v>
-      </c>
-      <c r="Z43" s="2" cm="1">
-        <f t="array" ref="Z43">SUMPRODUCT((Tabelle2[Seite]=V43)*Tabelle2[Score_Gewichtet])</f>
-        <v>6.7</v>
-      </c>
-      <c r="AA43" s="2"/>
-      <c r="AD43" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>11</v>
       </c>
@@ -4465,40 +4736,46 @@
       <c r="K44">
         <v>0.75</v>
       </c>
-      <c r="R44">
+      <c r="M44">
         <v>44</v>
       </c>
-      <c r="S44">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="T44">
-        <f t="shared" si="1"/>
+      <c r="N44">
+        <f>COUNTIF(B$2:B$1338, M44)</f>
+        <v>2</v>
+      </c>
+      <c r="O44">
+        <f>RANK(N44, $N$2:$N$116)</f>
         <v>112</v>
       </c>
-      <c r="V44">
+      <c r="Q44">
         <v>44</v>
       </c>
-      <c r="W44" s="1">
+      <c r="R44" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>43</v>
       </c>
+      <c r="S44">
+        <v>2</v>
+      </c>
+      <c r="T44">
+        <v>112</v>
+      </c>
+      <c r="U44" s="2" cm="1">
+        <f t="array" ref="U44">SUMPRODUCT((Tabelle2[Seite]=Q44)*Tabelle2[Score_Gewichtet])</f>
+        <v>1.25</v>
+      </c>
+      <c r="V44" s="2"/>
+      <c r="W44">
+        <v>0</v>
+      </c>
       <c r="X44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y44">
-        <v>112</v>
-      </c>
-      <c r="Z44" s="2" cm="1">
-        <f t="array" ref="Z44">SUMPRODUCT((Tabelle2[Seite]=V44)*Tabelle2[Score_Gewichtet])</f>
-        <v>1.25</v>
-      </c>
-      <c r="AA44" s="2"/>
-      <c r="AD44" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>11</v>
       </c>
@@ -4532,40 +4809,46 @@
       <c r="K45">
         <v>1.5</v>
       </c>
-      <c r="R45">
+      <c r="M45">
         <v>45</v>
       </c>
-      <c r="S45">
-        <f t="shared" si="0"/>
+      <c r="N45">
+        <f>COUNTIF(B$2:B$1338, M45)</f>
         <v>15</v>
       </c>
-      <c r="T45">
-        <f t="shared" si="1"/>
+      <c r="O45">
+        <f>RANK(N45, $N$2:$N$116)</f>
         <v>26</v>
       </c>
-      <c r="V45">
+      <c r="Q45">
         <v>45</v>
       </c>
-      <c r="W45" s="1">
+      <c r="R45" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>44</v>
       </c>
+      <c r="S45">
+        <v>15</v>
+      </c>
+      <c r="T45">
+        <v>26</v>
+      </c>
+      <c r="U45" s="2" cm="1">
+        <f t="array" ref="U45">SUMPRODUCT((Tabelle2[Seite]=Q45)*Tabelle2[Score_Gewichtet])</f>
+        <v>19.049999999999997</v>
+      </c>
+      <c r="V45" s="2"/>
+      <c r="W45">
+        <v>0</v>
+      </c>
       <c r="X45">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Y45">
-        <v>26</v>
-      </c>
-      <c r="Z45" s="2" cm="1">
-        <f t="array" ref="Z45">SUMPRODUCT((Tabelle2[Seite]=V45)*Tabelle2[Score_Gewichtet])</f>
-        <v>19.049999999999997</v>
-      </c>
-      <c r="AA45" s="2"/>
-      <c r="AD45" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>11</v>
       </c>
@@ -4599,40 +4882,46 @@
       <c r="K46">
         <v>1</v>
       </c>
-      <c r="R46">
+      <c r="M46">
         <v>46</v>
       </c>
-      <c r="S46">
-        <f t="shared" si="0"/>
+      <c r="N46">
+        <f>COUNTIF(B$2:B$1338, M46)</f>
         <v>5</v>
       </c>
-      <c r="T46">
-        <f t="shared" si="1"/>
+      <c r="O46">
+        <f>RANK(N46, $N$2:$N$116)</f>
         <v>100</v>
       </c>
-      <c r="V46">
+      <c r="Q46">
         <v>46</v>
       </c>
-      <c r="W46" s="1">
+      <c r="R46" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>45</v>
       </c>
+      <c r="S46">
+        <v>5</v>
+      </c>
+      <c r="T46">
+        <v>100</v>
+      </c>
+      <c r="U46" s="2" cm="1">
+        <f t="array" ref="U46">SUMPRODUCT((Tabelle2[Seite]=Q46)*Tabelle2[Score_Gewichtet])</f>
+        <v>8.25</v>
+      </c>
+      <c r="V46" s="2"/>
+      <c r="W46">
+        <v>0</v>
+      </c>
       <c r="X46">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y46">
-        <v>100</v>
-      </c>
-      <c r="Z46" s="2" cm="1">
-        <f t="array" ref="Z46">SUMPRODUCT((Tabelle2[Seite]=V46)*Tabelle2[Score_Gewichtet])</f>
-        <v>8.25</v>
-      </c>
-      <c r="AA46" s="2"/>
-      <c r="AD46" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -4666,40 +4955,46 @@
       <c r="K47">
         <v>4</v>
       </c>
-      <c r="R47">
+      <c r="M47">
         <v>47</v>
       </c>
-      <c r="S47">
-        <f t="shared" si="0"/>
+      <c r="N47">
+        <f>COUNTIF(B$2:B$1338, M47)</f>
         <v>9</v>
       </c>
-      <c r="T47">
-        <f t="shared" si="1"/>
+      <c r="O47">
+        <f>RANK(N47, $N$2:$N$116)</f>
         <v>61</v>
       </c>
-      <c r="V47">
+      <c r="Q47">
         <v>47</v>
       </c>
-      <c r="W47" s="1">
+      <c r="R47" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>46</v>
       </c>
+      <c r="S47">
+        <v>9</v>
+      </c>
+      <c r="T47">
+        <v>61</v>
+      </c>
+      <c r="U47" s="2" cm="1">
+        <f t="array" ref="U47">SUMPRODUCT((Tabelle2[Seite]=Q47)*Tabelle2[Score_Gewichtet])</f>
+        <v>13.4</v>
+      </c>
+      <c r="V47" s="2"/>
+      <c r="W47">
+        <v>0</v>
+      </c>
       <c r="X47">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y47">
-        <v>61</v>
-      </c>
-      <c r="Z47" s="2" cm="1">
-        <f t="array" ref="Z47">SUMPRODUCT((Tabelle2[Seite]=V47)*Tabelle2[Score_Gewichtet])</f>
-        <v>13.4</v>
-      </c>
-      <c r="AA47" s="2"/>
-      <c r="AD47" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>11</v>
       </c>
@@ -4733,40 +5028,46 @@
       <c r="K48">
         <v>0.5</v>
       </c>
-      <c r="R48">
+      <c r="M48">
         <v>48</v>
       </c>
-      <c r="S48">
-        <f t="shared" si="0"/>
+      <c r="N48">
+        <f>COUNTIF(B$2:B$1338, M48)</f>
         <v>10</v>
       </c>
-      <c r="T48">
-        <f t="shared" si="1"/>
+      <c r="O48">
+        <f>RANK(N48, $N$2:$N$116)</f>
         <v>55</v>
       </c>
-      <c r="V48">
+      <c r="Q48">
         <v>48</v>
       </c>
-      <c r="W48" s="1">
+      <c r="R48" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>47</v>
       </c>
+      <c r="S48">
+        <v>10</v>
+      </c>
+      <c r="T48">
+        <v>55</v>
+      </c>
+      <c r="U48" s="2" cm="1">
+        <f t="array" ref="U48">SUMPRODUCT((Tabelle2[Seite]=Q48)*Tabelle2[Score_Gewichtet])</f>
+        <v>24.400000000000002</v>
+      </c>
+      <c r="V48" s="2"/>
+      <c r="W48">
+        <v>0</v>
+      </c>
       <c r="X48">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y48">
-        <v>55</v>
-      </c>
-      <c r="Z48" s="2" cm="1">
-        <f t="array" ref="Z48">SUMPRODUCT((Tabelle2[Seite]=V48)*Tabelle2[Score_Gewichtet])</f>
-        <v>24.400000000000002</v>
-      </c>
-      <c r="AA48" s="2"/>
-      <c r="AD48" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>11</v>
       </c>
@@ -4800,40 +5101,46 @@
       <c r="K49">
         <v>0.1</v>
       </c>
-      <c r="R49">
+      <c r="M49">
         <v>49</v>
       </c>
-      <c r="S49">
-        <f t="shared" si="0"/>
+      <c r="N49">
+        <f>COUNTIF(B$2:B$1338, M49)</f>
         <v>8</v>
       </c>
-      <c r="T49">
-        <f t="shared" si="1"/>
+      <c r="O49">
+        <f>RANK(N49, $N$2:$N$116)</f>
         <v>75</v>
       </c>
-      <c r="V49">
+      <c r="Q49">
         <v>49</v>
       </c>
-      <c r="W49" s="1">
+      <c r="R49" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>48</v>
       </c>
+      <c r="S49">
+        <v>8</v>
+      </c>
+      <c r="T49">
+        <v>75</v>
+      </c>
+      <c r="U49" s="2" cm="1">
+        <f t="array" ref="U49">SUMPRODUCT((Tabelle2[Seite]=Q49)*Tabelle2[Score_Gewichtet])</f>
+        <v>14.149999999999999</v>
+      </c>
+      <c r="V49" s="2"/>
+      <c r="W49">
+        <v>0</v>
+      </c>
       <c r="X49">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y49">
-        <v>75</v>
-      </c>
-      <c r="Z49" s="2" cm="1">
-        <f t="array" ref="Z49">SUMPRODUCT((Tabelle2[Seite]=V49)*Tabelle2[Score_Gewichtet])</f>
-        <v>14.149999999999999</v>
-      </c>
-      <c r="AA49" s="2"/>
-      <c r="AD49" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>11</v>
       </c>
@@ -4867,40 +5174,46 @@
       <c r="K50">
         <v>0.1</v>
       </c>
-      <c r="R50">
+      <c r="M50">
         <v>50</v>
       </c>
-      <c r="S50">
-        <f t="shared" si="0"/>
+      <c r="N50">
+        <f>COUNTIF(B$2:B$1338, M50)</f>
         <v>9</v>
       </c>
-      <c r="T50">
-        <f t="shared" si="1"/>
+      <c r="O50">
+        <f>RANK(N50, $N$2:$N$116)</f>
         <v>61</v>
       </c>
-      <c r="V50">
+      <c r="Q50">
         <v>50</v>
       </c>
-      <c r="W50" s="1">
+      <c r="R50" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>49</v>
       </c>
+      <c r="S50">
+        <v>9</v>
+      </c>
+      <c r="T50">
+        <v>61</v>
+      </c>
+      <c r="U50" s="2" cm="1">
+        <f t="array" ref="U50">SUMPRODUCT((Tabelle2[Seite]=Q50)*Tabelle2[Score_Gewichtet])</f>
+        <v>15.6</v>
+      </c>
+      <c r="V50" s="2"/>
+      <c r="W50">
+        <v>0</v>
+      </c>
       <c r="X50">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y50">
-        <v>61</v>
-      </c>
-      <c r="Z50" s="2" cm="1">
-        <f t="array" ref="Z50">SUMPRODUCT((Tabelle2[Seite]=V50)*Tabelle2[Score_Gewichtet])</f>
-        <v>15.6</v>
-      </c>
-      <c r="AA50" s="2"/>
-      <c r="AD50" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>11</v>
       </c>
@@ -4934,40 +5247,46 @@
       <c r="K51">
         <v>0.5</v>
       </c>
-      <c r="R51">
+      <c r="M51">
         <v>51</v>
       </c>
-      <c r="S51">
-        <f t="shared" si="0"/>
+      <c r="N51">
+        <f>COUNTIF(B$2:B$1338, M51)</f>
         <v>16</v>
       </c>
-      <c r="T51">
-        <f t="shared" si="1"/>
+      <c r="O51">
+        <f>RANK(N51, $N$2:$N$116)</f>
         <v>21</v>
       </c>
-      <c r="V51">
+      <c r="Q51">
         <v>51</v>
       </c>
-      <c r="W51" s="1">
+      <c r="R51" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>50</v>
       </c>
+      <c r="S51">
+        <v>16</v>
+      </c>
+      <c r="T51">
+        <v>21</v>
+      </c>
+      <c r="U51" s="2" cm="1">
+        <f t="array" ref="U51">SUMPRODUCT((Tabelle2[Seite]=Q51)*Tabelle2[Score_Gewichtet])</f>
+        <v>15.7</v>
+      </c>
+      <c r="V51" s="2"/>
+      <c r="W51">
+        <v>0</v>
+      </c>
       <c r="X51">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>21</v>
-      </c>
-      <c r="Z51" s="2" cm="1">
-        <f t="array" ref="Z51">SUMPRODUCT((Tabelle2[Seite]=V51)*Tabelle2[Score_Gewichtet])</f>
-        <v>15.7</v>
-      </c>
-      <c r="AA51" s="2"/>
-      <c r="AD51" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="52" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>11</v>
       </c>
@@ -5001,40 +5320,46 @@
       <c r="K52">
         <v>0.1</v>
       </c>
-      <c r="R52">
+      <c r="M52">
         <v>52</v>
       </c>
-      <c r="S52">
-        <f t="shared" si="0"/>
+      <c r="N52">
+        <f>COUNTIF(B$2:B$1338, M52)</f>
         <v>20</v>
       </c>
-      <c r="T52">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="V52">
+      <c r="O52">
+        <f>RANK(N52, $N$2:$N$116)</f>
+        <v>13</v>
+      </c>
+      <c r="Q52">
         <v>52</v>
       </c>
-      <c r="W52" s="1">
+      <c r="R52" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>51</v>
       </c>
+      <c r="S52">
+        <v>20</v>
+      </c>
+      <c r="T52">
+        <v>13</v>
+      </c>
+      <c r="U52" s="2" cm="1">
+        <f t="array" ref="U52">SUMPRODUCT((Tabelle2[Seite]=Q52)*Tabelle2[Score_Gewichtet])</f>
+        <v>44.75</v>
+      </c>
+      <c r="V52" s="2"/>
+      <c r="W52">
+        <v>0</v>
+      </c>
       <c r="X52">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Y52">
-        <v>13</v>
-      </c>
-      <c r="Z52" s="2" cm="1">
-        <f t="array" ref="Z52">SUMPRODUCT((Tabelle2[Seite]=V52)*Tabelle2[Score_Gewichtet])</f>
-        <v>44.75</v>
-      </c>
-      <c r="AA52" s="2"/>
-      <c r="AD52" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>11</v>
       </c>
@@ -5068,45 +5393,48 @@
       <c r="K53">
         <v>1</v>
       </c>
-      <c r="R53">
+      <c r="M53">
         <v>53</v>
       </c>
-      <c r="S53">
-        <f t="shared" si="0"/>
+      <c r="N53">
+        <f>COUNTIF(B$2:B$1338, M53)</f>
         <v>8</v>
       </c>
-      <c r="T53">
-        <f t="shared" si="1"/>
+      <c r="O53">
+        <f>RANK(N53, $N$2:$N$116)</f>
         <v>75</v>
       </c>
-      <c r="V53">
+      <c r="Q53">
         <v>53</v>
       </c>
-      <c r="W53" s="1">
+      <c r="R53" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>52</v>
       </c>
+      <c r="S53">
+        <v>8</v>
+      </c>
+      <c r="T53">
+        <v>75</v>
+      </c>
+      <c r="U53" s="2" cm="1">
+        <f t="array" ref="U53">SUMPRODUCT((Tabelle2[Seite]=Q53)*Tabelle2[Score_Gewichtet])</f>
+        <v>2.95</v>
+      </c>
+      <c r="V53" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="W53">
+        <v>1</v>
+      </c>
       <c r="X53">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y53">
-        <v>75</v>
-      </c>
-      <c r="Z53" s="2" cm="1">
-        <f t="array" ref="Z53">SUMPRODUCT((Tabelle2[Seite]=V53)*Tabelle2[Score_Gewichtet])</f>
-        <v>2.95</v>
-      </c>
-      <c r="AA53" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="AB53" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>11</v>
       </c>
@@ -5140,45 +5468,48 @@
       <c r="K54">
         <v>14</v>
       </c>
-      <c r="R54">
+      <c r="M54">
         <v>54</v>
       </c>
-      <c r="S54">
-        <f t="shared" si="0"/>
+      <c r="N54">
+        <f>COUNTIF(B$2:B$1338, M54)</f>
         <v>12</v>
       </c>
-      <c r="T54">
-        <f t="shared" si="1"/>
+      <c r="O54">
+        <f>RANK(N54, $N$2:$N$116)</f>
         <v>39</v>
       </c>
-      <c r="V54">
+      <c r="Q54">
         <v>54</v>
       </c>
-      <c r="W54" s="1">
+      <c r="R54" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>53</v>
       </c>
+      <c r="S54">
+        <v>12</v>
+      </c>
+      <c r="T54">
+        <v>39</v>
+      </c>
+      <c r="U54" s="2" cm="1">
+        <f t="array" ref="U54">SUMPRODUCT((Tabelle2[Seite]=Q54)*Tabelle2[Score_Gewichtet])</f>
+        <v>9.9999999999999982</v>
+      </c>
+      <c r="V54" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="W54">
+        <v>1</v>
+      </c>
       <c r="X54">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y54">
-        <v>39</v>
-      </c>
-      <c r="Z54" s="2" cm="1">
-        <f t="array" ref="Z54">SUMPRODUCT((Tabelle2[Seite]=V54)*Tabelle2[Score_Gewichtet])</f>
-        <v>9.9999999999999982</v>
-      </c>
-      <c r="AA54" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="AB54" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>11</v>
       </c>
@@ -5212,40 +5543,46 @@
       <c r="K55">
         <v>7</v>
       </c>
-      <c r="R55">
+      <c r="M55">
         <v>55</v>
       </c>
-      <c r="S55">
-        <f t="shared" si="0"/>
+      <c r="N55">
+        <f>COUNTIF(B$2:B$1338, M55)</f>
         <v>15</v>
       </c>
-      <c r="T55">
-        <f t="shared" si="1"/>
+      <c r="O55">
+        <f>RANK(N55, $N$2:$N$116)</f>
         <v>26</v>
       </c>
-      <c r="V55">
+      <c r="Q55">
         <v>55</v>
       </c>
-      <c r="W55" s="1">
+      <c r="R55" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>54</v>
       </c>
+      <c r="S55">
+        <v>15</v>
+      </c>
+      <c r="T55">
+        <v>26</v>
+      </c>
+      <c r="U55" s="2" cm="1">
+        <f t="array" ref="U55">SUMPRODUCT((Tabelle2[Seite]=Q55)*Tabelle2[Score_Gewichtet])</f>
+        <v>8.8499999999999979</v>
+      </c>
+      <c r="V55" s="2"/>
+      <c r="W55">
+        <v>0</v>
+      </c>
       <c r="X55">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="Y55">
-        <v>26</v>
-      </c>
-      <c r="Z55" s="2" cm="1">
-        <f t="array" ref="Z55">SUMPRODUCT((Tabelle2[Seite]=V55)*Tabelle2[Score_Gewichtet])</f>
-        <v>8.8499999999999979</v>
-      </c>
-      <c r="AA55" s="2"/>
-      <c r="AD55" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="56" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>11</v>
       </c>
@@ -5279,40 +5616,46 @@
       <c r="K56">
         <v>7</v>
       </c>
-      <c r="R56">
+      <c r="M56">
         <v>56</v>
       </c>
-      <c r="S56">
-        <f t="shared" si="0"/>
+      <c r="N56">
+        <f>COUNTIF(B$2:B$1338, M56)</f>
         <v>18</v>
       </c>
-      <c r="T56">
-        <f t="shared" si="1"/>
+      <c r="O56">
+        <f>RANK(N56, $N$2:$N$116)</f>
         <v>18</v>
       </c>
-      <c r="V56">
+      <c r="Q56">
         <v>56</v>
       </c>
-      <c r="W56" s="1">
+      <c r="R56" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>55</v>
       </c>
+      <c r="S56">
+        <v>18</v>
+      </c>
+      <c r="T56">
+        <v>18</v>
+      </c>
+      <c r="U56" s="2" cm="1">
+        <f t="array" ref="U56">SUMPRODUCT((Tabelle2[Seite]=Q56)*Tabelle2[Score_Gewichtet])</f>
+        <v>11.149999999999997</v>
+      </c>
+      <c r="V56" s="2"/>
+      <c r="W56">
+        <v>0</v>
+      </c>
       <c r="X56">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y56">
-        <v>18</v>
-      </c>
-      <c r="Z56" s="2" cm="1">
-        <f t="array" ref="Z56">SUMPRODUCT((Tabelle2[Seite]=V56)*Tabelle2[Score_Gewichtet])</f>
-        <v>11.149999999999997</v>
-      </c>
-      <c r="AA56" s="2"/>
-      <c r="AD56" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="57" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>11</v>
       </c>
@@ -5346,40 +5689,46 @@
       <c r="K57">
         <v>1</v>
       </c>
-      <c r="R57">
+      <c r="M57">
         <v>57</v>
       </c>
-      <c r="S57">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="T57">
-        <f t="shared" si="1"/>
+      <c r="N57">
+        <f>COUNTIF(B$2:B$1338, M57)</f>
+        <v>13</v>
+      </c>
+      <c r="O57">
+        <f>RANK(N57, $N$2:$N$116)</f>
         <v>34</v>
       </c>
-      <c r="V57">
+      <c r="Q57">
         <v>57</v>
       </c>
-      <c r="W57" s="1">
+      <c r="R57" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>56</v>
       </c>
+      <c r="S57">
+        <v>13</v>
+      </c>
+      <c r="T57">
+        <v>34</v>
+      </c>
+      <c r="U57" s="2" cm="1">
+        <f t="array" ref="U57">SUMPRODUCT((Tabelle2[Seite]=Q57)*Tabelle2[Score_Gewichtet])</f>
+        <v>11.45</v>
+      </c>
+      <c r="V57" s="2"/>
+      <c r="W57">
+        <v>0</v>
+      </c>
       <c r="X57">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y57">
-        <v>34</v>
-      </c>
-      <c r="Z57" s="2" cm="1">
-        <f t="array" ref="Z57">SUMPRODUCT((Tabelle2[Seite]=V57)*Tabelle2[Score_Gewichtet])</f>
-        <v>11.45</v>
-      </c>
-      <c r="AA57" s="2"/>
-      <c r="AD57" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>11</v>
       </c>
@@ -5413,40 +5762,46 @@
       <c r="K58">
         <v>0.6</v>
       </c>
-      <c r="R58">
+      <c r="M58">
         <v>58</v>
       </c>
-      <c r="S58">
-        <f t="shared" si="0"/>
+      <c r="N58">
+        <f>COUNTIF(B$2:B$1338, M58)</f>
         <v>20</v>
       </c>
-      <c r="T58">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="V58">
+      <c r="O58">
+        <f>RANK(N58, $N$2:$N$116)</f>
+        <v>13</v>
+      </c>
+      <c r="Q58">
         <v>58</v>
       </c>
-      <c r="W58" s="1">
+      <c r="R58" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>57</v>
       </c>
+      <c r="S58">
+        <v>20</v>
+      </c>
+      <c r="T58">
+        <v>13</v>
+      </c>
+      <c r="U58" s="2" cm="1">
+        <f t="array" ref="U58">SUMPRODUCT((Tabelle2[Seite]=Q58)*Tabelle2[Score_Gewichtet])</f>
+        <v>13.299999999999999</v>
+      </c>
+      <c r="V58" s="2"/>
+      <c r="W58">
+        <v>0</v>
+      </c>
       <c r="X58">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Y58">
-        <v>13</v>
-      </c>
-      <c r="Z58" s="2" cm="1">
-        <f t="array" ref="Z58">SUMPRODUCT((Tabelle2[Seite]=V58)*Tabelle2[Score_Gewichtet])</f>
-        <v>13.299999999999999</v>
-      </c>
-      <c r="AA58" s="2"/>
-      <c r="AD58" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="59" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>11</v>
       </c>
@@ -5480,40 +5835,46 @@
       <c r="K59">
         <v>1.75</v>
       </c>
-      <c r="R59">
+      <c r="M59">
         <v>59</v>
       </c>
-      <c r="S59">
-        <f t="shared" si="0"/>
+      <c r="N59">
+        <f>COUNTIF(B$2:B$1338, M59)</f>
         <v>9</v>
       </c>
-      <c r="T59">
-        <f t="shared" si="1"/>
+      <c r="O59">
+        <f>RANK(N59, $N$2:$N$116)</f>
         <v>61</v>
       </c>
-      <c r="V59">
+      <c r="Q59">
         <v>59</v>
       </c>
-      <c r="W59" s="1">
+      <c r="R59" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>58</v>
       </c>
+      <c r="S59">
+        <v>9</v>
+      </c>
+      <c r="T59">
+        <v>61</v>
+      </c>
+      <c r="U59" s="2" cm="1">
+        <f t="array" ref="U59">SUMPRODUCT((Tabelle2[Seite]=Q59)*Tabelle2[Score_Gewichtet])</f>
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="V59" s="2"/>
+      <c r="W59">
+        <v>0</v>
+      </c>
       <c r="X59">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y59">
-        <v>61</v>
-      </c>
-      <c r="Z59" s="2" cm="1">
-        <f t="array" ref="Z59">SUMPRODUCT((Tabelle2[Seite]=V59)*Tabelle2[Score_Gewichtet])</f>
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="AA59" s="2"/>
-      <c r="AD59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="60" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>11</v>
       </c>
@@ -5547,40 +5908,46 @@
       <c r="K60">
         <v>0.5</v>
       </c>
-      <c r="R60">
+      <c r="M60">
         <v>60</v>
       </c>
-      <c r="S60">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="T60">
-        <f t="shared" si="1"/>
+      <c r="N60">
+        <f>COUNTIF(B$2:B$1338, M60)</f>
+        <v>13</v>
+      </c>
+      <c r="O60">
+        <f>RANK(N60, $N$2:$N$116)</f>
         <v>34</v>
       </c>
-      <c r="V60">
+      <c r="Q60">
         <v>60</v>
       </c>
-      <c r="W60" s="1">
+      <c r="R60" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>59</v>
       </c>
+      <c r="S60">
+        <v>13</v>
+      </c>
+      <c r="T60">
+        <v>34</v>
+      </c>
+      <c r="U60" s="2" cm="1">
+        <f t="array" ref="U60">SUMPRODUCT((Tabelle2[Seite]=Q60)*Tabelle2[Score_Gewichtet])</f>
+        <v>9.9499999999999993</v>
+      </c>
+      <c r="V60" s="2"/>
+      <c r="W60">
+        <v>0</v>
+      </c>
       <c r="X60">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Y60">
-        <v>34</v>
-      </c>
-      <c r="Z60" s="2" cm="1">
-        <f t="array" ref="Z60">SUMPRODUCT((Tabelle2[Seite]=V60)*Tabelle2[Score_Gewichtet])</f>
-        <v>9.9499999999999993</v>
-      </c>
-      <c r="AA60" s="2"/>
-      <c r="AD60" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="61" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>11</v>
       </c>
@@ -5614,40 +5981,46 @@
       <c r="K61">
         <v>0.6</v>
       </c>
-      <c r="R61">
+      <c r="M61">
         <v>61</v>
       </c>
-      <c r="S61">
-        <f t="shared" si="0"/>
+      <c r="N61">
+        <f>COUNTIF(B$2:B$1338, M61)</f>
         <v>23</v>
       </c>
-      <c r="T61">
-        <f t="shared" si="1"/>
+      <c r="O61">
+        <f>RANK(N61, $N$2:$N$116)</f>
         <v>8</v>
       </c>
-      <c r="V61">
+      <c r="Q61">
         <v>61</v>
       </c>
-      <c r="W61" s="1">
+      <c r="R61" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>60</v>
       </c>
+      <c r="S61">
+        <v>23</v>
+      </c>
+      <c r="T61">
+        <v>8</v>
+      </c>
+      <c r="U61" s="2" cm="1">
+        <f t="array" ref="U61">SUMPRODUCT((Tabelle2[Seite]=Q61)*Tabelle2[Score_Gewichtet])</f>
+        <v>27.45</v>
+      </c>
+      <c r="V61" s="2"/>
+      <c r="W61">
+        <v>0</v>
+      </c>
       <c r="X61">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="Y61">
-        <v>8</v>
-      </c>
-      <c r="Z61" s="2" cm="1">
-        <f t="array" ref="Z61">SUMPRODUCT((Tabelle2[Seite]=V61)*Tabelle2[Score_Gewichtet])</f>
-        <v>27.45</v>
-      </c>
-      <c r="AA61" s="2"/>
-      <c r="AD61" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="62" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>11</v>
       </c>
@@ -5681,40 +6054,46 @@
       <c r="K62">
         <v>0.5</v>
       </c>
-      <c r="R62">
+      <c r="M62">
         <v>62</v>
       </c>
-      <c r="S62">
-        <f t="shared" si="0"/>
+      <c r="N62">
+        <f>COUNTIF(B$2:B$1338, M62)</f>
         <v>8</v>
       </c>
-      <c r="T62">
-        <f t="shared" si="1"/>
+      <c r="O62">
+        <f>RANK(N62, $N$2:$N$116)</f>
         <v>75</v>
       </c>
-      <c r="V62">
+      <c r="Q62">
         <v>62</v>
       </c>
-      <c r="W62" s="1">
+      <c r="R62" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>61</v>
       </c>
+      <c r="S62">
+        <v>8</v>
+      </c>
+      <c r="T62">
+        <v>75</v>
+      </c>
+      <c r="U62" s="2" cm="1">
+        <f t="array" ref="U62">SUMPRODUCT((Tabelle2[Seite]=Q62)*Tabelle2[Score_Gewichtet])</f>
+        <v>16.599999999999998</v>
+      </c>
+      <c r="V62" s="2"/>
+      <c r="W62">
+        <v>0</v>
+      </c>
       <c r="X62">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y62">
-        <v>75</v>
-      </c>
-      <c r="Z62" s="2" cm="1">
-        <f t="array" ref="Z62">SUMPRODUCT((Tabelle2[Seite]=V62)*Tabelle2[Score_Gewichtet])</f>
-        <v>16.599999999999998</v>
-      </c>
-      <c r="AA62" s="2"/>
-      <c r="AD62" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="63" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>11</v>
       </c>
@@ -5748,40 +6127,46 @@
       <c r="K63">
         <v>2</v>
       </c>
-      <c r="R63">
+      <c r="M63">
         <v>63</v>
       </c>
-      <c r="S63">
-        <f t="shared" si="0"/>
+      <c r="N63">
+        <f>COUNTIF(B$2:B$1338, M63)</f>
         <v>4</v>
       </c>
-      <c r="T63">
-        <f t="shared" si="1"/>
+      <c r="O63">
+        <f>RANK(N63, $N$2:$N$116)</f>
         <v>104</v>
       </c>
-      <c r="V63">
+      <c r="Q63">
         <v>63</v>
       </c>
-      <c r="W63" s="1">
+      <c r="R63" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>62</v>
       </c>
+      <c r="S63">
+        <v>4</v>
+      </c>
+      <c r="T63">
+        <v>104</v>
+      </c>
+      <c r="U63" s="2" cm="1">
+        <f t="array" ref="U63">SUMPRODUCT((Tabelle2[Seite]=Q63)*Tabelle2[Score_Gewichtet])</f>
+        <v>3.6</v>
+      </c>
+      <c r="V63" s="2"/>
+      <c r="W63">
+        <v>0</v>
+      </c>
       <c r="X63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y63">
-        <v>104</v>
-      </c>
-      <c r="Z63" s="2" cm="1">
-        <f t="array" ref="Z63">SUMPRODUCT((Tabelle2[Seite]=V63)*Tabelle2[Score_Gewichtet])</f>
-        <v>3.6</v>
-      </c>
-      <c r="AA63" s="2"/>
-      <c r="AD63" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="64" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>11</v>
       </c>
@@ -5815,40 +6200,46 @@
       <c r="K64">
         <v>0.1</v>
       </c>
-      <c r="R64">
+      <c r="M64">
         <v>64</v>
       </c>
-      <c r="S64">
-        <f t="shared" si="0"/>
+      <c r="N64">
+        <f>COUNTIF(B$2:B$1338, M64)</f>
         <v>3</v>
       </c>
-      <c r="T64">
-        <f t="shared" si="1"/>
+      <c r="O64">
+        <f>RANK(N64, $N$2:$N$116)</f>
         <v>108</v>
       </c>
-      <c r="V64">
+      <c r="Q64">
         <v>64</v>
       </c>
-      <c r="W64" s="1">
+      <c r="R64" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>63</v>
       </c>
+      <c r="S64">
+        <v>3</v>
+      </c>
+      <c r="T64">
+        <v>108</v>
+      </c>
+      <c r="U64" s="2" cm="1">
+        <f t="array" ref="U64">SUMPRODUCT((Tabelle2[Seite]=Q64)*Tabelle2[Score_Gewichtet])</f>
+        <v>0.7</v>
+      </c>
+      <c r="V64" s="2"/>
+      <c r="W64">
+        <v>0</v>
+      </c>
       <c r="X64">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y64">
-        <v>108</v>
-      </c>
-      <c r="Z64" s="2" cm="1">
-        <f t="array" ref="Z64">SUMPRODUCT((Tabelle2[Seite]=V64)*Tabelle2[Score_Gewichtet])</f>
-        <v>0.7</v>
-      </c>
-      <c r="AA64" s="2"/>
-      <c r="AD64" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="65" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>11</v>
       </c>
@@ -5882,40 +6273,46 @@
       <c r="K65">
         <v>1.5</v>
       </c>
-      <c r="R65">
+      <c r="M65">
         <v>65</v>
       </c>
-      <c r="S65">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="T65">
-        <f t="shared" si="1"/>
+      <c r="N65">
+        <f>COUNTIF(B$2:B$1338, M65)</f>
+        <v>11</v>
+      </c>
+      <c r="O65">
+        <f>RANK(N65, $N$2:$N$116)</f>
         <v>47</v>
       </c>
-      <c r="V65">
+      <c r="Q65">
         <v>65</v>
       </c>
-      <c r="W65" s="1">
+      <c r="R65" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>64</v>
       </c>
+      <c r="S65">
+        <v>11</v>
+      </c>
+      <c r="T65">
+        <v>47</v>
+      </c>
+      <c r="U65" s="2" cm="1">
+        <f t="array" ref="U65">SUMPRODUCT((Tabelle2[Seite]=Q65)*Tabelle2[Score_Gewichtet])</f>
+        <v>16.3</v>
+      </c>
+      <c r="V65" s="2"/>
+      <c r="W65">
+        <v>0</v>
+      </c>
       <c r="X65">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y65">
-        <v>47</v>
-      </c>
-      <c r="Z65" s="2" cm="1">
-        <f t="array" ref="Z65">SUMPRODUCT((Tabelle2[Seite]=V65)*Tabelle2[Score_Gewichtet])</f>
-        <v>16.3</v>
-      </c>
-      <c r="AA65" s="2"/>
-      <c r="AD65" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="66" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>11</v>
       </c>
@@ -5949,40 +6346,46 @@
       <c r="K66">
         <v>1</v>
       </c>
-      <c r="R66">
+      <c r="M66">
         <v>66</v>
       </c>
-      <c r="S66">
-        <f t="shared" si="0"/>
+      <c r="N66">
+        <f>COUNTIF(B$2:B$1338, M66)</f>
         <v>7</v>
       </c>
-      <c r="T66">
-        <f t="shared" si="1"/>
+      <c r="O66">
+        <f>RANK(N66, $N$2:$N$116)</f>
         <v>87</v>
       </c>
-      <c r="V66">
+      <c r="Q66">
         <v>66</v>
       </c>
-      <c r="W66" s="1">
+      <c r="R66" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>65</v>
       </c>
+      <c r="S66">
+        <v>7</v>
+      </c>
+      <c r="T66">
+        <v>87</v>
+      </c>
+      <c r="U66" s="2" cm="1">
+        <f t="array" ref="U66">SUMPRODUCT((Tabelle2[Seite]=Q66)*Tabelle2[Score_Gewichtet])</f>
+        <v>12.7</v>
+      </c>
+      <c r="V66" s="2"/>
+      <c r="W66">
+        <v>0</v>
+      </c>
       <c r="X66">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y66">
-        <v>87</v>
-      </c>
-      <c r="Z66" s="2" cm="1">
-        <f t="array" ref="Z66">SUMPRODUCT((Tabelle2[Seite]=V66)*Tabelle2[Score_Gewichtet])</f>
-        <v>12.7</v>
-      </c>
-      <c r="AA66" s="2"/>
-      <c r="AD66" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="67" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>11</v>
       </c>
@@ -6016,45 +6419,48 @@
       <c r="K67">
         <v>0.3</v>
       </c>
-      <c r="R67">
+      <c r="M67">
         <v>67</v>
       </c>
-      <c r="S67">
-        <f t="shared" ref="S67:S116" si="2">COUNTIF(B$2:B$1338, R67)</f>
+      <c r="N67">
+        <f>COUNTIF(B$2:B$1338, M67)</f>
         <v>8</v>
       </c>
-      <c r="T67">
-        <f t="shared" ref="T67:T116" si="3">RANK(S67, $S$2:$S$116)</f>
+      <c r="O67">
+        <f>RANK(N67, $N$2:$N$116)</f>
         <v>75</v>
       </c>
-      <c r="V67">
+      <c r="Q67">
         <v>67</v>
       </c>
-      <c r="W67" s="1">
+      <c r="R67" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>66</v>
       </c>
+      <c r="S67">
+        <v>8</v>
+      </c>
+      <c r="T67">
+        <v>75</v>
+      </c>
+      <c r="U67" s="2" cm="1">
+        <f t="array" ref="U67">SUMPRODUCT((Tabelle2[Seite]=Q67)*Tabelle2[Score_Gewichtet])</f>
+        <v>8.0999999999999979</v>
+      </c>
+      <c r="V67" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="W67">
+        <v>1</v>
+      </c>
       <c r="X67">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y67">
-        <v>75</v>
-      </c>
-      <c r="Z67" s="2" cm="1">
-        <f t="array" ref="Z67">SUMPRODUCT((Tabelle2[Seite]=V67)*Tabelle2[Score_Gewichtet])</f>
-        <v>8.0999999999999979</v>
-      </c>
-      <c r="AA67" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="AB67" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:31" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>11</v>
       </c>
@@ -6088,45 +6494,48 @@
       <c r="K68">
         <v>1.5</v>
       </c>
-      <c r="R68">
+      <c r="M68">
         <v>68</v>
       </c>
-      <c r="S68">
-        <f t="shared" si="2"/>
+      <c r="N68">
+        <f>COUNTIF(B$2:B$1338, M68)</f>
         <v>21</v>
       </c>
-      <c r="T68">
-        <f t="shared" si="3"/>
+      <c r="O68">
+        <f>RANK(N68, $N$2:$N$116)</f>
         <v>10</v>
       </c>
-      <c r="V68">
+      <c r="Q68">
         <v>68</v>
       </c>
-      <c r="W68" s="1">
+      <c r="R68" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>67</v>
       </c>
+      <c r="S68">
+        <v>21</v>
+      </c>
+      <c r="T68">
+        <v>10</v>
+      </c>
+      <c r="U68" s="2" cm="1">
+        <f t="array" ref="U68">SUMPRODUCT((Tabelle2[Seite]=Q68)*Tabelle2[Score_Gewichtet])</f>
+        <v>20.05</v>
+      </c>
+      <c r="V68" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="W68">
+        <v>1</v>
+      </c>
       <c r="X68">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="Y68">
-        <v>10</v>
-      </c>
-      <c r="Z68" s="2" cm="1">
-        <f t="array" ref="Z68">SUMPRODUCT((Tabelle2[Seite]=V68)*Tabelle2[Score_Gewichtet])</f>
-        <v>20.05</v>
-      </c>
-      <c r="AA68" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="AB68" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE68">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:31" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>11</v>
       </c>
@@ -6160,45 +6569,48 @@
       <c r="K69">
         <v>0.1</v>
       </c>
-      <c r="R69">
+      <c r="M69">
         <v>69</v>
       </c>
-      <c r="S69">
-        <f t="shared" si="2"/>
+      <c r="N69">
+        <f>COUNTIF(B$2:B$1338, M69)</f>
         <v>21</v>
       </c>
-      <c r="T69">
-        <f t="shared" si="3"/>
+      <c r="O69">
+        <f>RANK(N69, $N$2:$N$116)</f>
         <v>10</v>
       </c>
-      <c r="V69">
+      <c r="Q69">
         <v>69</v>
       </c>
-      <c r="W69" s="1">
+      <c r="R69" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>68</v>
       </c>
+      <c r="S69">
+        <v>21</v>
+      </c>
+      <c r="T69">
+        <v>10</v>
+      </c>
+      <c r="U69" s="2" cm="1">
+        <f t="array" ref="U69">SUMPRODUCT((Tabelle2[Seite]=Q69)*Tabelle2[Score_Gewichtet])</f>
+        <v>11.95</v>
+      </c>
+      <c r="V69" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="W69">
+        <v>1</v>
+      </c>
       <c r="X69">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="Y69">
-        <v>10</v>
-      </c>
-      <c r="Z69" s="2" cm="1">
-        <f t="array" ref="Z69">SUMPRODUCT((Tabelle2[Seite]=V69)*Tabelle2[Score_Gewichtet])</f>
-        <v>11.95</v>
-      </c>
-      <c r="AA69" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="AB69" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:31" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>11</v>
       </c>
@@ -6232,45 +6644,48 @@
       <c r="K70">
         <v>1.5</v>
       </c>
-      <c r="R70">
+      <c r="M70">
         <v>70</v>
       </c>
-      <c r="S70">
-        <f t="shared" si="2"/>
+      <c r="N70">
+        <f>COUNTIF(B$2:B$1338, M70)</f>
         <v>10</v>
       </c>
-      <c r="T70">
-        <f t="shared" si="3"/>
+      <c r="O70">
+        <f>RANK(N70, $N$2:$N$116)</f>
         <v>55</v>
       </c>
-      <c r="V70">
+      <c r="Q70">
         <v>70</v>
       </c>
-      <c r="W70" s="1">
+      <c r="R70" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>69</v>
       </c>
+      <c r="S70">
+        <v>10</v>
+      </c>
+      <c r="T70">
+        <v>55</v>
+      </c>
+      <c r="U70" s="2" cm="1">
+        <f t="array" ref="U70">SUMPRODUCT((Tabelle2[Seite]=Q70)*Tabelle2[Score_Gewichtet])</f>
+        <v>12.6</v>
+      </c>
+      <c r="V70" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="W70">
+        <v>1</v>
+      </c>
       <c r="X70">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y70">
-        <v>55</v>
-      </c>
-      <c r="Z70" s="2" cm="1">
-        <f t="array" ref="Z70">SUMPRODUCT((Tabelle2[Seite]=V70)*Tabelle2[Score_Gewichtet])</f>
-        <v>12.6</v>
-      </c>
-      <c r="AA70" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="AB70" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:31" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>11</v>
       </c>
@@ -6304,40 +6719,46 @@
       <c r="K71">
         <v>1</v>
       </c>
-      <c r="R71">
+      <c r="M71">
         <v>71</v>
       </c>
-      <c r="S71">
-        <f t="shared" si="2"/>
+      <c r="N71">
+        <f>COUNTIF(B$2:B$1338, M71)</f>
         <v>9</v>
       </c>
-      <c r="T71">
-        <f t="shared" si="3"/>
+      <c r="O71">
+        <f>RANK(N71, $N$2:$N$116)</f>
         <v>61</v>
       </c>
-      <c r="V71">
+      <c r="Q71">
         <v>71</v>
       </c>
-      <c r="W71" s="1">
+      <c r="R71" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>70</v>
       </c>
+      <c r="S71">
+        <v>9</v>
+      </c>
+      <c r="T71">
+        <v>61</v>
+      </c>
+      <c r="U71" s="2" cm="1">
+        <f t="array" ref="U71">SUMPRODUCT((Tabelle2[Seite]=Q71)*Tabelle2[Score_Gewichtet])</f>
+        <v>6.6000000000000005</v>
+      </c>
+      <c r="V71" s="2"/>
+      <c r="W71">
+        <v>0</v>
+      </c>
       <c r="X71">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y71">
-        <v>61</v>
-      </c>
-      <c r="Z71" s="2" cm="1">
-        <f t="array" ref="Z71">SUMPRODUCT((Tabelle2[Seite]=V71)*Tabelle2[Score_Gewichtet])</f>
-        <v>6.6000000000000005</v>
-      </c>
-      <c r="AA71" s="2"/>
-      <c r="AD71" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="72" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>11</v>
       </c>
@@ -6371,40 +6792,46 @@
       <c r="K72">
         <v>1</v>
       </c>
-      <c r="R72">
+      <c r="M72">
         <v>72</v>
       </c>
-      <c r="S72">
-        <f t="shared" si="2"/>
+      <c r="N72">
+        <f>COUNTIF(B$2:B$1338, M72)</f>
         <v>4</v>
       </c>
-      <c r="T72">
-        <f t="shared" si="3"/>
+      <c r="O72">
+        <f>RANK(N72, $N$2:$N$116)</f>
         <v>104</v>
       </c>
-      <c r="V72">
+      <c r="Q72">
         <v>72</v>
       </c>
-      <c r="W72" s="1">
+      <c r="R72" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>71</v>
       </c>
+      <c r="S72">
+        <v>4</v>
+      </c>
+      <c r="T72">
+        <v>104</v>
+      </c>
+      <c r="U72" s="2" cm="1">
+        <f t="array" ref="U72">SUMPRODUCT((Tabelle2[Seite]=Q72)*Tabelle2[Score_Gewichtet])</f>
+        <v>5.8000000000000007</v>
+      </c>
+      <c r="V72" s="2"/>
+      <c r="W72">
+        <v>0</v>
+      </c>
       <c r="X72">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y72">
-        <v>104</v>
-      </c>
-      <c r="Z72" s="2" cm="1">
-        <f t="array" ref="Z72">SUMPRODUCT((Tabelle2[Seite]=V72)*Tabelle2[Score_Gewichtet])</f>
-        <v>5.8000000000000007</v>
-      </c>
-      <c r="AA72" s="2"/>
-      <c r="AD72" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="73" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>11</v>
       </c>
@@ -6438,40 +6865,46 @@
       <c r="K73">
         <v>1.5</v>
       </c>
-      <c r="R73">
+      <c r="M73">
         <v>73</v>
       </c>
-      <c r="S73">
-        <f t="shared" si="2"/>
+      <c r="N73">
+        <f>COUNTIF(B$2:B$1338, M73)</f>
         <v>20</v>
       </c>
-      <c r="T73">
-        <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
-      <c r="V73">
+      <c r="O73">
+        <f>RANK(N73, $N$2:$N$116)</f>
+        <v>13</v>
+      </c>
+      <c r="Q73">
         <v>73</v>
       </c>
-      <c r="W73" s="1">
+      <c r="R73" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>72</v>
       </c>
+      <c r="S73">
+        <v>20</v>
+      </c>
+      <c r="T73">
+        <v>13</v>
+      </c>
+      <c r="U73" s="2" cm="1">
+        <f t="array" ref="U73">SUMPRODUCT((Tabelle2[Seite]=Q73)*Tabelle2[Score_Gewichtet])</f>
+        <v>18.599999999999998</v>
+      </c>
+      <c r="V73" s="2"/>
+      <c r="W73">
+        <v>0</v>
+      </c>
       <c r="X73">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="Y73">
-        <v>13</v>
-      </c>
-      <c r="Z73" s="2" cm="1">
-        <f t="array" ref="Z73">SUMPRODUCT((Tabelle2[Seite]=V73)*Tabelle2[Score_Gewichtet])</f>
-        <v>18.599999999999998</v>
-      </c>
-      <c r="AA73" s="2"/>
-      <c r="AD73" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="74" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>11</v>
       </c>
@@ -6505,40 +6938,46 @@
       <c r="K74">
         <v>0.6</v>
       </c>
-      <c r="R74">
+      <c r="M74">
         <v>74</v>
       </c>
-      <c r="S74">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-      <c r="T74">
-        <f t="shared" si="3"/>
+      <c r="N74">
+        <f>COUNTIF(B$2:B$1338, M74)</f>
+        <v>11</v>
+      </c>
+      <c r="O74">
+        <f>RANK(N74, $N$2:$N$116)</f>
         <v>47</v>
       </c>
-      <c r="V74">
+      <c r="Q74">
         <v>74</v>
       </c>
-      <c r="W74" s="1">
+      <c r="R74" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>73</v>
       </c>
+      <c r="S74">
+        <v>11</v>
+      </c>
+      <c r="T74">
+        <v>47</v>
+      </c>
+      <c r="U74" s="2" cm="1">
+        <f t="array" ref="U74">SUMPRODUCT((Tabelle2[Seite]=Q74)*Tabelle2[Score_Gewichtet])</f>
+        <v>10.799999999999999</v>
+      </c>
+      <c r="V74" s="2"/>
+      <c r="W74">
+        <v>0</v>
+      </c>
       <c r="X74">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y74">
-        <v>47</v>
-      </c>
-      <c r="Z74" s="2" cm="1">
-        <f t="array" ref="Z74">SUMPRODUCT((Tabelle2[Seite]=V74)*Tabelle2[Score_Gewichtet])</f>
-        <v>10.799999999999999</v>
-      </c>
-      <c r="AA74" s="2"/>
-      <c r="AD74" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="75" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>11</v>
       </c>
@@ -6572,40 +7011,46 @@
       <c r="K75">
         <v>1.35</v>
       </c>
-      <c r="R75">
+      <c r="M75">
         <v>75</v>
       </c>
-      <c r="S75">
-        <f t="shared" si="2"/>
+      <c r="N75">
+        <f>COUNTIF(B$2:B$1338, M75)</f>
         <v>14</v>
       </c>
-      <c r="T75">
-        <f t="shared" si="3"/>
+      <c r="O75">
+        <f>RANK(N75, $N$2:$N$116)</f>
         <v>31</v>
       </c>
-      <c r="V75">
+      <c r="Q75">
         <v>75</v>
       </c>
-      <c r="W75" s="1">
+      <c r="R75" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>74</v>
       </c>
+      <c r="S75">
+        <v>14</v>
+      </c>
+      <c r="T75">
+        <v>31</v>
+      </c>
+      <c r="U75" s="2" cm="1">
+        <f t="array" ref="U75">SUMPRODUCT((Tabelle2[Seite]=Q75)*Tabelle2[Score_Gewichtet])</f>
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="V75" s="2"/>
+      <c r="W75">
+        <v>0</v>
+      </c>
       <c r="X75">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Y75">
-        <v>31</v>
-      </c>
-      <c r="Z75" s="2" cm="1">
-        <f t="array" ref="Z75">SUMPRODUCT((Tabelle2[Seite]=V75)*Tabelle2[Score_Gewichtet])</f>
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="AA75" s="2"/>
-      <c r="AD75" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="76" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>11</v>
       </c>
@@ -6639,40 +7084,46 @@
       <c r="K76">
         <v>0.75</v>
       </c>
-      <c r="R76">
+      <c r="M76">
         <v>76</v>
       </c>
-      <c r="S76">
-        <f t="shared" si="2"/>
+      <c r="N76">
+        <f>COUNTIF(B$2:B$1338, M76)</f>
         <v>16</v>
       </c>
-      <c r="T76">
-        <f t="shared" si="3"/>
+      <c r="O76">
+        <f>RANK(N76, $N$2:$N$116)</f>
         <v>21</v>
       </c>
-      <c r="V76">
+      <c r="Q76">
         <v>76</v>
       </c>
-      <c r="W76" s="1">
+      <c r="R76" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>75</v>
       </c>
+      <c r="S76">
+        <v>16</v>
+      </c>
+      <c r="T76">
+        <v>21</v>
+      </c>
+      <c r="U76" s="2" cm="1">
+        <f t="array" ref="U76">SUMPRODUCT((Tabelle2[Seite]=Q76)*Tabelle2[Score_Gewichtet])</f>
+        <v>8.3999999999999986</v>
+      </c>
+      <c r="V76" s="2"/>
+      <c r="W76">
+        <v>0</v>
+      </c>
       <c r="X76">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y76">
-        <v>21</v>
-      </c>
-      <c r="Z76" s="2" cm="1">
-        <f t="array" ref="Z76">SUMPRODUCT((Tabelle2[Seite]=V76)*Tabelle2[Score_Gewichtet])</f>
-        <v>8.3999999999999986</v>
-      </c>
-      <c r="AA76" s="2"/>
-      <c r="AD76" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="77" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>11</v>
       </c>
@@ -6706,40 +7157,46 @@
       <c r="K77">
         <v>1</v>
       </c>
-      <c r="R77">
+      <c r="M77">
         <v>77</v>
       </c>
-      <c r="S77">
-        <f t="shared" si="2"/>
+      <c r="N77">
+        <f>COUNTIF(B$2:B$1338, M77)</f>
         <v>10</v>
       </c>
-      <c r="T77">
-        <f t="shared" si="3"/>
+      <c r="O77">
+        <f>RANK(N77, $N$2:$N$116)</f>
         <v>55</v>
       </c>
-      <c r="V77">
+      <c r="Q77">
         <v>77</v>
       </c>
-      <c r="W77" s="1">
+      <c r="R77" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>76</v>
       </c>
+      <c r="S77">
+        <v>10</v>
+      </c>
+      <c r="T77">
+        <v>55</v>
+      </c>
+      <c r="U77" s="2" cm="1">
+        <f t="array" ref="U77">SUMPRODUCT((Tabelle2[Seite]=Q77)*Tabelle2[Score_Gewichtet])</f>
+        <v>14.7</v>
+      </c>
+      <c r="V77" s="2"/>
+      <c r="W77">
+        <v>0</v>
+      </c>
       <c r="X77">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y77">
-        <v>55</v>
-      </c>
-      <c r="Z77" s="2" cm="1">
-        <f t="array" ref="Z77">SUMPRODUCT((Tabelle2[Seite]=V77)*Tabelle2[Score_Gewichtet])</f>
-        <v>14.7</v>
-      </c>
-      <c r="AA77" s="2"/>
-      <c r="AD77" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="78" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>11</v>
       </c>
@@ -6773,40 +7230,46 @@
       <c r="K78">
         <v>1.5</v>
       </c>
-      <c r="R78">
+      <c r="M78">
         <v>78</v>
       </c>
-      <c r="S78">
-        <f t="shared" si="2"/>
+      <c r="N78">
+        <f>COUNTIF(B$2:B$1338, M78)</f>
         <v>4</v>
       </c>
-      <c r="T78">
-        <f t="shared" si="3"/>
+      <c r="O78">
+        <f>RANK(N78, $N$2:$N$116)</f>
         <v>104</v>
       </c>
-      <c r="V78">
+      <c r="Q78">
         <v>78</v>
       </c>
-      <c r="W78" s="1">
+      <c r="R78" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>77</v>
       </c>
+      <c r="S78">
+        <v>4</v>
+      </c>
+      <c r="T78">
+        <v>104</v>
+      </c>
+      <c r="U78" s="2" cm="1">
+        <f t="array" ref="U78">SUMPRODUCT((Tabelle2[Seite]=Q78)*Tabelle2[Score_Gewichtet])</f>
+        <v>6.25</v>
+      </c>
+      <c r="V78" s="2"/>
+      <c r="W78">
+        <v>0</v>
+      </c>
       <c r="X78">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y78">
-        <v>104</v>
-      </c>
-      <c r="Z78" s="2" cm="1">
-        <f t="array" ref="Z78">SUMPRODUCT((Tabelle2[Seite]=V78)*Tabelle2[Score_Gewichtet])</f>
-        <v>6.25</v>
-      </c>
-      <c r="AA78" s="2"/>
-      <c r="AD78" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="79" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>11</v>
       </c>
@@ -6840,40 +7303,46 @@
       <c r="K79">
         <v>1.35</v>
       </c>
-      <c r="R79">
+      <c r="M79">
         <v>79</v>
       </c>
-      <c r="S79">
-        <f t="shared" si="2"/>
+      <c r="N79">
+        <f>COUNTIF(B$2:B$1338, M79)</f>
         <v>8</v>
       </c>
-      <c r="T79">
-        <f t="shared" si="3"/>
+      <c r="O79">
+        <f>RANK(N79, $N$2:$N$116)</f>
         <v>75</v>
       </c>
-      <c r="V79">
+      <c r="Q79">
         <v>79</v>
       </c>
-      <c r="W79" s="1">
+      <c r="R79" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>78</v>
       </c>
+      <c r="S79">
+        <v>8</v>
+      </c>
+      <c r="T79">
+        <v>75</v>
+      </c>
+      <c r="U79" s="2" cm="1">
+        <f t="array" ref="U79">SUMPRODUCT((Tabelle2[Seite]=Q79)*Tabelle2[Score_Gewichtet])</f>
+        <v>5.45</v>
+      </c>
+      <c r="V79" s="2"/>
+      <c r="W79">
+        <v>0</v>
+      </c>
       <c r="X79">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y79">
-        <v>75</v>
-      </c>
-      <c r="Z79" s="2" cm="1">
-        <f t="array" ref="Z79">SUMPRODUCT((Tabelle2[Seite]=V79)*Tabelle2[Score_Gewichtet])</f>
-        <v>5.45</v>
-      </c>
-      <c r="AA79" s="2"/>
-      <c r="AD79" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="80" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>11</v>
       </c>
@@ -6907,40 +7376,46 @@
       <c r="K80">
         <v>0.4</v>
       </c>
-      <c r="R80">
+      <c r="M80">
         <v>80</v>
       </c>
-      <c r="S80">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-      <c r="T80">
-        <f t="shared" si="3"/>
+      <c r="N80">
+        <f>COUNTIF(B$2:B$1338, M80)</f>
+        <v>11</v>
+      </c>
+      <c r="O80">
+        <f>RANK(N80, $N$2:$N$116)</f>
         <v>47</v>
       </c>
-      <c r="V80">
+      <c r="Q80">
         <v>80</v>
       </c>
-      <c r="W80" s="1">
+      <c r="R80" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>79</v>
       </c>
+      <c r="S80">
+        <v>11</v>
+      </c>
+      <c r="T80">
+        <v>47</v>
+      </c>
+      <c r="U80" s="2" cm="1">
+        <f t="array" ref="U80">SUMPRODUCT((Tabelle2[Seite]=Q80)*Tabelle2[Score_Gewichtet])</f>
+        <v>11.1</v>
+      </c>
+      <c r="V80" s="2"/>
+      <c r="W80">
+        <v>0</v>
+      </c>
       <c r="X80">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y80">
-        <v>47</v>
-      </c>
-      <c r="Z80" s="2" cm="1">
-        <f t="array" ref="Z80">SUMPRODUCT((Tabelle2[Seite]=V80)*Tabelle2[Score_Gewichtet])</f>
-        <v>11.1</v>
-      </c>
-      <c r="AA80" s="2"/>
-      <c r="AD80" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="81" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>11</v>
       </c>
@@ -6974,45 +7449,48 @@
       <c r="K81">
         <v>0.75</v>
       </c>
-      <c r="R81">
+      <c r="M81">
         <v>81</v>
       </c>
-      <c r="S81">
-        <f t="shared" si="2"/>
+      <c r="N81">
+        <f>COUNTIF(B$2:B$1338, M81)</f>
         <v>16</v>
       </c>
-      <c r="T81">
-        <f t="shared" si="3"/>
+      <c r="O81">
+        <f>RANK(N81, $N$2:$N$116)</f>
         <v>21</v>
       </c>
-      <c r="V81">
+      <c r="Q81">
         <v>81</v>
       </c>
-      <c r="W81" s="1">
+      <c r="R81" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>80</v>
       </c>
+      <c r="S81">
+        <v>16</v>
+      </c>
+      <c r="T81">
+        <v>21</v>
+      </c>
+      <c r="U81" s="2" cm="1">
+        <f t="array" ref="U81">SUMPRODUCT((Tabelle2[Seite]=Q81)*Tabelle2[Score_Gewichtet])</f>
+        <v>31.1</v>
+      </c>
+      <c r="V81" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="W81">
+        <v>2</v>
+      </c>
       <c r="X81">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y81">
-        <v>21</v>
-      </c>
-      <c r="Z81" s="2" cm="1">
-        <f t="array" ref="Z81">SUMPRODUCT((Tabelle2[Seite]=V81)*Tabelle2[Score_Gewichtet])</f>
-        <v>31.1</v>
-      </c>
-      <c r="AA81" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB81" t="s">
-        <v>150</v>
-      </c>
-      <c r="AE81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:31" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>11</v>
       </c>
@@ -7046,45 +7524,48 @@
       <c r="K82">
         <v>0.5</v>
       </c>
-      <c r="R82">
+      <c r="M82">
         <v>82</v>
       </c>
-      <c r="S82">
-        <f t="shared" si="2"/>
+      <c r="N82">
+        <f>COUNTIF(B$2:B$1338, M82)</f>
         <v>27</v>
       </c>
-      <c r="T82">
-        <f t="shared" si="3"/>
+      <c r="O82">
+        <f>RANK(N82, $N$2:$N$116)</f>
         <v>4</v>
       </c>
-      <c r="V82">
+      <c r="Q82">
         <v>82</v>
       </c>
-      <c r="W82" s="1">
+      <c r="R82" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>81</v>
       </c>
+      <c r="S82">
+        <v>27</v>
+      </c>
+      <c r="T82">
+        <v>4</v>
+      </c>
+      <c r="U82" s="2" cm="1">
+        <f t="array" ref="U82">SUMPRODUCT((Tabelle2[Seite]=Q82)*Tabelle2[Score_Gewichtet])</f>
+        <v>31.200000000000003</v>
+      </c>
+      <c r="V82" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="W82">
+        <v>2</v>
+      </c>
       <c r="X82">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="Y82">
-        <v>4</v>
-      </c>
-      <c r="Z82" s="2" cm="1">
-        <f t="array" ref="Z82">SUMPRODUCT((Tabelle2[Seite]=V82)*Tabelle2[Score_Gewichtet])</f>
-        <v>31.200000000000003</v>
-      </c>
-      <c r="AA82" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB82" t="s">
-        <v>150</v>
-      </c>
-      <c r="AE82">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:31" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>11</v>
       </c>
@@ -7118,45 +7599,48 @@
       <c r="K83">
         <v>0.2</v>
       </c>
-      <c r="R83">
+      <c r="M83">
         <v>83</v>
       </c>
-      <c r="S83">
-        <f t="shared" si="2"/>
+      <c r="N83">
+        <f>COUNTIF(B$2:B$1338, M83)</f>
         <v>25</v>
       </c>
-      <c r="T83">
-        <f t="shared" si="3"/>
+      <c r="O83">
+        <f>RANK(N83, $N$2:$N$116)</f>
         <v>7</v>
       </c>
-      <c r="V83">
+      <c r="Q83">
         <v>83</v>
       </c>
-      <c r="W83" s="1">
+      <c r="R83" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>82</v>
       </c>
+      <c r="S83">
+        <v>25</v>
+      </c>
+      <c r="T83">
+        <v>7</v>
+      </c>
+      <c r="U83" s="2" cm="1">
+        <f t="array" ref="U83">SUMPRODUCT((Tabelle2[Seite]=Q83)*Tabelle2[Score_Gewichtet])</f>
+        <v>24.150000000000002</v>
+      </c>
+      <c r="V83" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="W83">
+        <v>1</v>
+      </c>
       <c r="X83">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="Y83">
-        <v>7</v>
-      </c>
-      <c r="Z83" s="2" cm="1">
-        <f t="array" ref="Z83">SUMPRODUCT((Tabelle2[Seite]=V83)*Tabelle2[Score_Gewichtet])</f>
-        <v>24.150000000000002</v>
-      </c>
-      <c r="AA83" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="AB83" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE83">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:31" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>11</v>
       </c>
@@ -7190,45 +7674,48 @@
       <c r="K84">
         <v>1.5</v>
       </c>
-      <c r="R84">
+      <c r="M84">
         <v>84</v>
       </c>
-      <c r="S84">
-        <f t="shared" si="2"/>
+      <c r="N84">
+        <f>COUNTIF(B$2:B$1338, M84)</f>
         <v>31</v>
       </c>
-      <c r="T84">
-        <f t="shared" si="3"/>
+      <c r="O84">
+        <f>RANK(N84, $N$2:$N$116)</f>
         <v>3</v>
       </c>
-      <c r="V84">
+      <c r="Q84">
         <v>84</v>
       </c>
-      <c r="W84" s="1">
+      <c r="R84" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>83</v>
       </c>
+      <c r="S84">
+        <v>31</v>
+      </c>
+      <c r="T84">
+        <v>3</v>
+      </c>
+      <c r="U84" s="2" cm="1">
+        <f t="array" ref="U84">SUMPRODUCT((Tabelle2[Seite]=Q84)*Tabelle2[Score_Gewichtet])</f>
+        <v>27.749999999999996</v>
+      </c>
+      <c r="V84" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="W84">
+        <v>1</v>
+      </c>
       <c r="X84">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="Y84">
-        <v>3</v>
-      </c>
-      <c r="Z84" s="2" cm="1">
-        <f t="array" ref="Z84">SUMPRODUCT((Tabelle2[Seite]=V84)*Tabelle2[Score_Gewichtet])</f>
-        <v>27.749999999999996</v>
-      </c>
-      <c r="AA84" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="AB84" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE84">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:31" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>11</v>
       </c>
@@ -7262,40 +7749,48 @@
       <c r="K85">
         <v>0.1</v>
       </c>
-      <c r="R85">
+      <c r="M85">
         <v>85</v>
       </c>
-      <c r="S85">
-        <f t="shared" si="2"/>
+      <c r="N85">
+        <f>COUNTIF(B$2:B$1338, M85)</f>
         <v>23</v>
       </c>
-      <c r="T85">
-        <f t="shared" si="3"/>
+      <c r="O85">
+        <f>RANK(N85, $N$2:$N$116)</f>
         <v>8</v>
       </c>
-      <c r="V85">
+      <c r="Q85">
         <v>85</v>
       </c>
-      <c r="W85" s="1">
+      <c r="R85" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>84</v>
       </c>
+      <c r="S85">
+        <v>23</v>
+      </c>
+      <c r="T85">
+        <v>8</v>
+      </c>
+      <c r="U85" s="2" cm="1">
+        <f t="array" ref="U85">SUMPRODUCT((Tabelle2[Seite]=Q85)*Tabelle2[Score_Gewichtet])</f>
+        <v>16.600000000000001</v>
+      </c>
+      <c r="V85" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="W85">
+        <v>0</v>
+      </c>
       <c r="X85">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="Y85">
-        <v>8</v>
-      </c>
-      <c r="Z85" s="2" cm="1">
-        <f t="array" ref="Z85">SUMPRODUCT((Tabelle2[Seite]=V85)*Tabelle2[Score_Gewichtet])</f>
-        <v>16.600000000000001</v>
-      </c>
-      <c r="AA85" s="2"/>
-      <c r="AD85" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="86" spans="1:31" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>11</v>
       </c>
@@ -7329,40 +7824,48 @@
       <c r="K86">
         <v>0.5</v>
       </c>
-      <c r="R86">
+      <c r="M86">
         <v>86</v>
       </c>
-      <c r="S86">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-      <c r="T86">
-        <f t="shared" si="3"/>
+      <c r="N86">
+        <f>COUNTIF(B$2:B$1338, M86)</f>
+        <v>11</v>
+      </c>
+      <c r="O86">
+        <f>RANK(N86, $N$2:$N$116)</f>
         <v>47</v>
       </c>
-      <c r="V86">
+      <c r="Q86">
         <v>86</v>
       </c>
-      <c r="W86" s="1">
+      <c r="R86" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>85</v>
       </c>
+      <c r="S86">
+        <v>11</v>
+      </c>
+      <c r="T86">
+        <v>47</v>
+      </c>
+      <c r="U86" s="2" cm="1">
+        <f t="array" ref="U86">SUMPRODUCT((Tabelle2[Seite]=Q86)*Tabelle2[Score_Gewichtet])</f>
+        <v>7.8499999999999988</v>
+      </c>
+      <c r="V86" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="W86">
+        <v>0</v>
+      </c>
       <c r="X86">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="Y86">
-        <v>47</v>
-      </c>
-      <c r="Z86" s="2" cm="1">
-        <f t="array" ref="Z86">SUMPRODUCT((Tabelle2[Seite]=V86)*Tabelle2[Score_Gewichtet])</f>
-        <v>7.8499999999999988</v>
-      </c>
-      <c r="AA86" s="2"/>
-      <c r="AD86" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="87" spans="1:31" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>11</v>
       </c>
@@ -7396,40 +7899,48 @@
       <c r="K87">
         <v>0.1</v>
       </c>
-      <c r="R87">
+      <c r="M87">
         <v>87</v>
       </c>
-      <c r="S87">
-        <f t="shared" si="2"/>
+      <c r="N87">
+        <f>COUNTIF(B$2:B$1338, M87)</f>
         <v>12</v>
       </c>
-      <c r="T87">
-        <f t="shared" si="3"/>
+      <c r="O87">
+        <f>RANK(N87, $N$2:$N$116)</f>
         <v>39</v>
       </c>
-      <c r="V87">
+      <c r="Q87">
         <v>87</v>
       </c>
-      <c r="W87" s="1">
+      <c r="R87" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>86</v>
       </c>
+      <c r="S87">
+        <v>12</v>
+      </c>
+      <c r="T87">
+        <v>39</v>
+      </c>
+      <c r="U87" s="2" cm="1">
+        <f t="array" ref="U87">SUMPRODUCT((Tabelle2[Seite]=Q87)*Tabelle2[Score_Gewichtet])</f>
+        <v>8.2999999999999989</v>
+      </c>
+      <c r="V87" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="W87">
+        <v>0</v>
+      </c>
       <c r="X87">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y87">
-        <v>39</v>
-      </c>
-      <c r="Z87" s="2" cm="1">
-        <f t="array" ref="Z87">SUMPRODUCT((Tabelle2[Seite]=V87)*Tabelle2[Score_Gewichtet])</f>
-        <v>8.2999999999999989</v>
-      </c>
-      <c r="AA87" s="2"/>
-      <c r="AD87" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="88" spans="1:31" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>11</v>
       </c>
@@ -7463,40 +7974,48 @@
       <c r="K88">
         <v>0.2</v>
       </c>
-      <c r="R88">
+      <c r="M88">
         <v>88</v>
       </c>
-      <c r="S88">
-        <f t="shared" si="2"/>
+      <c r="N88">
+        <f>COUNTIF(B$2:B$1338, M88)</f>
         <v>15</v>
       </c>
-      <c r="T88">
-        <f t="shared" si="3"/>
+      <c r="O88">
+        <f>RANK(N88, $N$2:$N$116)</f>
         <v>26</v>
       </c>
-      <c r="V88">
+      <c r="Q88">
         <v>88</v>
       </c>
-      <c r="W88" s="1">
+      <c r="R88" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>87</v>
       </c>
+      <c r="S88">
+        <v>15</v>
+      </c>
+      <c r="T88">
+        <v>26</v>
+      </c>
+      <c r="U88" s="2" cm="1">
+        <f t="array" ref="U88">SUMPRODUCT((Tabelle2[Seite]=Q88)*Tabelle2[Score_Gewichtet])</f>
+        <v>9.1999999999999975</v>
+      </c>
+      <c r="V88" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="W88">
+        <v>0</v>
+      </c>
       <c r="X88">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="Y88">
-        <v>26</v>
-      </c>
-      <c r="Z88" s="2" cm="1">
-        <f t="array" ref="Z88">SUMPRODUCT((Tabelle2[Seite]=V88)*Tabelle2[Score_Gewichtet])</f>
-        <v>9.1999999999999975</v>
-      </c>
-      <c r="AA88" s="2"/>
-      <c r="AD88" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="89" spans="1:31" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>11</v>
       </c>
@@ -7530,40 +8049,46 @@
       <c r="K89">
         <v>0.5</v>
       </c>
-      <c r="R89">
+      <c r="M89">
         <v>89</v>
       </c>
-      <c r="S89">
-        <f t="shared" si="2"/>
+      <c r="N89">
+        <f>COUNTIF(B$2:B$1338, M89)</f>
         <v>8</v>
       </c>
-      <c r="T89">
-        <f t="shared" si="3"/>
+      <c r="O89">
+        <f>RANK(N89, $N$2:$N$116)</f>
         <v>75</v>
       </c>
-      <c r="V89">
+      <c r="Q89">
         <v>89</v>
       </c>
-      <c r="W89" s="1">
+      <c r="R89" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>88</v>
       </c>
+      <c r="S89">
+        <v>8</v>
+      </c>
+      <c r="T89">
+        <v>75</v>
+      </c>
+      <c r="U89" s="2" cm="1">
+        <f t="array" ref="U89">SUMPRODUCT((Tabelle2[Seite]=Q89)*Tabelle2[Score_Gewichtet])</f>
+        <v>6.75</v>
+      </c>
+      <c r="V89" s="2"/>
+      <c r="W89">
+        <v>0</v>
+      </c>
       <c r="X89">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y89">
-        <v>75</v>
-      </c>
-      <c r="Z89" s="2" cm="1">
-        <f t="array" ref="Z89">SUMPRODUCT((Tabelle2[Seite]=V89)*Tabelle2[Score_Gewichtet])</f>
-        <v>6.75</v>
-      </c>
-      <c r="AA89" s="2"/>
-      <c r="AD89" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="90" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>11</v>
       </c>
@@ -7597,40 +8122,46 @@
       <c r="K90">
         <v>1</v>
       </c>
-      <c r="R90">
+      <c r="M90">
         <v>90</v>
       </c>
-      <c r="S90">
-        <f t="shared" si="2"/>
+      <c r="N90">
+        <f>COUNTIF(B$2:B$1338, M90)</f>
         <v>9</v>
       </c>
-      <c r="T90">
-        <f t="shared" si="3"/>
+      <c r="O90">
+        <f>RANK(N90, $N$2:$N$116)</f>
         <v>61</v>
       </c>
-      <c r="V90">
+      <c r="Q90">
         <v>90</v>
       </c>
-      <c r="W90" s="1">
+      <c r="R90" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>89</v>
       </c>
+      <c r="S90">
+        <v>9</v>
+      </c>
+      <c r="T90">
+        <v>61</v>
+      </c>
+      <c r="U90" s="2" cm="1">
+        <f t="array" ref="U90">SUMPRODUCT((Tabelle2[Seite]=Q90)*Tabelle2[Score_Gewichtet])</f>
+        <v>15.7</v>
+      </c>
+      <c r="V90" s="2"/>
+      <c r="W90">
+        <v>0</v>
+      </c>
       <c r="X90">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y90">
-        <v>61</v>
-      </c>
-      <c r="Z90" s="2" cm="1">
-        <f t="array" ref="Z90">SUMPRODUCT((Tabelle2[Seite]=V90)*Tabelle2[Score_Gewichtet])</f>
-        <v>15.7</v>
-      </c>
-      <c r="AA90" s="2"/>
-      <c r="AD90" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="91" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>11</v>
       </c>
@@ -7664,40 +8195,46 @@
       <c r="K91">
         <v>0.5</v>
       </c>
-      <c r="R91">
+      <c r="M91">
         <v>91</v>
       </c>
-      <c r="S91">
-        <f t="shared" si="2"/>
+      <c r="N91">
+        <f>COUNTIF(B$2:B$1338, M91)</f>
         <v>7</v>
       </c>
-      <c r="T91">
-        <f t="shared" si="3"/>
+      <c r="O91">
+        <f>RANK(N91, $N$2:$N$116)</f>
         <v>87</v>
       </c>
-      <c r="V91">
+      <c r="Q91">
         <v>91</v>
       </c>
-      <c r="W91" s="1">
+      <c r="R91" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>90</v>
       </c>
+      <c r="S91">
+        <v>7</v>
+      </c>
+      <c r="T91">
+        <v>87</v>
+      </c>
+      <c r="U91" s="2" cm="1">
+        <f t="array" ref="U91">SUMPRODUCT((Tabelle2[Seite]=Q91)*Tabelle2[Score_Gewichtet])</f>
+        <v>13.049999999999999</v>
+      </c>
+      <c r="V91" s="2"/>
+      <c r="W91">
+        <v>0</v>
+      </c>
       <c r="X91">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y91">
-        <v>87</v>
-      </c>
-      <c r="Z91" s="2" cm="1">
-        <f t="array" ref="Z91">SUMPRODUCT((Tabelle2[Seite]=V91)*Tabelle2[Score_Gewichtet])</f>
-        <v>13.049999999999999</v>
-      </c>
-      <c r="AA91" s="2"/>
-      <c r="AD91" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="92" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>11</v>
       </c>
@@ -7731,40 +8268,46 @@
       <c r="K92">
         <v>0.2</v>
       </c>
-      <c r="R92">
+      <c r="M92">
         <v>92</v>
       </c>
-      <c r="S92">
-        <f t="shared" si="2"/>
+      <c r="N92">
+        <f>COUNTIF(B$2:B$1338, M92)</f>
         <v>16</v>
       </c>
-      <c r="T92">
-        <f t="shared" si="3"/>
+      <c r="O92">
+        <f>RANK(N92, $N$2:$N$116)</f>
         <v>21</v>
       </c>
-      <c r="V92">
+      <c r="Q92">
         <v>92</v>
       </c>
-      <c r="W92" s="1">
+      <c r="R92" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>91</v>
       </c>
+      <c r="S92">
+        <v>16</v>
+      </c>
+      <c r="T92">
+        <v>21</v>
+      </c>
+      <c r="U92" s="2" cm="1">
+        <f t="array" ref="U92">SUMPRODUCT((Tabelle2[Seite]=Q92)*Tabelle2[Score_Gewichtet])</f>
+        <v>14.049999999999999</v>
+      </c>
+      <c r="V92" s="2"/>
+      <c r="W92">
+        <v>0</v>
+      </c>
       <c r="X92">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="Y92">
-        <v>21</v>
-      </c>
-      <c r="Z92" s="2" cm="1">
-        <f t="array" ref="Z92">SUMPRODUCT((Tabelle2[Seite]=V92)*Tabelle2[Score_Gewichtet])</f>
-        <v>14.049999999999999</v>
-      </c>
-      <c r="AA92" s="2"/>
-      <c r="AD92" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="93" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>11</v>
       </c>
@@ -7798,40 +8341,46 @@
       <c r="K93">
         <v>1.2</v>
       </c>
-      <c r="R93">
+      <c r="M93">
         <v>93</v>
       </c>
-      <c r="S93">
-        <f t="shared" si="2"/>
+      <c r="N93">
+        <f>COUNTIF(B$2:B$1338, M93)</f>
         <v>7</v>
       </c>
-      <c r="T93">
-        <f t="shared" si="3"/>
+      <c r="O93">
+        <f>RANK(N93, $N$2:$N$116)</f>
         <v>87</v>
       </c>
-      <c r="V93">
+      <c r="Q93">
         <v>93</v>
       </c>
-      <c r="W93" s="1">
+      <c r="R93" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>92</v>
       </c>
+      <c r="S93">
+        <v>7</v>
+      </c>
+      <c r="T93">
+        <v>87</v>
+      </c>
+      <c r="U93" s="2" cm="1">
+        <f t="array" ref="U93">SUMPRODUCT((Tabelle2[Seite]=Q93)*Tabelle2[Score_Gewichtet])</f>
+        <v>11.6</v>
+      </c>
+      <c r="V93" s="2"/>
+      <c r="W93">
+        <v>0</v>
+      </c>
       <c r="X93">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y93">
-        <v>87</v>
-      </c>
-      <c r="Z93" s="2" cm="1">
-        <f t="array" ref="Z93">SUMPRODUCT((Tabelle2[Seite]=V93)*Tabelle2[Score_Gewichtet])</f>
-        <v>11.6</v>
-      </c>
-      <c r="AA93" s="2"/>
-      <c r="AD93" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="94" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>11</v>
       </c>
@@ -7865,40 +8414,46 @@
       <c r="K94">
         <v>1.1000000000000001</v>
       </c>
-      <c r="R94">
+      <c r="M94">
         <v>94</v>
       </c>
-      <c r="S94">
-        <f t="shared" si="2"/>
+      <c r="N94">
+        <f>COUNTIF(B$2:B$1338, M94)</f>
         <v>6</v>
       </c>
-      <c r="T94">
-        <f t="shared" si="3"/>
+      <c r="O94">
+        <f>RANK(N94, $N$2:$N$116)</f>
         <v>95</v>
       </c>
-      <c r="V94">
+      <c r="Q94">
         <v>94</v>
       </c>
-      <c r="W94" s="1">
+      <c r="R94" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>93</v>
       </c>
+      <c r="S94">
+        <v>6</v>
+      </c>
+      <c r="T94">
+        <v>95</v>
+      </c>
+      <c r="U94" s="2" cm="1">
+        <f t="array" ref="U94">SUMPRODUCT((Tabelle2[Seite]=Q94)*Tabelle2[Score_Gewichtet])</f>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="V94" s="2"/>
+      <c r="W94">
+        <v>0</v>
+      </c>
       <c r="X94">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y94">
-        <v>95</v>
-      </c>
-      <c r="Z94" s="2" cm="1">
-        <f t="array" ref="Z94">SUMPRODUCT((Tabelle2[Seite]=V94)*Tabelle2[Score_Gewichtet])</f>
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="AA94" s="2"/>
-      <c r="AD94" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="95" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>11</v>
       </c>
@@ -7932,40 +8487,46 @@
       <c r="K95">
         <v>2</v>
       </c>
-      <c r="R95">
+      <c r="M95">
         <v>95</v>
       </c>
-      <c r="S95">
-        <f t="shared" si="2"/>
+      <c r="N95">
+        <f>COUNTIF(B$2:B$1338, M95)</f>
         <v>12</v>
       </c>
-      <c r="T95">
-        <f t="shared" si="3"/>
+      <c r="O95">
+        <f>RANK(N95, $N$2:$N$116)</f>
         <v>39</v>
       </c>
-      <c r="V95">
+      <c r="Q95">
         <v>95</v>
       </c>
-      <c r="W95" s="1">
+      <c r="R95" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>94</v>
       </c>
+      <c r="S95">
+        <v>12</v>
+      </c>
+      <c r="T95">
+        <v>39</v>
+      </c>
+      <c r="U95" s="2" cm="1">
+        <f t="array" ref="U95">SUMPRODUCT((Tabelle2[Seite]=Q95)*Tabelle2[Score_Gewichtet])</f>
+        <v>11.299999999999999</v>
+      </c>
+      <c r="V95" s="2"/>
+      <c r="W95">
+        <v>0</v>
+      </c>
       <c r="X95">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Y95">
-        <v>39</v>
-      </c>
-      <c r="Z95" s="2" cm="1">
-        <f t="array" ref="Z95">SUMPRODUCT((Tabelle2[Seite]=V95)*Tabelle2[Score_Gewichtet])</f>
-        <v>11.299999999999999</v>
-      </c>
-      <c r="AA95" s="2"/>
-      <c r="AD95" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="96" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>11</v>
       </c>
@@ -7999,40 +8560,46 @@
       <c r="K96">
         <v>0.5</v>
       </c>
-      <c r="R96">
+      <c r="M96">
         <v>96</v>
       </c>
-      <c r="S96">
-        <f t="shared" si="2"/>
+      <c r="N96">
+        <f>COUNTIF(B$2:B$1338, M96)</f>
         <v>5</v>
       </c>
-      <c r="T96">
-        <f t="shared" si="3"/>
+      <c r="O96">
+        <f>RANK(N96, $N$2:$N$116)</f>
         <v>100</v>
       </c>
-      <c r="V96">
+      <c r="Q96">
         <v>96</v>
       </c>
-      <c r="W96" s="1">
+      <c r="R96" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>95</v>
       </c>
+      <c r="S96">
+        <v>5</v>
+      </c>
+      <c r="T96">
+        <v>100</v>
+      </c>
+      <c r="U96" s="2" cm="1">
+        <f t="array" ref="U96">SUMPRODUCT((Tabelle2[Seite]=Q96)*Tabelle2[Score_Gewichtet])</f>
+        <v>4.5</v>
+      </c>
+      <c r="V96" s="2"/>
+      <c r="W96">
+        <v>0</v>
+      </c>
       <c r="X96">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y96">
-        <v>100</v>
-      </c>
-      <c r="Z96" s="2" cm="1">
-        <f t="array" ref="Z96">SUMPRODUCT((Tabelle2[Seite]=V96)*Tabelle2[Score_Gewichtet])</f>
-        <v>4.5</v>
-      </c>
-      <c r="AA96" s="2"/>
-      <c r="AD96" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="97" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>11</v>
       </c>
@@ -8066,40 +8633,46 @@
       <c r="K97">
         <v>1</v>
       </c>
-      <c r="R97">
+      <c r="M97">
         <v>97</v>
       </c>
-      <c r="S97">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-      <c r="T97">
-        <f t="shared" si="3"/>
+      <c r="N97">
+        <f>COUNTIF(B$2:B$1338, M97)</f>
+        <v>11</v>
+      </c>
+      <c r="O97">
+        <f>RANK(N97, $N$2:$N$116)</f>
         <v>47</v>
       </c>
-      <c r="V97">
+      <c r="Q97">
         <v>97</v>
       </c>
-      <c r="W97" s="1">
+      <c r="R97" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>96</v>
       </c>
+      <c r="S97">
+        <v>11</v>
+      </c>
+      <c r="T97">
+        <v>47</v>
+      </c>
+      <c r="U97" s="2" cm="1">
+        <f t="array" ref="U97">SUMPRODUCT((Tabelle2[Seite]=Q97)*Tabelle2[Score_Gewichtet])</f>
+        <v>8.9499999999999993</v>
+      </c>
+      <c r="V97" s="2"/>
+      <c r="W97">
+        <v>0</v>
+      </c>
       <c r="X97">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y97">
-        <v>47</v>
-      </c>
-      <c r="Z97" s="2" cm="1">
-        <f t="array" ref="Z97">SUMPRODUCT((Tabelle2[Seite]=V97)*Tabelle2[Score_Gewichtet])</f>
-        <v>8.9499999999999993</v>
-      </c>
-      <c r="AA97" s="2"/>
-      <c r="AD97" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="98" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>11</v>
       </c>
@@ -8133,40 +8706,46 @@
       <c r="K98">
         <v>1</v>
       </c>
-      <c r="R98">
+      <c r="M98">
         <v>98</v>
       </c>
-      <c r="S98">
-        <f t="shared" si="2"/>
+      <c r="N98">
+        <f>COUNTIF(B$2:B$1338, M98)</f>
         <v>14</v>
       </c>
-      <c r="T98">
-        <f t="shared" si="3"/>
+      <c r="O98">
+        <f>RANK(N98, $N$2:$N$116)</f>
         <v>31</v>
       </c>
-      <c r="V98">
+      <c r="Q98">
         <v>98</v>
       </c>
-      <c r="W98" s="1">
+      <c r="R98" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>97</v>
       </c>
+      <c r="S98">
+        <v>14</v>
+      </c>
+      <c r="T98">
+        <v>31</v>
+      </c>
+      <c r="U98" s="2" cm="1">
+        <f t="array" ref="U98">SUMPRODUCT((Tabelle2[Seite]=Q98)*Tabelle2[Score_Gewichtet])</f>
+        <v>16.949999999999996</v>
+      </c>
+      <c r="V98" s="2"/>
+      <c r="W98">
+        <v>0</v>
+      </c>
       <c r="X98">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Y98">
-        <v>31</v>
-      </c>
-      <c r="Z98" s="2" cm="1">
-        <f t="array" ref="Z98">SUMPRODUCT((Tabelle2[Seite]=V98)*Tabelle2[Score_Gewichtet])</f>
-        <v>16.949999999999996</v>
-      </c>
-      <c r="AA98" s="2"/>
-      <c r="AD98" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="99" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>11</v>
       </c>
@@ -8200,576 +8779,646 @@
       <c r="K99">
         <v>0.6</v>
       </c>
-      <c r="R99">
+      <c r="M99">
         <v>103</v>
       </c>
+      <c r="N99">
+        <f>COUNTIF(B$2:B$1338, M99)</f>
+        <v>15</v>
+      </c>
+      <c r="O99">
+        <f>RANK(N99, $N$2:$N$116)</f>
+        <v>26</v>
+      </c>
+      <c r="Q99">
+        <v>99</v>
+      </c>
+      <c r="R99" s="1">
+        <f>Tabelle3[[#This Row],[Seite]]-1</f>
+        <v>98</v>
+      </c>
       <c r="S99">
-        <f t="shared" si="2"/>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="T99">
-        <f t="shared" si="3"/>
-        <v>26</v>
-      </c>
-      <c r="V99">
+        <v>104</v>
+      </c>
+      <c r="U99" s="2" cm="1">
+        <f t="array" ref="U99">SUMPRODUCT((Tabelle2[Seite]=Q99)*Tabelle2[Score_Gewichtet])</f>
+        <v>0</v>
+      </c>
+      <c r="V99" s="2"/>
+      <c r="W99">
+        <v>0</v>
+      </c>
+      <c r="X99">
+        <v>1</v>
+      </c>
+      <c r="Y99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>11</v>
+      </c>
+      <c r="B100">
+        <v>11</v>
+      </c>
+      <c r="C100" t="s">
+        <v>42</v>
+      </c>
+      <c r="D100" t="s">
+        <v>13</v>
+      </c>
+      <c r="E100" t="s">
+        <v>70</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>1</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+      <c r="J100">
+        <v>2</v>
+      </c>
+      <c r="K100">
+        <v>0.7</v>
+      </c>
+      <c r="M100">
+        <v>104</v>
+      </c>
+      <c r="N100">
+        <f>COUNTIF(B$2:B$1338, M100)</f>
+        <v>21</v>
+      </c>
+      <c r="O100">
+        <f>RANK(N100, $N$2:$N$116)</f>
+        <v>10</v>
+      </c>
+      <c r="Q100">
+        <v>100</v>
+      </c>
+      <c r="R100" s="1">
+        <f>Tabelle3[[#This Row],[Seite]]-1</f>
+        <v>99</v>
+      </c>
+      <c r="S100">
+        <v>0</v>
+      </c>
+      <c r="T100">
+        <v>104</v>
+      </c>
+      <c r="U100" s="2" cm="1">
+        <f t="array" ref="U100">SUMPRODUCT((Tabelle2[Seite]=Q100)*Tabelle2[Score_Gewichtet])</f>
+        <v>0</v>
+      </c>
+      <c r="V100" s="2"/>
+      <c r="W100">
+        <v>0</v>
+      </c>
+      <c r="X100">
+        <v>1</v>
+      </c>
+      <c r="Y100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>11</v>
+      </c>
+      <c r="B101">
+        <v>11</v>
+      </c>
+      <c r="C101" t="s">
+        <v>42</v>
+      </c>
+      <c r="D101" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" t="s">
+        <v>52</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>1</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>1</v>
+      </c>
+      <c r="K101">
+        <v>0.5</v>
+      </c>
+      <c r="M101">
+        <v>105</v>
+      </c>
+      <c r="N101">
+        <f>COUNTIF(B$2:B$1338, M101)</f>
+        <v>20</v>
+      </c>
+      <c r="O101">
+        <f>RANK(N101, $N$2:$N$116)</f>
+        <v>13</v>
+      </c>
+      <c r="Q101">
+        <v>101</v>
+      </c>
+      <c r="R101" s="1">
+        <f>Tabelle3[[#This Row],[Seite]]-1</f>
+        <v>100</v>
+      </c>
+      <c r="S101">
+        <v>0</v>
+      </c>
+      <c r="T101">
+        <v>104</v>
+      </c>
+      <c r="U101" s="2" cm="1">
+        <f t="array" ref="U101">SUMPRODUCT((Tabelle2[Seite]=Q101)*Tabelle2[Score_Gewichtet])</f>
+        <v>0</v>
+      </c>
+      <c r="V101" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="W101">
+        <v>1</v>
+      </c>
+      <c r="X101">
+        <v>2</v>
+      </c>
+      <c r="Y101">
+        <v>2</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="102" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>11</v>
+      </c>
+      <c r="B102">
+        <v>12</v>
+      </c>
+      <c r="C102" t="s">
+        <v>20</v>
+      </c>
+      <c r="D102" t="s">
+        <v>18</v>
+      </c>
+      <c r="E102" t="s">
+        <v>71</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>0</v>
+      </c>
+      <c r="H102">
+        <v>1</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
+      <c r="K102">
+        <v>0.6</v>
+      </c>
+      <c r="M102">
+        <v>106</v>
+      </c>
+      <c r="N102">
+        <f>COUNTIF(B$2:B$1338, M102)</f>
+        <v>14</v>
+      </c>
+      <c r="O102">
+        <f>RANK(N102, $N$2:$N$116)</f>
+        <v>31</v>
+      </c>
+      <c r="Q102">
+        <v>102</v>
+      </c>
+      <c r="R102" s="1">
+        <f>Tabelle3[[#This Row],[Seite]]-1</f>
+        <v>101</v>
+      </c>
+      <c r="S102">
+        <v>0</v>
+      </c>
+      <c r="T102">
+        <v>104</v>
+      </c>
+      <c r="U102" s="2" cm="1">
+        <f t="array" ref="U102">SUMPRODUCT((Tabelle2[Seite]=Q102)*Tabelle2[Score_Gewichtet])</f>
+        <v>0</v>
+      </c>
+      <c r="V102" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="W102">
+        <v>1</v>
+      </c>
+      <c r="X102">
+        <v>2</v>
+      </c>
+      <c r="Y102">
+        <v>2</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="103" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>11</v>
+      </c>
+      <c r="B103">
+        <v>12</v>
+      </c>
+      <c r="C103" t="s">
+        <v>20</v>
+      </c>
+      <c r="D103" t="s">
+        <v>13</v>
+      </c>
+      <c r="E103" t="s">
+        <v>72</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>1</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>1</v>
+      </c>
+      <c r="K103">
+        <v>0.75</v>
+      </c>
+      <c r="M103">
+        <v>107</v>
+      </c>
+      <c r="N103">
+        <f>COUNTIF(B$2:B$1338, M103)</f>
+        <v>4</v>
+      </c>
+      <c r="O103">
+        <f>RANK(N103, $N$2:$N$116)</f>
+        <v>104</v>
+      </c>
+      <c r="Q103">
         <v>103</v>
       </c>
-      <c r="W99" s="1">
+      <c r="R103" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>102</v>
       </c>
-      <c r="X99">
+      <c r="S103">
         <v>15</v>
       </c>
-      <c r="Y99">
+      <c r="T103">
         <v>26</v>
       </c>
-      <c r="Z99" s="2" cm="1">
-        <f t="array" ref="Z99">SUMPRODUCT((Tabelle2[Seite]=V99)*Tabelle2[Score_Gewichtet])</f>
+      <c r="U103" s="2" cm="1">
+        <f t="array" ref="U103">SUMPRODUCT((Tabelle2[Seite]=Q103)*Tabelle2[Score_Gewichtet])</f>
         <v>21.5</v>
       </c>
-      <c r="AA99" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="AB99" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE99">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="100" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A100" t="s">
-        <v>11</v>
-      </c>
-      <c r="B100">
-        <v>11</v>
-      </c>
-      <c r="C100" t="s">
-        <v>42</v>
-      </c>
-      <c r="D100" t="s">
-        <v>13</v>
-      </c>
-      <c r="E100" t="s">
-        <v>70</v>
-      </c>
-      <c r="F100">
-        <v>0</v>
-      </c>
-      <c r="G100">
-        <v>0</v>
-      </c>
-      <c r="H100">
-        <v>1</v>
-      </c>
-      <c r="I100">
-        <v>1</v>
-      </c>
-      <c r="J100">
-        <v>2</v>
-      </c>
-      <c r="K100">
-        <v>0.7</v>
-      </c>
-      <c r="R100">
+      <c r="V103" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="W103">
+        <v>1</v>
+      </c>
+      <c r="X103">
+        <v>2</v>
+      </c>
+      <c r="Y103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>11</v>
+      </c>
+      <c r="B104">
+        <v>12</v>
+      </c>
+      <c r="C104" t="s">
+        <v>20</v>
+      </c>
+      <c r="D104" t="s">
+        <v>13</v>
+      </c>
+      <c r="E104" t="s">
+        <v>73</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>1</v>
+      </c>
+      <c r="K104">
+        <v>0.75</v>
+      </c>
+      <c r="M104">
+        <v>108</v>
+      </c>
+      <c r="N104">
+        <f>COUNTIF(B$2:B$1338, M104)</f>
+        <v>13</v>
+      </c>
+      <c r="O104">
+        <f>RANK(N104, $N$2:$N$116)</f>
+        <v>34</v>
+      </c>
+      <c r="Q104">
         <v>104</v>
       </c>
-      <c r="S100">
-        <f t="shared" si="2"/>
-        <v>21</v>
-      </c>
-      <c r="T100">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
-      <c r="V100">
-        <v>104</v>
-      </c>
-      <c r="W100" s="1">
+      <c r="R104" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>103</v>
       </c>
-      <c r="X100">
+      <c r="S104">
         <v>21</v>
       </c>
-      <c r="Y100">
+      <c r="T104">
         <v>10</v>
       </c>
-      <c r="Z100" s="2" cm="1">
-        <f t="array" ref="Z100">SUMPRODUCT((Tabelle2[Seite]=V100)*Tabelle2[Score_Gewichtet])</f>
+      <c r="U104" s="2" cm="1">
+        <f t="array" ref="U104">SUMPRODUCT((Tabelle2[Seite]=Q104)*Tabelle2[Score_Gewichtet])</f>
         <v>17</v>
       </c>
-      <c r="AA100" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="AB100" t="s">
-        <v>151</v>
-      </c>
-      <c r="AE100">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
-        <v>11</v>
-      </c>
-      <c r="B101">
-        <v>11</v>
-      </c>
-      <c r="C101" t="s">
-        <v>42</v>
-      </c>
-      <c r="D101" t="s">
-        <v>13</v>
-      </c>
-      <c r="E101" t="s">
-        <v>52</v>
-      </c>
-      <c r="F101">
-        <v>0</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1</v>
-      </c>
-      <c r="K101">
+      <c r="V104" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="W104">
+        <v>1</v>
+      </c>
+      <c r="X104">
+        <v>2</v>
+      </c>
+      <c r="Y104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>11</v>
+      </c>
+      <c r="B105">
+        <v>12</v>
+      </c>
+      <c r="C105" t="s">
+        <v>20</v>
+      </c>
+      <c r="D105" t="s">
+        <v>13</v>
+      </c>
+      <c r="E105" t="s">
+        <v>33</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <v>1</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>1</v>
+      </c>
+      <c r="K105">
         <v>0.5</v>
       </c>
-      <c r="R101">
+      <c r="M105">
+        <v>109</v>
+      </c>
+      <c r="N105">
+        <f>COUNTIF(B$2:B$1338, M105)</f>
+        <v>5</v>
+      </c>
+      <c r="O105">
+        <f>RANK(N105, $N$2:$N$116)</f>
+        <v>100</v>
+      </c>
+      <c r="Q105">
         <v>105</v>
       </c>
-      <c r="S101">
-        <f t="shared" si="2"/>
-        <v>20</v>
-      </c>
-      <c r="T101">
-        <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
-      <c r="V101">
-        <v>105</v>
-      </c>
-      <c r="W101" s="1">
+      <c r="R105" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>104</v>
       </c>
-      <c r="X101">
+      <c r="S105">
         <v>20</v>
       </c>
-      <c r="Y101">
-        <v>13</v>
-      </c>
-      <c r="Z101" s="2" cm="1">
-        <f t="array" ref="Z101">SUMPRODUCT((Tabelle2[Seite]=V101)*Tabelle2[Score_Gewichtet])</f>
+      <c r="T105">
+        <v>13</v>
+      </c>
+      <c r="U105" s="2" cm="1">
+        <f t="array" ref="U105">SUMPRODUCT((Tabelle2[Seite]=Q105)*Tabelle2[Score_Gewichtet])</f>
         <v>21.55</v>
       </c>
-      <c r="AA101" s="2"/>
-      <c r="AD101" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="102" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
-        <v>11</v>
-      </c>
-      <c r="B102">
+      <c r="V105" s="2"/>
+      <c r="W105">
+        <v>0</v>
+      </c>
+      <c r="X105">
+        <v>1</v>
+      </c>
+      <c r="Y105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>11</v>
+      </c>
+      <c r="B106">
         <v>12</v>
       </c>
-      <c r="C102" t="s">
-        <v>20</v>
-      </c>
-      <c r="D102" t="s">
-        <v>18</v>
-      </c>
-      <c r="E102" t="s">
-        <v>71</v>
-      </c>
-      <c r="F102">
-        <v>0</v>
-      </c>
-      <c r="G102">
-        <v>0</v>
-      </c>
-      <c r="H102">
-        <v>1</v>
-      </c>
-      <c r="I102">
-        <v>0</v>
-      </c>
-      <c r="J102">
-        <v>1</v>
-      </c>
-      <c r="K102">
-        <v>0.6</v>
-      </c>
-      <c r="R102">
+      <c r="C106" t="s">
+        <v>12</v>
+      </c>
+      <c r="D106" t="s">
+        <v>13</v>
+      </c>
+      <c r="E106" t="s">
+        <v>14</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106">
+        <v>1</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>1</v>
+      </c>
+      <c r="K106">
+        <v>0.5</v>
+      </c>
+      <c r="M106">
+        <v>110</v>
+      </c>
+      <c r="N106">
+        <f>COUNTIF(B$2:B$1338, M106)</f>
+        <v>9</v>
+      </c>
+      <c r="O106">
+        <f>RANK(N106, $N$2:$N$116)</f>
+        <v>61</v>
+      </c>
+      <c r="Q106">
         <v>106</v>
       </c>
-      <c r="S102">
-        <f t="shared" si="2"/>
-        <v>14</v>
-      </c>
-      <c r="T102">
-        <f t="shared" si="3"/>
-        <v>31</v>
-      </c>
-      <c r="V102">
-        <v>106</v>
-      </c>
-      <c r="W102" s="1">
+      <c r="R106" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>105</v>
       </c>
-      <c r="X102">
+      <c r="S106">
         <v>14</v>
       </c>
-      <c r="Y102">
+      <c r="T106">
         <v>31</v>
       </c>
-      <c r="Z102" s="2" cm="1">
-        <f t="array" ref="Z102">SUMPRODUCT((Tabelle2[Seite]=V102)*Tabelle2[Score_Gewichtet])</f>
+      <c r="U106" s="2" cm="1">
+        <f t="array" ref="U106">SUMPRODUCT((Tabelle2[Seite]=Q106)*Tabelle2[Score_Gewichtet])</f>
         <v>10.299999999999999</v>
       </c>
-      <c r="AA102" s="2"/>
-      <c r="AD102" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="103" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A103" t="s">
-        <v>11</v>
-      </c>
-      <c r="B103">
+      <c r="V106" s="2"/>
+      <c r="W106">
+        <v>0</v>
+      </c>
+      <c r="X106">
+        <v>1</v>
+      </c>
+      <c r="Y106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>11</v>
+      </c>
+      <c r="B107">
         <v>12</v>
       </c>
-      <c r="C103" t="s">
-        <v>20</v>
-      </c>
-      <c r="D103" t="s">
-        <v>13</v>
-      </c>
-      <c r="E103" t="s">
-        <v>72</v>
-      </c>
-      <c r="F103">
-        <v>0</v>
-      </c>
-      <c r="G103">
-        <v>1</v>
-      </c>
-      <c r="H103">
-        <v>0</v>
-      </c>
-      <c r="I103">
-        <v>0</v>
-      </c>
-      <c r="J103">
-        <v>1</v>
-      </c>
-      <c r="K103">
-        <v>0.75</v>
-      </c>
-      <c r="R103">
+      <c r="C107" t="s">
+        <v>12</v>
+      </c>
+      <c r="D107" t="s">
+        <v>13</v>
+      </c>
+      <c r="E107" t="s">
+        <v>74</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="G107">
+        <v>0</v>
+      </c>
+      <c r="H107">
+        <v>1</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>1</v>
+      </c>
+      <c r="K107">
+        <v>0.5</v>
+      </c>
+      <c r="M107">
+        <v>111</v>
+      </c>
+      <c r="N107">
+        <f>COUNTIF(B$2:B$1338, M107)</f>
+        <v>11</v>
+      </c>
+      <c r="O107">
+        <f>RANK(N107, $N$2:$N$116)</f>
+        <v>47</v>
+      </c>
+      <c r="Q107">
         <v>107</v>
       </c>
-      <c r="S103">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="T103">
-        <f t="shared" si="3"/>
-        <v>104</v>
-      </c>
-      <c r="V103">
-        <v>107</v>
-      </c>
-      <c r="W103" s="1">
+      <c r="R107" s="1">
         <f>Tabelle3[[#This Row],[Seite]]-1</f>
         <v>106</v>
       </c>
-      <c r="X103">
+      <c r="S107">
         <v>4</v>
       </c>
-      <c r="Y103">
+      <c r="T107">
         <v>104</v>
       </c>
-      <c r="Z103" s="2" cm="1">
-        <f t="array" ref="Z103">SUMPRODUCT((Tabelle2[Seite]=V103)*Tabelle2[Score_Gewichtet])</f>
+      <c r="U107" s="2" cm="1">
+        <f t="array" ref="U107">SUMPRODUCT((Tabelle2[Seite]=Q107)*Tabelle2[Score_Gewichtet])</f>
         <v>3.4000000000000004</v>
       </c>
-      <c r="AA103" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="AD103" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="104" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A104" t="s">
-        <v>11</v>
-      </c>
-      <c r="B104">
-        <v>12</v>
-      </c>
-      <c r="C104" t="s">
-        <v>20</v>
-      </c>
-      <c r="D104" t="s">
-        <v>13</v>
-      </c>
-      <c r="E104" t="s">
-        <v>73</v>
-      </c>
-      <c r="F104">
-        <v>0</v>
-      </c>
-      <c r="G104">
-        <v>1</v>
-      </c>
-      <c r="H104">
-        <v>0</v>
-      </c>
-      <c r="I104">
-        <v>0</v>
-      </c>
-      <c r="J104">
-        <v>1</v>
-      </c>
-      <c r="K104">
-        <v>0.75</v>
-      </c>
-      <c r="R104">
-        <v>108</v>
-      </c>
-      <c r="S104">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-      <c r="T104">
-        <f t="shared" si="3"/>
-        <v>34</v>
-      </c>
-      <c r="V104">
-        <v>108</v>
-      </c>
-      <c r="W104" s="1">
-        <f>Tabelle3[[#This Row],[Seite]]-1</f>
-        <v>107</v>
-      </c>
-      <c r="X104">
-        <v>13</v>
-      </c>
-      <c r="Y104">
-        <v>34</v>
-      </c>
-      <c r="Z104" s="2" cm="1">
-        <f t="array" ref="Z104">SUMPRODUCT((Tabelle2[Seite]=V104)*Tabelle2[Score_Gewichtet])</f>
-        <v>8.5499999999999989</v>
-      </c>
-      <c r="AA104" s="2"/>
-    </row>
-    <row r="105" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A105" t="s">
-        <v>11</v>
-      </c>
-      <c r="B105">
-        <v>12</v>
-      </c>
-      <c r="C105" t="s">
-        <v>20</v>
-      </c>
-      <c r="D105" t="s">
-        <v>13</v>
-      </c>
-      <c r="E105" t="s">
-        <v>33</v>
-      </c>
-      <c r="F105">
-        <v>0</v>
-      </c>
-      <c r="G105">
-        <v>0</v>
-      </c>
-      <c r="H105">
-        <v>1</v>
-      </c>
-      <c r="I105">
-        <v>0</v>
-      </c>
-      <c r="J105">
-        <v>1</v>
-      </c>
-      <c r="K105">
-        <v>0.5</v>
-      </c>
-      <c r="R105">
-        <v>109</v>
-      </c>
-      <c r="S105">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="T105">
-        <f t="shared" si="3"/>
-        <v>100</v>
-      </c>
-      <c r="V105">
-        <v>109</v>
-      </c>
-      <c r="W105" s="1">
-        <f>Tabelle3[[#This Row],[Seite]]-1</f>
-        <v>108</v>
-      </c>
-      <c r="X105">
-        <v>5</v>
-      </c>
-      <c r="Y105">
-        <v>100</v>
-      </c>
-      <c r="Z105" s="2" cm="1">
-        <f t="array" ref="Z105">SUMPRODUCT((Tabelle2[Seite]=V105)*Tabelle2[Score_Gewichtet])</f>
-        <v>6.1</v>
-      </c>
-      <c r="AA105" s="2"/>
-    </row>
-    <row r="106" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A106" t="s">
-        <v>11</v>
-      </c>
-      <c r="B106">
-        <v>12</v>
-      </c>
-      <c r="C106" t="s">
-        <v>12</v>
-      </c>
-      <c r="D106" t="s">
-        <v>13</v>
-      </c>
-      <c r="E106" t="s">
-        <v>14</v>
-      </c>
-      <c r="F106">
-        <v>0</v>
-      </c>
-      <c r="G106">
-        <v>0</v>
-      </c>
-      <c r="H106">
-        <v>1</v>
-      </c>
-      <c r="I106">
-        <v>0</v>
-      </c>
-      <c r="J106">
-        <v>1</v>
-      </c>
-      <c r="K106">
-        <v>0.5</v>
-      </c>
-      <c r="R106">
-        <v>110</v>
-      </c>
-      <c r="S106">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="T106">
-        <f t="shared" si="3"/>
-        <v>61</v>
-      </c>
-      <c r="V106">
-        <v>110</v>
-      </c>
-      <c r="W106" s="1">
-        <f>Tabelle3[[#This Row],[Seite]]-1</f>
-        <v>109</v>
-      </c>
-      <c r="X106">
-        <v>9</v>
-      </c>
-      <c r="Y106">
-        <v>61</v>
-      </c>
-      <c r="Z106" s="2" cm="1">
-        <f t="array" ref="Z106">SUMPRODUCT((Tabelle2[Seite]=V106)*Tabelle2[Score_Gewichtet])</f>
-        <v>7.15</v>
-      </c>
-      <c r="AA106" s="2"/>
-    </row>
-    <row r="107" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A107" t="s">
-        <v>11</v>
-      </c>
-      <c r="B107">
-        <v>12</v>
-      </c>
-      <c r="C107" t="s">
-        <v>12</v>
-      </c>
-      <c r="D107" t="s">
-        <v>13</v>
-      </c>
-      <c r="E107" t="s">
-        <v>74</v>
-      </c>
-      <c r="F107">
-        <v>0</v>
-      </c>
-      <c r="G107">
-        <v>0</v>
-      </c>
-      <c r="H107">
-        <v>1</v>
-      </c>
-      <c r="I107">
-        <v>0</v>
-      </c>
-      <c r="J107">
-        <v>1</v>
-      </c>
-      <c r="K107">
-        <v>0.5</v>
-      </c>
-      <c r="R107">
-        <v>111</v>
-      </c>
-      <c r="S107">
-        <f t="shared" si="2"/>
-        <v>11</v>
-      </c>
-      <c r="T107">
-        <f t="shared" si="3"/>
-        <v>47</v>
-      </c>
-      <c r="V107">
-        <v>111</v>
-      </c>
-      <c r="W107" s="1">
-        <f>Tabelle3[[#This Row],[Seite]]-1</f>
-        <v>110</v>
+      <c r="V107" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="W107">
+        <v>0</v>
       </c>
       <c r="X107">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y107">
-        <v>47</v>
-      </c>
-      <c r="Z107" s="2" cm="1">
-        <f t="array" ref="Z107">SUMPRODUCT((Tabelle2[Seite]=V107)*Tabelle2[Score_Gewichtet])</f>
-        <v>18.45</v>
-      </c>
-      <c r="AA107" s="2"/>
-    </row>
-    <row r="108" spans="1:31" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>11</v>
       </c>
@@ -8803,37 +9452,20 @@
       <c r="K108">
         <v>0.5</v>
       </c>
-      <c r="R108">
+      <c r="M108">
         <v>112</v>
       </c>
-      <c r="S108">
-        <f t="shared" si="2"/>
+      <c r="N108">
+        <f>COUNTIF(B$2:B$1338, M108)</f>
         <v>6</v>
       </c>
-      <c r="T108">
-        <f t="shared" si="3"/>
+      <c r="O108">
+        <f>RANK(N108, $N$2:$N$116)</f>
         <v>95</v>
       </c>
-      <c r="V108">
-        <v>112</v>
-      </c>
-      <c r="W108" s="1">
-        <f>Tabelle3[[#This Row],[Seite]]-1</f>
-        <v>111</v>
-      </c>
-      <c r="X108">
-        <v>6</v>
-      </c>
-      <c r="Y108">
-        <v>95</v>
-      </c>
-      <c r="Z108" s="2" cm="1">
-        <f t="array" ref="Z108">SUMPRODUCT((Tabelle2[Seite]=V108)*Tabelle2[Score_Gewichtet])</f>
-        <v>1.35</v>
-      </c>
-      <c r="AA108" s="2"/>
-    </row>
-    <row r="109" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="W108" s="1"/>
+    </row>
+    <row r="109" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>11</v>
       </c>
@@ -8867,37 +9499,20 @@
       <c r="K109">
         <v>0.1</v>
       </c>
-      <c r="R109">
+      <c r="M109">
         <v>113</v>
       </c>
-      <c r="S109">
-        <f t="shared" si="2"/>
+      <c r="N109">
+        <f>COUNTIF(B$2:B$1338, M109)</f>
         <v>8</v>
       </c>
-      <c r="T109">
-        <f t="shared" si="3"/>
+      <c r="O109">
+        <f>RANK(N109, $N$2:$N$116)</f>
         <v>75</v>
       </c>
-      <c r="V109">
-        <v>113</v>
-      </c>
-      <c r="W109" s="1">
-        <f>Tabelle3[[#This Row],[Seite]]-1</f>
-        <v>112</v>
-      </c>
-      <c r="X109">
-        <v>8</v>
-      </c>
-      <c r="Y109">
-        <v>75</v>
-      </c>
-      <c r="Z109" s="2" cm="1">
-        <f t="array" ref="Z109">SUMPRODUCT((Tabelle2[Seite]=V109)*Tabelle2[Score_Gewichtet])</f>
-        <v>3.5</v>
-      </c>
-      <c r="AA109" s="2"/>
-    </row>
-    <row r="110" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="W109" s="1"/>
+    </row>
+    <row r="110" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>11</v>
       </c>
@@ -8931,37 +9546,20 @@
       <c r="K110">
         <v>0.5</v>
       </c>
-      <c r="R110">
+      <c r="M110">
         <v>114</v>
       </c>
-      <c r="S110">
-        <f t="shared" si="2"/>
+      <c r="N110">
+        <f>COUNTIF(B$2:B$1338, M110)</f>
         <v>7</v>
       </c>
-      <c r="T110">
-        <f t="shared" si="3"/>
+      <c r="O110">
+        <f>RANK(N110, $N$2:$N$116)</f>
         <v>87</v>
       </c>
-      <c r="V110">
-        <v>114</v>
-      </c>
-      <c r="W110" s="1">
-        <f>Tabelle3[[#This Row],[Seite]]-1</f>
-        <v>113</v>
-      </c>
-      <c r="X110">
-        <v>7</v>
-      </c>
-      <c r="Y110">
-        <v>87</v>
-      </c>
-      <c r="Z110" s="2" cm="1">
-        <f t="array" ref="Z110">SUMPRODUCT((Tabelle2[Seite]=V110)*Tabelle2[Score_Gewichtet])</f>
-        <v>8.25</v>
-      </c>
-      <c r="AA110" s="2"/>
-    </row>
-    <row r="111" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="W110" s="1"/>
+    </row>
+    <row r="111" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>11</v>
       </c>
@@ -8995,37 +9593,20 @@
       <c r="K111">
         <v>0.1</v>
       </c>
-      <c r="R111">
+      <c r="M111">
         <v>115</v>
       </c>
-      <c r="S111">
-        <f t="shared" si="2"/>
-        <v>13</v>
-      </c>
-      <c r="T111">
-        <f t="shared" si="3"/>
+      <c r="N111">
+        <f>COUNTIF(B$2:B$1338, M111)</f>
+        <v>13</v>
+      </c>
+      <c r="O111">
+        <f>RANK(N111, $N$2:$N$116)</f>
         <v>34</v>
       </c>
-      <c r="V111">
-        <v>115</v>
-      </c>
-      <c r="W111" s="1">
-        <f>Tabelle3[[#This Row],[Seite]]-1</f>
-        <v>114</v>
-      </c>
-      <c r="X111">
-        <v>13</v>
-      </c>
-      <c r="Y111">
-        <v>34</v>
-      </c>
-      <c r="Z111" s="2" cm="1">
-        <f t="array" ref="Z111">SUMPRODUCT((Tabelle2[Seite]=V111)*Tabelle2[Score_Gewichtet])</f>
-        <v>13.899999999999999</v>
-      </c>
-      <c r="AA111" s="2"/>
-    </row>
-    <row r="112" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="W111" s="1"/>
+    </row>
+    <row r="112" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>11</v>
       </c>
@@ -9059,37 +9640,20 @@
       <c r="K112">
         <v>0.75</v>
       </c>
-      <c r="R112">
+      <c r="M112">
         <v>116</v>
       </c>
-      <c r="S112">
-        <f t="shared" si="2"/>
+      <c r="N112">
+        <f>COUNTIF(B$2:B$1338, M112)</f>
         <v>8</v>
       </c>
-      <c r="T112">
-        <f t="shared" si="3"/>
+      <c r="O112">
+        <f>RANK(N112, $N$2:$N$116)</f>
         <v>75</v>
       </c>
-      <c r="V112">
-        <v>116</v>
-      </c>
-      <c r="W112" s="1">
-        <f>Tabelle3[[#This Row],[Seite]]-1</f>
-        <v>115</v>
-      </c>
-      <c r="X112">
-        <v>8</v>
-      </c>
-      <c r="Y112">
-        <v>75</v>
-      </c>
-      <c r="Z112" s="2" cm="1">
-        <f t="array" ref="Z112">SUMPRODUCT((Tabelle2[Seite]=V112)*Tabelle2[Score_Gewichtet])</f>
-        <v>4.8500000000000005</v>
-      </c>
-      <c r="AA112" s="2"/>
-    </row>
-    <row r="113" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="W112" s="1"/>
+    </row>
+    <row r="113" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>11</v>
       </c>
@@ -9123,37 +9687,20 @@
       <c r="K113">
         <v>0.5</v>
       </c>
-      <c r="R113">
+      <c r="M113">
         <v>117</v>
       </c>
-      <c r="S113">
-        <f t="shared" si="2"/>
+      <c r="N113">
+        <f>COUNTIF(B$2:B$1338, M113)</f>
         <v>7</v>
       </c>
-      <c r="T113">
-        <f t="shared" si="3"/>
+      <c r="O113">
+        <f>RANK(N113, $N$2:$N$116)</f>
         <v>87</v>
       </c>
-      <c r="V113">
-        <v>117</v>
-      </c>
-      <c r="W113" s="1">
-        <f>Tabelle3[[#This Row],[Seite]]-1</f>
-        <v>116</v>
-      </c>
-      <c r="X113">
-        <v>7</v>
-      </c>
-      <c r="Y113">
-        <v>87</v>
-      </c>
-      <c r="Z113" s="2" cm="1">
-        <f t="array" ref="Z113">SUMPRODUCT((Tabelle2[Seite]=V113)*Tabelle2[Score_Gewichtet])</f>
-        <v>6.6</v>
-      </c>
-      <c r="AA113" s="2"/>
-    </row>
-    <row r="114" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="W113" s="1"/>
+    </row>
+    <row r="114" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>11</v>
       </c>
@@ -9187,37 +9734,20 @@
       <c r="K114">
         <v>0.1</v>
       </c>
-      <c r="R114">
+      <c r="M114">
         <v>118</v>
       </c>
-      <c r="S114">
-        <f t="shared" si="2"/>
+      <c r="N114">
+        <f>COUNTIF(B$2:B$1338, M114)</f>
         <v>8</v>
       </c>
-      <c r="T114">
-        <f t="shared" si="3"/>
+      <c r="O114">
+        <f>RANK(N114, $N$2:$N$116)</f>
         <v>75</v>
       </c>
-      <c r="V114">
-        <v>118</v>
-      </c>
-      <c r="W114" s="3">
-        <f>Tabelle3[[#This Row],[Seite]]-1</f>
-        <v>117</v>
-      </c>
-      <c r="X114">
-        <v>8</v>
-      </c>
-      <c r="Y114">
-        <v>75</v>
-      </c>
-      <c r="Z114" s="2" cm="1">
-        <f t="array" ref="Z114">SUMPRODUCT((Tabelle2[Seite]=V114)*Tabelle2[Score_Gewichtet])</f>
-        <v>5.6</v>
-      </c>
-      <c r="AA114" s="2"/>
-    </row>
-    <row r="115" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="W114" s="1"/>
+    </row>
+    <row r="115" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>11</v>
       </c>
@@ -9251,37 +9781,20 @@
       <c r="K115">
         <v>0.1</v>
       </c>
-      <c r="R115">
+      <c r="M115">
         <v>120</v>
       </c>
-      <c r="S115">
-        <f t="shared" si="2"/>
+      <c r="N115">
+        <f>COUNTIF(B$2:B$1338, M115)</f>
         <v>36</v>
       </c>
-      <c r="T115">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="V115">
-        <v>120</v>
-      </c>
-      <c r="W115" s="3">
-        <f>Tabelle3[[#This Row],[Seite]]-1</f>
-        <v>119</v>
-      </c>
-      <c r="X115">
-        <v>36</v>
-      </c>
-      <c r="Y115">
-        <v>1</v>
-      </c>
-      <c r="Z115" s="2" cm="1">
-        <f t="array" ref="Z115">SUMPRODUCT((Tabelle2[Seite]=V115)*Tabelle2[Score_Gewichtet])</f>
-        <v>35.999999999999993</v>
-      </c>
-      <c r="AA115" s="2"/>
-    </row>
-    <row r="116" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="O115">
+        <f>RANK(N115, $N$2:$N$116)</f>
+        <v>1</v>
+      </c>
+      <c r="W115" s="1"/>
+    </row>
+    <row r="116" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>11</v>
       </c>
@@ -9315,37 +9828,20 @@
       <c r="K116">
         <v>0.6</v>
       </c>
-      <c r="R116">
+      <c r="M116">
         <v>121</v>
       </c>
-      <c r="S116">
-        <f t="shared" si="2"/>
+      <c r="N116">
+        <f>COUNTIF(B$2:B$1338, M116)</f>
         <v>7</v>
       </c>
-      <c r="T116">
-        <f t="shared" si="3"/>
+      <c r="O116">
+        <f>RANK(N116, $N$2:$N$116)</f>
         <v>87</v>
       </c>
-      <c r="V116">
-        <v>121</v>
-      </c>
-      <c r="W116" s="3">
-        <f>Tabelle3[[#This Row],[Seite]]-1</f>
-        <v>120</v>
-      </c>
-      <c r="X116">
-        <v>7</v>
-      </c>
-      <c r="Y116">
-        <v>87</v>
-      </c>
-      <c r="Z116" s="2" cm="1">
-        <f t="array" ref="Z116">SUMPRODUCT((Tabelle2[Seite]=V116)*Tabelle2[Score_Gewichtet])</f>
-        <v>7.4</v>
-      </c>
-      <c r="AA116" s="2"/>
-    </row>
-    <row r="117" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="W116" s="1"/>
+    </row>
+    <row r="117" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>11</v>
       </c>
@@ -9379,11 +9875,9 @@
       <c r="K117">
         <v>0.6</v>
       </c>
-      <c r="W117" s="3"/>
-      <c r="Z117" s="2"/>
-      <c r="AA117" s="2"/>
-    </row>
-    <row r="118" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="W117" s="1"/>
+    </row>
+    <row r="118" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>11</v>
       </c>
@@ -9418,10 +9912,8 @@
         <v>0.1</v>
       </c>
       <c r="W118" s="3"/>
-      <c r="Z118" s="2"/>
-      <c r="AA118" s="2"/>
-    </row>
-    <row r="119" spans="1:27" x14ac:dyDescent="0.2">
+    </row>
+    <row r="119" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>11</v>
       </c>
@@ -9455,8 +9947,9 @@
       <c r="K119">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="W119" s="3"/>
+    </row>
+    <row r="120" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>11</v>
       </c>
@@ -9490,8 +9983,9 @@
       <c r="K120">
         <v>1.5</v>
       </c>
-    </row>
-    <row r="121" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="W120" s="3"/>
+    </row>
+    <row r="121" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>11</v>
       </c>
@@ -9525,8 +10019,9 @@
       <c r="K121">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="122" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="W121" s="3"/>
+    </row>
+    <row r="122" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>11</v>
       </c>
@@ -9560,8 +10055,9 @@
       <c r="K122">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="123" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="W122" s="3"/>
+    </row>
+    <row r="123" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>11</v>
       </c>
@@ -9596,7 +10092,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="124" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>11</v>
       </c>
@@ -9631,7 +10127,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="125" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>11</v>
       </c>
@@ -9666,7 +10162,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="126" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>11</v>
       </c>
@@ -9701,7 +10197,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="127" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>11</v>
       </c>
@@ -9736,7 +10232,7 @@
         <v>3.35</v>
       </c>
     </row>
-    <row r="128" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>11</v>
       </c>
@@ -9771,7 +10267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>11</v>
       </c>
@@ -9806,7 +10302,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>11</v>
       </c>
@@ -9841,7 +10337,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>11</v>
       </c>
@@ -9876,7 +10372,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>11</v>
       </c>
@@ -9911,7 +10407,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>11</v>
       </c>
@@ -9946,7 +10442,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>11</v>
       </c>
@@ -9981,7 +10477,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>11</v>
       </c>
@@ -10016,7 +10512,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>11</v>
       </c>
@@ -10050,8 +10546,12 @@
       <c r="K136">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="U136" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="V136" s="2"/>
+    </row>
+    <row r="137" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>11</v>
       </c>
@@ -10085,8 +10585,22 @@
       <c r="K137">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="U137">
+        <v>3</v>
+      </c>
+      <c r="V137" t="s">
+        <v>28</v>
+      </c>
+      <c r="W137">
+        <f>COUNTIF(Tabelle3[Stufe BNE],U137)</f>
+        <v>0</v>
+      </c>
+      <c r="X137" s="4">
+        <f>W137/W$141</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>11</v>
       </c>
@@ -10120,8 +10634,22 @@
       <c r="K138">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="U138">
+        <v>2</v>
+      </c>
+      <c r="V138" t="s">
+        <v>18</v>
+      </c>
+      <c r="W138">
+        <f>COUNTIF(Tabelle3[Stufe BNE],U138)</f>
+        <v>4</v>
+      </c>
+      <c r="X138" s="4">
+        <f>W138/W$141</f>
+        <v>3.7735849056603772E-2</v>
+      </c>
+    </row>
+    <row r="139" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>11</v>
       </c>
@@ -10155,8 +10683,22 @@
       <c r="K139">
         <v>1</v>
       </c>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="U139">
+        <v>1</v>
+      </c>
+      <c r="V139" t="s">
+        <v>13</v>
+      </c>
+      <c r="W139">
+        <f>COUNTIF(Tabelle3[Stufe BNE],U139)</f>
+        <v>22</v>
+      </c>
+      <c r="X139" s="4">
+        <f>W139/W$141</f>
+        <v>0.20754716981132076</v>
+      </c>
+    </row>
+    <row r="140" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>11</v>
       </c>
@@ -10190,8 +10732,22 @@
       <c r="K140">
         <v>1</v>
       </c>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="U140">
+        <v>0</v>
+      </c>
+      <c r="V140" t="s">
+        <v>168</v>
+      </c>
+      <c r="W140">
+        <f>COUNTIF(Tabelle3[Stufe BNE],U140)</f>
+        <v>80</v>
+      </c>
+      <c r="X140" s="4">
+        <f>W140/W$141</f>
+        <v>0.75471698113207553</v>
+      </c>
+    </row>
+    <row r="141" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>11</v>
       </c>
@@ -10225,8 +10781,15 @@
       <c r="K141">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="V141" t="s">
+        <v>169</v>
+      </c>
+      <c r="W141">
+        <f>SUM(W137:W140)</f>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="142" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>11</v>
       </c>
@@ -10261,7 +10824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>11</v>
       </c>
@@ -10295,8 +10858,11 @@
       <c r="K143">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="U143" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="144" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>11</v>
       </c>
@@ -10330,8 +10896,22 @@
       <c r="K144">
         <v>1</v>
       </c>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="U144">
+        <v>3</v>
+      </c>
+      <c r="V144" t="s">
+        <v>28</v>
+      </c>
+      <c r="W144">
+        <f>COUNTIF(Tabelle3[Reflexionstiefe],U144)</f>
+        <v>0</v>
+      </c>
+      <c r="X144" s="4">
+        <f>W144/W$141</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>11</v>
       </c>
@@ -10365,8 +10945,22 @@
       <c r="K145">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="U145">
+        <v>2</v>
+      </c>
+      <c r="V145" t="s">
+        <v>18</v>
+      </c>
+      <c r="W145">
+        <f>COUNTIF(Tabelle3[Reflexionstiefe],U145)</f>
+        <v>14</v>
+      </c>
+      <c r="X145" s="4">
+        <f t="shared" ref="X145:X146" si="0">W145/W$141</f>
+        <v>0.13207547169811321</v>
+      </c>
+    </row>
+    <row r="146" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>11</v>
       </c>
@@ -10400,8 +10994,22 @@
       <c r="K146">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="U146">
+        <v>1</v>
+      </c>
+      <c r="V146" t="s">
+        <v>13</v>
+      </c>
+      <c r="W146">
+        <f>COUNTIF(Tabelle3[Reflexionstiefe],U146)</f>
+        <v>92</v>
+      </c>
+      <c r="X146" s="4">
+        <f t="shared" si="0"/>
+        <v>0.86792452830188682</v>
+      </c>
+    </row>
+    <row r="147" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>11</v>
       </c>
@@ -10436,7 +11044,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>11</v>
       </c>
@@ -10471,7 +11079,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>11</v>
       </c>
@@ -10505,8 +11113,11 @@
       <c r="K149">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="U149" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="150" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>11</v>
       </c>
@@ -10540,8 +11151,22 @@
       <c r="K150">
         <v>1</v>
       </c>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="U150">
+        <v>3</v>
+      </c>
+      <c r="V150" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="W150">
+        <f>COUNTIF(Tabelle3[Einschätzung Potenzial],U150)</f>
+        <v>9</v>
+      </c>
+      <c r="X150" s="4">
+        <f>W150/W$141</f>
+        <v>8.4905660377358486E-2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>11</v>
       </c>
@@ -10575,8 +11200,22 @@
       <c r="K151">
         <v>0.75</v>
       </c>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="U151">
+        <v>2</v>
+      </c>
+      <c r="V151" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="W151">
+        <f>COUNTIF(Tabelle3[Einschätzung Potenzial],U151)</f>
+        <v>19</v>
+      </c>
+      <c r="X151" s="4">
+        <f t="shared" ref="X151:X152" si="1">W151/W$141</f>
+        <v>0.17924528301886791</v>
+      </c>
+    </row>
+    <row r="152" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>11</v>
       </c>
@@ -10610,8 +11249,22 @@
       <c r="K152">
         <v>0.85</v>
       </c>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="U152">
+        <v>1</v>
+      </c>
+      <c r="V152" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="W152">
+        <f>COUNTIF(Tabelle3[Einschätzung Potenzial],U152)</f>
+        <v>2</v>
+      </c>
+      <c r="X152" s="4">
+        <f t="shared" si="1"/>
+        <v>1.8867924528301886E-2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>11</v>
       </c>
@@ -10645,8 +11298,22 @@
       <c r="K153">
         <v>0.6</v>
       </c>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="U153">
+        <v>0</v>
+      </c>
+      <c r="V153" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="W153">
+        <f>COUNTIF(Tabelle3[Einschätzung Potenzial],U153)</f>
+        <v>76</v>
+      </c>
+      <c r="X153" s="4">
+        <f t="shared" ref="X153" si="2">W153/W$141</f>
+        <v>0.71698113207547165</v>
+      </c>
+    </row>
+    <row r="154" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>11</v>
       </c>
@@ -10681,7 +11348,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>11</v>
       </c>
@@ -10716,7 +11383,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>11</v>
       </c>
@@ -10751,7 +11418,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>11</v>
       </c>
@@ -10786,7 +11453,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>11</v>
       </c>
@@ -10821,7 +11488,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>11</v>
       </c>
@@ -10856,7 +11523,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>11</v>
       </c>
@@ -52122,8 +52789,8 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="Z2:Z116">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="U2:U107">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -52133,9 +52800,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.78740157499999996" right="0.78740157499999996" top="0.984251969" bottom="0.984251969" header="0.4921259845" footer="0.4921259845"/>
-  <ignoredErrors>
-    <ignoredError sqref="AD2:AD40 AD81 AD83:AD84 AD100 AD104:AD116" calculatedColumn="1"/>
-  </ignoredErrors>
   <tableParts count="2">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
